--- a/03_内部設計/022-クラス仕様書/util/SplitKeywordUtilのクラス仕様書.xlsx
+++ b/03_内部設計/022-クラス仕様書/util/SplitKeywordUtilのクラス仕様書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52B3DCE-7E67-4796-97DA-A00A60960998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AD484F-9949-4BFE-896D-25627C6204CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">クラス仕様!$A$1:$BI$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（splitKeyword）'!$A$1:$BI$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（splitKeyword）'!$A$1:$BI$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -188,213 +188,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1.1) String型のArrayList、spacesを作成する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1.2) spacesに半角スペースと全角スペースを追加する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1) スペースのリストを作成する。</t>
-    <rPh sb="12" eb="14">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.2) spaceを拡張for文で繰り返し処理を行う。</t>
-    <rPh sb="11" eb="13">
-      <t>カクチョウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>カエ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.2.1) indexOfメソッドで先頭スペースのインデックス番号を検索する。</t>
-    <rPh sb="19" eb="21">
-      <t>セントウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ケンサク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.2.1.1) スペースが存在しない場合(戻り値が-1)は、continue文で繰り返し処理を抜ける。</t>
-    <rPh sb="14" eb="16">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>カエ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>ヌ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.1) Integer型のArrayList、breakIndexを作成する。</t>
-    <rPh sb="12" eb="13">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.2.1.2) スペースが存在する場合は、インデックス番号をbreakIndexに追加する。</t>
-    <rPh sb="28" eb="30">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.2.2) breakIndexの重複を削除する。</t>
-    <rPh sb="18" eb="20">
-      <t>チョウフク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.2.3) breakIndexを昇順に並べ替える。</t>
-    <rPh sb="18" eb="20">
-      <t>ショウジュン</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ナラ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3) スペースごとに文字を切り出し、リストに格納する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>(※インデックス番号は、rawKeywordの先頭を0とした時の番号。)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.1) String型のArrayList、resultを作成する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.1.1) breakIndexの要素数が0の場合、resultにrawKeywordを追加する。</t>
-    <rPh sb="18" eb="21">
-      <t>ヨウソスウ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.1.2) breakIndexの要素数が0でない場合、for文で繰り返し処理を行う。</t>
-    <rPh sb="32" eb="33">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.1.2.1) breakIndexに格納されているインデックス番号をもとに、rawKeywordを切り出す。</t>
-    <rPh sb="20" eb="22">
-      <t>カクノウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.1.2.2) resultに切り出した文字列を追加する。</t>
-    <rPh sb="16" eb="17">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>モジレツ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>4) resultを返す。</t>
-    <rPh sb="10" eb="11">
-      <t>カエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2) rawKeywordにおける、スペースのインデックス番号をリストにまとめる。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>rawKeyword</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>result</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>奈良田　岬</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -450,20 +243,189 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>検索キーワードからスペースごとに単語を切り出し、リストに格納して返す。</t>
+    <t>2) 1文字以上かつ、空白文字でない文字列を、正規表現として定義する。</t>
+    <rPh sb="4" eb="8">
+      <t>モジイジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>クウハクモジ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>セイキヒョウゲン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.1) Patternクラスのstaticメソッド、compileを呼び出す。</t>
+    <rPh sb="35" eb="36">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数として、"[\\S]+"、Pattern.UNICODE_CHARACTER_CLASSを渡す。</t>
     <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pattern型の変数pに戻り値を代入する。</t>
+    <rPh sb="13" eb="14">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ダイニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3) 検索キーワードが、2)で定義した正規表現と一致するかどうかをチェックする。</t>
+    <rPh sb="15" eb="17">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>セイキヒョウゲン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.1) Patternクラスのmatcherメソッドを呼び出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数として、rawKeywordを渡し、Matcher型の変数mに代入する。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ダイニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4) 正規表現と一致した文字列を、文字列型のリストに格納する。</t>
+    <rPh sb="3" eb="5">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>モジレツガタ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.1) String型のArrayList、resultを作成する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1) 戻り値として返すリストを生成する。</t>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.1) 正規表現と一致するとき、while文で繰り返し処理を行う。</t>
+    <rPh sb="22" eb="23">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.1.1) Matcherクラスのgroupメソッドで一致した文字列を取り出し、resultに追加する。</t>
+    <rPh sb="28" eb="30">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5) 戻り値を返す</t>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規表現を利用して検索キーワードから単語を切り出し、リストに格納して返す。</t>
+    <rPh sb="0" eb="4">
+      <t>セイキヒョウゲン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
       <t>ケンサク</t>
     </rPh>
-    <rPh sb="16" eb="18">
+    <rPh sb="18" eb="20">
       <t>タンゴ</t>
     </rPh>
-    <rPh sb="19" eb="20">
+    <rPh sb="21" eb="22">
       <t>キ</t>
     </rPh>
-    <rPh sb="28" eb="30">
+    <rPh sb="30" eb="32">
       <t>カクノウ</t>
     </rPh>
-    <rPh sb="32" eb="33">
+    <rPh sb="34" eb="35">
       <t>カエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -668,7 +630,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -741,53 +703,35 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -801,11 +745,23 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1157,85 +1113,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="32" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="31" t="s">
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
-      <c r="AB1" s="32" t="s">
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="31" t="s">
-        <v>63</v>
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="25" t="s">
+        <v>42</v>
       </c>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
-      <c r="AJ1" s="31"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
-      <c r="AM1" s="31"/>
-      <c r="AN1" s="31"/>
-      <c r="AO1" s="31"/>
-      <c r="AP1" s="31"/>
-      <c r="AQ1" s="32" t="s">
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
+      <c r="AK1" s="25"/>
+      <c r="AL1" s="25"/>
+      <c r="AM1" s="25"/>
+      <c r="AN1" s="25"/>
+      <c r="AO1" s="25"/>
+      <c r="AP1" s="25"/>
+      <c r="AQ1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="31" t="s">
+      <c r="AR1" s="24"/>
+      <c r="AS1" s="24"/>
+      <c r="AT1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" s="31"/>
-      <c r="AV1" s="31"/>
-      <c r="AW1" s="31"/>
-      <c r="AX1" s="31"/>
-      <c r="AY1" s="31"/>
-      <c r="AZ1" s="31"/>
-      <c r="BA1" s="32" t="s">
+      <c r="AU1" s="25"/>
+      <c r="AV1" s="25"/>
+      <c r="AW1" s="25"/>
+      <c r="AX1" s="25"/>
+      <c r="AY1" s="25"/>
+      <c r="AZ1" s="25"/>
+      <c r="BA1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-      <c r="BD1" s="29">
+      <c r="BB1" s="24"/>
+      <c r="BC1" s="24"/>
+      <c r="BD1" s="26">
         <v>45553</v>
       </c>
-      <c r="BE1" s="29"/>
-      <c r="BF1" s="29"/>
-      <c r="BG1" s="29"/>
-      <c r="BH1" s="29"/>
-      <c r="BI1" s="29"/>
+      <c r="BE1" s="26"/>
+      <c r="BF1" s="26"/>
+      <c r="BG1" s="26"/>
+      <c r="BH1" s="26"/>
+      <c r="BI1" s="26"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1435,82 +1391,82 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="32" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="32" t="s">
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="31" t="str">
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="25" t="str">
         <f>G5</f>
         <v>SplitKeywordUtil</v>
       </c>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="31"/>
-      <c r="AN2" s="31"/>
-      <c r="AO2" s="31"/>
-      <c r="AP2" s="31"/>
-      <c r="AQ2" s="32" t="s">
+      <c r="AF2" s="25"/>
+      <c r="AG2" s="25"/>
+      <c r="AH2" s="25"/>
+      <c r="AI2" s="25"/>
+      <c r="AJ2" s="25"/>
+      <c r="AK2" s="25"/>
+      <c r="AL2" s="25"/>
+      <c r="AM2" s="25"/>
+      <c r="AN2" s="25"/>
+      <c r="AO2" s="25"/>
+      <c r="AP2" s="25"/>
+      <c r="AQ2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="31" t="s">
-        <v>62</v>
+      <c r="AR2" s="24"/>
+      <c r="AS2" s="24"/>
+      <c r="AT2" s="25" t="s">
+        <v>41</v>
       </c>
-      <c r="AU2" s="31"/>
-      <c r="AV2" s="31"/>
-      <c r="AW2" s="31"/>
-      <c r="AX2" s="31"/>
-      <c r="AY2" s="31"/>
-      <c r="AZ2" s="31"/>
-      <c r="BA2" s="32" t="s">
+      <c r="AU2" s="25"/>
+      <c r="AV2" s="25"/>
+      <c r="AW2" s="25"/>
+      <c r="AX2" s="25"/>
+      <c r="AY2" s="25"/>
+      <c r="AZ2" s="25"/>
+      <c r="BA2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-      <c r="BD2" s="29">
+      <c r="BB2" s="24"/>
+      <c r="BC2" s="24"/>
+      <c r="BD2" s="26">
         <v>45566</v>
       </c>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
-      <c r="BI2" s="29"/>
+      <c r="BE2" s="26"/>
+      <c r="BF2" s="26"/>
+      <c r="BG2" s="26"/>
+      <c r="BH2" s="26"/>
+      <c r="BI2" s="26"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -1773,927 +1729,942 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="26" t="s">
-        <v>64</v>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="28" t="s">
+        <v>43</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="26"/>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="26"/>
-      <c r="AH4" s="26"/>
-      <c r="AI4" s="26"/>
-      <c r="AJ4" s="26"/>
-      <c r="AK4" s="26"/>
-      <c r="AL4" s="26"/>
-      <c r="AM4" s="26"/>
-      <c r="AN4" s="26"/>
-      <c r="AO4" s="26"/>
-      <c r="AP4" s="26"/>
-      <c r="AQ4" s="26"/>
-      <c r="AR4" s="26"/>
-      <c r="AS4" s="26"/>
-      <c r="AT4" s="26"/>
-      <c r="AU4" s="26"/>
-      <c r="AV4" s="26"/>
-      <c r="AW4" s="26"/>
-      <c r="AX4" s="26"/>
-      <c r="AY4" s="26"/>
-      <c r="AZ4" s="26"/>
-      <c r="BA4" s="26"/>
-      <c r="BB4" s="26"/>
-      <c r="BC4" s="26"/>
-      <c r="BD4" s="26"/>
-      <c r="BE4" s="26"/>
-      <c r="BF4" s="26"/>
-      <c r="BG4" s="26"/>
-      <c r="BH4" s="26"/>
-      <c r="BI4" s="26"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="26" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="26"/>
-      <c r="Y5" s="26"/>
-      <c r="Z5" s="26"/>
-      <c r="AA5" s="26"/>
-      <c r="AB5" s="26"/>
-      <c r="AC5" s="26"/>
-      <c r="AD5" s="26"/>
-      <c r="AE5" s="26"/>
-      <c r="AF5" s="26"/>
-      <c r="AG5" s="26"/>
-      <c r="AH5" s="26"/>
-      <c r="AI5" s="26"/>
-      <c r="AJ5" s="26"/>
-      <c r="AK5" s="26"/>
-      <c r="AL5" s="26"/>
-      <c r="AM5" s="26"/>
-      <c r="AN5" s="26"/>
-      <c r="AO5" s="26"/>
-      <c r="AP5" s="26"/>
-      <c r="AQ5" s="26"/>
-      <c r="AR5" s="26"/>
-      <c r="AS5" s="26"/>
-      <c r="AT5" s="26"/>
-      <c r="AU5" s="26"/>
-      <c r="AV5" s="26"/>
-      <c r="AW5" s="26"/>
-      <c r="AX5" s="26"/>
-      <c r="AY5" s="26"/>
-      <c r="AZ5" s="26"/>
-      <c r="BA5" s="26"/>
-      <c r="BB5" s="26"/>
-      <c r="BC5" s="26"/>
-      <c r="BD5" s="26"/>
-      <c r="BE5" s="26"/>
-      <c r="BF5" s="26"/>
-      <c r="BG5" s="26"/>
-      <c r="BH5" s="26"/>
-      <c r="BI5" s="26"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="26" t="s">
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="26"/>
-      <c r="W6" s="26"/>
-      <c r="X6" s="26"/>
-      <c r="Y6" s="26"/>
-      <c r="Z6" s="26"/>
-      <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AD6" s="28" t="s">
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="28"/>
-      <c r="AH6" s="28"/>
-      <c r="AI6" s="28"/>
-      <c r="AJ6" s="26" t="s">
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="27"/>
+      <c r="AG6" s="27"/>
+      <c r="AH6" s="27"/>
+      <c r="AI6" s="27"/>
+      <c r="AJ6" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="AK6" s="26"/>
-      <c r="AL6" s="26"/>
-      <c r="AM6" s="26"/>
-      <c r="AN6" s="26"/>
-      <c r="AO6" s="26"/>
-      <c r="AP6" s="26"/>
-      <c r="AQ6" s="26"/>
-      <c r="AR6" s="26"/>
-      <c r="AS6" s="26"/>
-      <c r="AT6" s="26"/>
-      <c r="AU6" s="26"/>
-      <c r="AV6" s="26"/>
-      <c r="AW6" s="26"/>
-      <c r="AX6" s="26"/>
-      <c r="AY6" s="26"/>
-      <c r="AZ6" s="26"/>
-      <c r="BA6" s="26"/>
-      <c r="BB6" s="26"/>
-      <c r="BC6" s="26"/>
-      <c r="BD6" s="26"/>
-      <c r="BE6" s="26"/>
-      <c r="BF6" s="26"/>
-      <c r="BG6" s="26"/>
-      <c r="BH6" s="26"/>
-      <c r="BI6" s="26"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28" t="s">
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="V8" s="28"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="28"/>
-      <c r="AE8" s="28" t="s">
+      <c r="V8" s="27"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="27"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="27"/>
+      <c r="AC8" s="27"/>
+      <c r="AD8" s="27"/>
+      <c r="AE8" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="AF8" s="28"/>
-      <c r="AG8" s="28"/>
-      <c r="AH8" s="28"/>
-      <c r="AI8" s="28"/>
-      <c r="AJ8" s="28"/>
-      <c r="AK8" s="28"/>
-      <c r="AL8" s="28"/>
-      <c r="AM8" s="28"/>
-      <c r="AN8" s="28"/>
-      <c r="AO8" s="28" t="s">
+      <c r="AF8" s="27"/>
+      <c r="AG8" s="27"/>
+      <c r="AH8" s="27"/>
+      <c r="AI8" s="27"/>
+      <c r="AJ8" s="27"/>
+      <c r="AK8" s="27"/>
+      <c r="AL8" s="27"/>
+      <c r="AM8" s="27"/>
+      <c r="AN8" s="27"/>
+      <c r="AO8" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="AP8" s="28"/>
-      <c r="AQ8" s="28"/>
-      <c r="AR8" s="28"/>
-      <c r="AS8" s="28"/>
-      <c r="AT8" s="28"/>
-      <c r="AU8" s="28"/>
-      <c r="AV8" s="28"/>
-      <c r="AW8" s="28"/>
-      <c r="AX8" s="28"/>
-      <c r="AY8" s="28"/>
-      <c r="AZ8" s="28"/>
-      <c r="BA8" s="28"/>
-      <c r="BB8" s="28"/>
-      <c r="BC8" s="28"/>
-      <c r="BD8" s="28"/>
-      <c r="BE8" s="28"/>
-      <c r="BF8" s="28"/>
-      <c r="BG8" s="28"/>
-      <c r="BH8" s="28"/>
-      <c r="BI8" s="28"/>
+      <c r="AP8" s="27"/>
+      <c r="AQ8" s="27"/>
+      <c r="AR8" s="27"/>
+      <c r="AS8" s="27"/>
+      <c r="AT8" s="27"/>
+      <c r="AU8" s="27"/>
+      <c r="AV8" s="27"/>
+      <c r="AW8" s="27"/>
+      <c r="AX8" s="27"/>
+      <c r="AY8" s="27"/>
+      <c r="AZ8" s="27"/>
+      <c r="BA8" s="27"/>
+      <c r="BB8" s="27"/>
+      <c r="BC8" s="27"/>
+      <c r="BD8" s="27"/>
+      <c r="BE8" s="27"/>
+      <c r="BF8" s="27"/>
+      <c r="BG8" s="27"/>
+      <c r="BH8" s="27"/>
+      <c r="BI8" s="27"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="27"/>
-      <c r="AC9" s="27"/>
-      <c r="AD9" s="27"/>
-      <c r="AE9" s="27"/>
-      <c r="AF9" s="27"/>
-      <c r="AG9" s="27"/>
-      <c r="AH9" s="27"/>
-      <c r="AI9" s="27"/>
-      <c r="AJ9" s="27"/>
-      <c r="AK9" s="27"/>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="27"/>
-      <c r="AN9" s="27"/>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="27"/>
-      <c r="AQ9" s="27"/>
-      <c r="AR9" s="27"/>
-      <c r="AS9" s="27"/>
-      <c r="AT9" s="27"/>
-      <c r="AU9" s="27"/>
-      <c r="AV9" s="27"/>
-      <c r="AW9" s="27"/>
-      <c r="AX9" s="27"/>
-      <c r="AY9" s="27"/>
-      <c r="AZ9" s="27"/>
-      <c r="BA9" s="27"/>
-      <c r="BB9" s="27"/>
-      <c r="BC9" s="27"/>
-      <c r="BD9" s="27"/>
-      <c r="BE9" s="27"/>
-      <c r="BF9" s="27"/>
-      <c r="BG9" s="27"/>
-      <c r="BH9" s="27"/>
-      <c r="BI9" s="27"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="31"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="31"/>
+      <c r="AH9" s="31"/>
+      <c r="AI9" s="31"/>
+      <c r="AJ9" s="31"/>
+      <c r="AK9" s="31"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="31"/>
+      <c r="AN9" s="31"/>
+      <c r="AO9" s="31"/>
+      <c r="AP9" s="31"/>
+      <c r="AQ9" s="31"/>
+      <c r="AR9" s="31"/>
+      <c r="AS9" s="31"/>
+      <c r="AT9" s="31"/>
+      <c r="AU9" s="31"/>
+      <c r="AV9" s="31"/>
+      <c r="AW9" s="31"/>
+      <c r="AX9" s="31"/>
+      <c r="AY9" s="31"/>
+      <c r="AZ9" s="31"/>
+      <c r="BA9" s="31"/>
+      <c r="BB9" s="31"/>
+      <c r="BC9" s="31"/>
+      <c r="BD9" s="31"/>
+      <c r="BE9" s="31"/>
+      <c r="BF9" s="31"/>
+      <c r="BG9" s="31"/>
+      <c r="BH9" s="31"/>
+      <c r="BI9" s="31"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
-      <c r="AA10" s="27"/>
-      <c r="AB10" s="27"/>
-      <c r="AC10" s="27"/>
-      <c r="AD10" s="27"/>
-      <c r="AE10" s="27"/>
-      <c r="AF10" s="27"/>
-      <c r="AG10" s="27"/>
-      <c r="AH10" s="27"/>
-      <c r="AI10" s="27"/>
-      <c r="AJ10" s="27"/>
-      <c r="AK10" s="27"/>
-      <c r="AL10" s="27"/>
-      <c r="AM10" s="27"/>
-      <c r="AN10" s="27"/>
-      <c r="AO10" s="27"/>
-      <c r="AP10" s="27"/>
-      <c r="AQ10" s="27"/>
-      <c r="AR10" s="27"/>
-      <c r="AS10" s="27"/>
-      <c r="AT10" s="27"/>
-      <c r="AU10" s="27"/>
-      <c r="AV10" s="27"/>
-      <c r="AW10" s="27"/>
-      <c r="AX10" s="27"/>
-      <c r="AY10" s="27"/>
-      <c r="AZ10" s="27"/>
-      <c r="BA10" s="27"/>
-      <c r="BB10" s="27"/>
-      <c r="BC10" s="27"/>
-      <c r="BD10" s="27"/>
-      <c r="BE10" s="27"/>
-      <c r="BF10" s="27"/>
-      <c r="BG10" s="27"/>
-      <c r="BH10" s="27"/>
-      <c r="BI10" s="27"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="31"/>
+      <c r="AE10" s="31"/>
+      <c r="AF10" s="31"/>
+      <c r="AG10" s="31"/>
+      <c r="AH10" s="31"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="31"/>
+      <c r="AK10" s="31"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="31"/>
+      <c r="AN10" s="31"/>
+      <c r="AO10" s="31"/>
+      <c r="AP10" s="31"/>
+      <c r="AQ10" s="31"/>
+      <c r="AR10" s="31"/>
+      <c r="AS10" s="31"/>
+      <c r="AT10" s="31"/>
+      <c r="AU10" s="31"/>
+      <c r="AV10" s="31"/>
+      <c r="AW10" s="31"/>
+      <c r="AX10" s="31"/>
+      <c r="AY10" s="31"/>
+      <c r="AZ10" s="31"/>
+      <c r="BA10" s="31"/>
+      <c r="BB10" s="31"/>
+      <c r="BC10" s="31"/>
+      <c r="BD10" s="31"/>
+      <c r="BE10" s="31"/>
+      <c r="BF10" s="31"/>
+      <c r="BG10" s="31"/>
+      <c r="BH10" s="31"/>
+      <c r="BI10" s="31"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="27"/>
-      <c r="Y11" s="27"/>
-      <c r="Z11" s="27"/>
-      <c r="AA11" s="27"/>
-      <c r="AB11" s="27"/>
-      <c r="AC11" s="27"/>
-      <c r="AD11" s="27"/>
-      <c r="AE11" s="27"/>
-      <c r="AF11" s="27"/>
-      <c r="AG11" s="27"/>
-      <c r="AH11" s="27"/>
-      <c r="AI11" s="27"/>
-      <c r="AJ11" s="27"/>
-      <c r="AK11" s="27"/>
-      <c r="AL11" s="27"/>
-      <c r="AM11" s="27"/>
-      <c r="AN11" s="27"/>
-      <c r="AO11" s="27"/>
-      <c r="AP11" s="27"/>
-      <c r="AQ11" s="27"/>
-      <c r="AR11" s="27"/>
-      <c r="AS11" s="27"/>
-      <c r="AT11" s="27"/>
-      <c r="AU11" s="27"/>
-      <c r="AV11" s="27"/>
-      <c r="AW11" s="27"/>
-      <c r="AX11" s="27"/>
-      <c r="AY11" s="27"/>
-      <c r="AZ11" s="27"/>
-      <c r="BA11" s="27"/>
-      <c r="BB11" s="27"/>
-      <c r="BC11" s="27"/>
-      <c r="BD11" s="27"/>
-      <c r="BE11" s="27"/>
-      <c r="BF11" s="27"/>
-      <c r="BG11" s="27"/>
-      <c r="BH11" s="27"/>
-      <c r="BI11" s="27"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="31"/>
+      <c r="AH11" s="31"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="31"/>
+      <c r="AK11" s="31"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="31"/>
+      <c r="AN11" s="31"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="31"/>
+      <c r="AQ11" s="31"/>
+      <c r="AR11" s="31"/>
+      <c r="AS11" s="31"/>
+      <c r="AT11" s="31"/>
+      <c r="AU11" s="31"/>
+      <c r="AV11" s="31"/>
+      <c r="AW11" s="31"/>
+      <c r="AX11" s="31"/>
+      <c r="AY11" s="31"/>
+      <c r="AZ11" s="31"/>
+      <c r="BA11" s="31"/>
+      <c r="BB11" s="31"/>
+      <c r="BC11" s="31"/>
+      <c r="BD11" s="31"/>
+      <c r="BE11" s="31"/>
+      <c r="BF11" s="31"/>
+      <c r="BG11" s="31"/>
+      <c r="BH11" s="31"/>
+      <c r="BI11" s="31"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="28"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="28"/>
-      <c r="W13" s="28"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="28"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="28"/>
-      <c r="AE13" s="28"/>
-      <c r="AF13" s="28"/>
-      <c r="AG13" s="28"/>
-      <c r="AH13" s="28"/>
-      <c r="AI13" s="28"/>
-      <c r="AJ13" s="28"/>
-      <c r="AK13" s="28"/>
-      <c r="AL13" s="28"/>
-      <c r="AM13" s="28"/>
-      <c r="AN13" s="28"/>
-      <c r="AO13" s="28"/>
-      <c r="AP13" s="28"/>
-      <c r="AQ13" s="28"/>
-      <c r="AR13" s="28"/>
-      <c r="AS13" s="28"/>
-      <c r="AT13" s="28"/>
-      <c r="AU13" s="28"/>
-      <c r="AV13" s="28"/>
-      <c r="AW13" s="28"/>
-      <c r="AX13" s="28"/>
-      <c r="AY13" s="28"/>
-      <c r="AZ13" s="28"/>
-      <c r="BA13" s="28"/>
-      <c r="BB13" s="28"/>
-      <c r="BC13" s="28"/>
-      <c r="BD13" s="28"/>
-      <c r="BE13" s="28"/>
-      <c r="BF13" s="28"/>
-      <c r="BG13" s="28"/>
-      <c r="BH13" s="28"/>
-      <c r="BI13" s="28"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="27"/>
+      <c r="AF13" s="27"/>
+      <c r="AG13" s="27"/>
+      <c r="AH13" s="27"/>
+      <c r="AI13" s="27"/>
+      <c r="AJ13" s="27"/>
+      <c r="AK13" s="27"/>
+      <c r="AL13" s="27"/>
+      <c r="AM13" s="27"/>
+      <c r="AN13" s="27"/>
+      <c r="AO13" s="27"/>
+      <c r="AP13" s="27"/>
+      <c r="AQ13" s="27"/>
+      <c r="AR13" s="27"/>
+      <c r="AS13" s="27"/>
+      <c r="AT13" s="27"/>
+      <c r="AU13" s="27"/>
+      <c r="AV13" s="27"/>
+      <c r="AW13" s="27"/>
+      <c r="AX13" s="27"/>
+      <c r="AY13" s="27"/>
+      <c r="AZ13" s="27"/>
+      <c r="BA13" s="27"/>
+      <c r="BB13" s="27"/>
+      <c r="BC13" s="27"/>
+      <c r="BD13" s="27"/>
+      <c r="BE13" s="27"/>
+      <c r="BF13" s="27"/>
+      <c r="BG13" s="27"/>
+      <c r="BH13" s="27"/>
+      <c r="BI13" s="27"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="44" t="s">
-        <v>65</v>
+      <c r="A14" s="32" t="s">
+        <v>44</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="45"/>
-      <c r="U14" s="45"/>
-      <c r="V14" s="45"/>
-      <c r="W14" s="45"/>
-      <c r="X14" s="45"/>
-      <c r="Y14" s="45"/>
-      <c r="Z14" s="45"/>
-      <c r="AA14" s="45"/>
-      <c r="AB14" s="45"/>
-      <c r="AC14" s="45"/>
-      <c r="AD14" s="45"/>
-      <c r="AE14" s="45"/>
-      <c r="AF14" s="45"/>
-      <c r="AG14" s="45"/>
-      <c r="AH14" s="45"/>
-      <c r="AI14" s="45"/>
-      <c r="AJ14" s="45"/>
-      <c r="AK14" s="45"/>
-      <c r="AL14" s="45"/>
-      <c r="AM14" s="45"/>
-      <c r="AN14" s="45"/>
-      <c r="AO14" s="45"/>
-      <c r="AP14" s="45"/>
-      <c r="AQ14" s="45"/>
-      <c r="AR14" s="45"/>
-      <c r="AS14" s="45"/>
-      <c r="AT14" s="45"/>
-      <c r="AU14" s="45"/>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
-      <c r="BB14" s="45"/>
-      <c r="BC14" s="45"/>
-      <c r="BD14" s="45"/>
-      <c r="BE14" s="45"/>
-      <c r="BF14" s="45"/>
-      <c r="BG14" s="45"/>
-      <c r="BH14" s="45"/>
-      <c r="BI14" s="45"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="33"/>
+      <c r="V14" s="33"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="33"/>
+      <c r="Y14" s="33"/>
+      <c r="Z14" s="33"/>
+      <c r="AA14" s="33"/>
+      <c r="AB14" s="33"/>
+      <c r="AC14" s="33"/>
+      <c r="AD14" s="33"/>
+      <c r="AE14" s="33"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="33"/>
+      <c r="AH14" s="33"/>
+      <c r="AI14" s="33"/>
+      <c r="AJ14" s="33"/>
+      <c r="AK14" s="33"/>
+      <c r="AL14" s="33"/>
+      <c r="AM14" s="33"/>
+      <c r="AN14" s="33"/>
+      <c r="AO14" s="33"/>
+      <c r="AP14" s="33"/>
+      <c r="AQ14" s="33"/>
+      <c r="AR14" s="33"/>
+      <c r="AS14" s="33"/>
+      <c r="AT14" s="33"/>
+      <c r="AU14" s="33"/>
+      <c r="AV14" s="33"/>
+      <c r="AW14" s="33"/>
+      <c r="AX14" s="33"/>
+      <c r="AY14" s="33"/>
+      <c r="AZ14" s="33"/>
+      <c r="BA14" s="33"/>
+      <c r="BB14" s="33"/>
+      <c r="BC14" s="33"/>
+      <c r="BD14" s="33"/>
+      <c r="BE14" s="33"/>
+      <c r="BF14" s="33"/>
+      <c r="BG14" s="33"/>
+      <c r="BH14" s="33"/>
+      <c r="BI14" s="33"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="45"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
-      <c r="U15" s="45"/>
-      <c r="V15" s="45"/>
-      <c r="W15" s="45"/>
-      <c r="X15" s="45"/>
-      <c r="Y15" s="45"/>
-      <c r="Z15" s="45"/>
-      <c r="AA15" s="45"/>
-      <c r="AB15" s="45"/>
-      <c r="AC15" s="45"/>
-      <c r="AD15" s="45"/>
-      <c r="AE15" s="45"/>
-      <c r="AF15" s="45"/>
-      <c r="AG15" s="45"/>
-      <c r="AH15" s="45"/>
-      <c r="AI15" s="45"/>
-      <c r="AJ15" s="45"/>
-      <c r="AK15" s="45"/>
-      <c r="AL15" s="45"/>
-      <c r="AM15" s="45"/>
-      <c r="AN15" s="45"/>
-      <c r="AO15" s="45"/>
-      <c r="AP15" s="45"/>
-      <c r="AQ15" s="45"/>
-      <c r="AR15" s="45"/>
-      <c r="AS15" s="45"/>
-      <c r="AT15" s="45"/>
-      <c r="AU15" s="45"/>
-      <c r="AV15" s="45"/>
-      <c r="AW15" s="45"/>
-      <c r="AX15" s="45"/>
-      <c r="AY15" s="45"/>
-      <c r="AZ15" s="45"/>
-      <c r="BA15" s="45"/>
-      <c r="BB15" s="45"/>
-      <c r="BC15" s="45"/>
-      <c r="BD15" s="45"/>
-      <c r="BE15" s="45"/>
-      <c r="BF15" s="45"/>
-      <c r="BG15" s="45"/>
-      <c r="BH15" s="45"/>
-      <c r="BI15" s="45"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="33"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="33"/>
+      <c r="V15" s="33"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="33"/>
+      <c r="Y15" s="33"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="33"/>
+      <c r="AC15" s="33"/>
+      <c r="AD15" s="33"/>
+      <c r="AE15" s="33"/>
+      <c r="AF15" s="33"/>
+      <c r="AG15" s="33"/>
+      <c r="AH15" s="33"/>
+      <c r="AI15" s="33"/>
+      <c r="AJ15" s="33"/>
+      <c r="AK15" s="33"/>
+      <c r="AL15" s="33"/>
+      <c r="AM15" s="33"/>
+      <c r="AN15" s="33"/>
+      <c r="AO15" s="33"/>
+      <c r="AP15" s="33"/>
+      <c r="AQ15" s="33"/>
+      <c r="AR15" s="33"/>
+      <c r="AS15" s="33"/>
+      <c r="AT15" s="33"/>
+      <c r="AU15" s="33"/>
+      <c r="AV15" s="33"/>
+      <c r="AW15" s="33"/>
+      <c r="AX15" s="33"/>
+      <c r="AY15" s="33"/>
+      <c r="AZ15" s="33"/>
+      <c r="BA15" s="33"/>
+      <c r="BB15" s="33"/>
+      <c r="BC15" s="33"/>
+      <c r="BD15" s="33"/>
+      <c r="BE15" s="33"/>
+      <c r="BF15" s="33"/>
+      <c r="BG15" s="33"/>
+      <c r="BH15" s="33"/>
+      <c r="BI15" s="33"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="45"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
-      <c r="U16" s="45"/>
-      <c r="V16" s="45"/>
-      <c r="W16" s="45"/>
-      <c r="X16" s="45"/>
-      <c r="Y16" s="45"/>
-      <c r="Z16" s="45"/>
-      <c r="AA16" s="45"/>
-      <c r="AB16" s="45"/>
-      <c r="AC16" s="45"/>
-      <c r="AD16" s="45"/>
-      <c r="AE16" s="45"/>
-      <c r="AF16" s="45"/>
-      <c r="AG16" s="45"/>
-      <c r="AH16" s="45"/>
-      <c r="AI16" s="45"/>
-      <c r="AJ16" s="45"/>
-      <c r="AK16" s="45"/>
-      <c r="AL16" s="45"/>
-      <c r="AM16" s="45"/>
-      <c r="AN16" s="45"/>
-      <c r="AO16" s="45"/>
-      <c r="AP16" s="45"/>
-      <c r="AQ16" s="45"/>
-      <c r="AR16" s="45"/>
-      <c r="AS16" s="45"/>
-      <c r="AT16" s="45"/>
-      <c r="AU16" s="45"/>
-      <c r="AV16" s="45"/>
-      <c r="AW16" s="45"/>
-      <c r="AX16" s="45"/>
-      <c r="AY16" s="45"/>
-      <c r="AZ16" s="45"/>
-      <c r="BA16" s="45"/>
-      <c r="BB16" s="45"/>
-      <c r="BC16" s="45"/>
-      <c r="BD16" s="45"/>
-      <c r="BE16" s="45"/>
-      <c r="BF16" s="45"/>
-      <c r="BG16" s="45"/>
-      <c r="BH16" s="45"/>
-      <c r="BI16" s="45"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="33"/>
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="33"/>
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="33"/>
+      <c r="AH16" s="33"/>
+      <c r="AI16" s="33"/>
+      <c r="AJ16" s="33"/>
+      <c r="AK16" s="33"/>
+      <c r="AL16" s="33"/>
+      <c r="AM16" s="33"/>
+      <c r="AN16" s="33"/>
+      <c r="AO16" s="33"/>
+      <c r="AP16" s="33"/>
+      <c r="AQ16" s="33"/>
+      <c r="AR16" s="33"/>
+      <c r="AS16" s="33"/>
+      <c r="AT16" s="33"/>
+      <c r="AU16" s="33"/>
+      <c r="AV16" s="33"/>
+      <c r="AW16" s="33"/>
+      <c r="AX16" s="33"/>
+      <c r="AY16" s="33"/>
+      <c r="AZ16" s="33"/>
+      <c r="BA16" s="33"/>
+      <c r="BB16" s="33"/>
+      <c r="BC16" s="33"/>
+      <c r="BD16" s="33"/>
+      <c r="BE16" s="33"/>
+      <c r="BF16" s="33"/>
+      <c r="BG16" s="33"/>
+      <c r="BH16" s="33"/>
+      <c r="BI16" s="33"/>
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="45"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="45"/>
-      <c r="U17" s="45"/>
-      <c r="V17" s="45"/>
-      <c r="W17" s="45"/>
-      <c r="X17" s="45"/>
-      <c r="Y17" s="45"/>
-      <c r="Z17" s="45"/>
-      <c r="AA17" s="45"/>
-      <c r="AB17" s="45"/>
-      <c r="AC17" s="45"/>
-      <c r="AD17" s="45"/>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="45"/>
-      <c r="AG17" s="45"/>
-      <c r="AH17" s="45"/>
-      <c r="AI17" s="45"/>
-      <c r="AJ17" s="45"/>
-      <c r="AK17" s="45"/>
-      <c r="AL17" s="45"/>
-      <c r="AM17" s="45"/>
-      <c r="AN17" s="45"/>
-      <c r="AO17" s="45"/>
-      <c r="AP17" s="45"/>
-      <c r="AQ17" s="45"/>
-      <c r="AR17" s="45"/>
-      <c r="AS17" s="45"/>
-      <c r="AT17" s="45"/>
-      <c r="AU17" s="45"/>
-      <c r="AV17" s="45"/>
-      <c r="AW17" s="45"/>
-      <c r="AX17" s="45"/>
-      <c r="AY17" s="45"/>
-      <c r="AZ17" s="45"/>
-      <c r="BA17" s="45"/>
-      <c r="BB17" s="45"/>
-      <c r="BC17" s="45"/>
-      <c r="BD17" s="45"/>
-      <c r="BE17" s="45"/>
-      <c r="BF17" s="45"/>
-      <c r="BG17" s="45"/>
-      <c r="BH17" s="45"/>
-      <c r="BI17" s="45"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="33"/>
+      <c r="AA17" s="33"/>
+      <c r="AB17" s="33"/>
+      <c r="AC17" s="33"/>
+      <c r="AD17" s="33"/>
+      <c r="AE17" s="33"/>
+      <c r="AF17" s="33"/>
+      <c r="AG17" s="33"/>
+      <c r="AH17" s="33"/>
+      <c r="AI17" s="33"/>
+      <c r="AJ17" s="33"/>
+      <c r="AK17" s="33"/>
+      <c r="AL17" s="33"/>
+      <c r="AM17" s="33"/>
+      <c r="AN17" s="33"/>
+      <c r="AO17" s="33"/>
+      <c r="AP17" s="33"/>
+      <c r="AQ17" s="33"/>
+      <c r="AR17" s="33"/>
+      <c r="AS17" s="33"/>
+      <c r="AT17" s="33"/>
+      <c r="AU17" s="33"/>
+      <c r="AV17" s="33"/>
+      <c r="AW17" s="33"/>
+      <c r="AX17" s="33"/>
+      <c r="AY17" s="33"/>
+      <c r="AZ17" s="33"/>
+      <c r="BA17" s="33"/>
+      <c r="BB17" s="33"/>
+      <c r="BC17" s="33"/>
+      <c r="BD17" s="33"/>
+      <c r="BE17" s="33"/>
+      <c r="BF17" s="33"/>
+      <c r="BG17" s="33"/>
+      <c r="BH17" s="33"/>
+      <c r="BI17" s="33"/>
     </row>
     <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
-      <c r="U18" s="45"/>
-      <c r="V18" s="45"/>
-      <c r="W18" s="45"/>
-      <c r="X18" s="45"/>
-      <c r="Y18" s="45"/>
-      <c r="Z18" s="45"/>
-      <c r="AA18" s="45"/>
-      <c r="AB18" s="45"/>
-      <c r="AC18" s="45"/>
-      <c r="AD18" s="45"/>
-      <c r="AE18" s="45"/>
-      <c r="AF18" s="45"/>
-      <c r="AG18" s="45"/>
-      <c r="AH18" s="45"/>
-      <c r="AI18" s="45"/>
-      <c r="AJ18" s="45"/>
-      <c r="AK18" s="45"/>
-      <c r="AL18" s="45"/>
-      <c r="AM18" s="45"/>
-      <c r="AN18" s="45"/>
-      <c r="AO18" s="45"/>
-      <c r="AP18" s="45"/>
-      <c r="AQ18" s="45"/>
-      <c r="AR18" s="45"/>
-      <c r="AS18" s="45"/>
-      <c r="AT18" s="45"/>
-      <c r="AU18" s="45"/>
-      <c r="AV18" s="45"/>
-      <c r="AW18" s="45"/>
-      <c r="AX18" s="45"/>
-      <c r="AY18" s="45"/>
-      <c r="AZ18" s="45"/>
-      <c r="BA18" s="45"/>
-      <c r="BB18" s="45"/>
-      <c r="BC18" s="45"/>
-      <c r="BD18" s="45"/>
-      <c r="BE18" s="45"/>
-      <c r="BF18" s="45"/>
-      <c r="BG18" s="45"/>
-      <c r="BH18" s="45"/>
-      <c r="BI18" s="45"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="33"/>
+      <c r="AA18" s="33"/>
+      <c r="AB18" s="33"/>
+      <c r="AC18" s="33"/>
+      <c r="AD18" s="33"/>
+      <c r="AE18" s="33"/>
+      <c r="AF18" s="33"/>
+      <c r="AG18" s="33"/>
+      <c r="AH18" s="33"/>
+      <c r="AI18" s="33"/>
+      <c r="AJ18" s="33"/>
+      <c r="AK18" s="33"/>
+      <c r="AL18" s="33"/>
+      <c r="AM18" s="33"/>
+      <c r="AN18" s="33"/>
+      <c r="AO18" s="33"/>
+      <c r="AP18" s="33"/>
+      <c r="AQ18" s="33"/>
+      <c r="AR18" s="33"/>
+      <c r="AS18" s="33"/>
+      <c r="AT18" s="33"/>
+      <c r="AU18" s="33"/>
+      <c r="AV18" s="33"/>
+      <c r="AW18" s="33"/>
+      <c r="AX18" s="33"/>
+      <c r="AY18" s="33"/>
+      <c r="AZ18" s="33"/>
+      <c r="BA18" s="33"/>
+      <c r="BB18" s="33"/>
+      <c r="BC18" s="33"/>
+      <c r="BD18" s="33"/>
+      <c r="BE18" s="33"/>
+      <c r="BF18" s="33"/>
+      <c r="BG18" s="33"/>
+      <c r="BH18" s="33"/>
+      <c r="BI18" s="33"/>
     </row>
     <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="45"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="45"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
-      <c r="T19" s="45"/>
-      <c r="U19" s="45"/>
-      <c r="V19" s="45"/>
-      <c r="W19" s="45"/>
-      <c r="X19" s="45"/>
-      <c r="Y19" s="45"/>
-      <c r="Z19" s="45"/>
-      <c r="AA19" s="45"/>
-      <c r="AB19" s="45"/>
-      <c r="AC19" s="45"/>
-      <c r="AD19" s="45"/>
-      <c r="AE19" s="45"/>
-      <c r="AF19" s="45"/>
-      <c r="AG19" s="45"/>
-      <c r="AH19" s="45"/>
-      <c r="AI19" s="45"/>
-      <c r="AJ19" s="45"/>
-      <c r="AK19" s="45"/>
-      <c r="AL19" s="45"/>
-      <c r="AM19" s="45"/>
-      <c r="AN19" s="45"/>
-      <c r="AO19" s="45"/>
-      <c r="AP19" s="45"/>
-      <c r="AQ19" s="45"/>
-      <c r="AR19" s="45"/>
-      <c r="AS19" s="45"/>
-      <c r="AT19" s="45"/>
-      <c r="AU19" s="45"/>
-      <c r="AV19" s="45"/>
-      <c r="AW19" s="45"/>
-      <c r="AX19" s="45"/>
-      <c r="AY19" s="45"/>
-      <c r="AZ19" s="45"/>
-      <c r="BA19" s="45"/>
-      <c r="BB19" s="45"/>
-      <c r="BC19" s="45"/>
-      <c r="BD19" s="45"/>
-      <c r="BE19" s="45"/>
-      <c r="BF19" s="45"/>
-      <c r="BG19" s="45"/>
-      <c r="BH19" s="45"/>
-      <c r="BI19" s="45"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="33"/>
+      <c r="AC19" s="33"/>
+      <c r="AD19" s="33"/>
+      <c r="AE19" s="33"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="33"/>
+      <c r="AH19" s="33"/>
+      <c r="AI19" s="33"/>
+      <c r="AJ19" s="33"/>
+      <c r="AK19" s="33"/>
+      <c r="AL19" s="33"/>
+      <c r="AM19" s="33"/>
+      <c r="AN19" s="33"/>
+      <c r="AO19" s="33"/>
+      <c r="AP19" s="33"/>
+      <c r="AQ19" s="33"/>
+      <c r="AR19" s="33"/>
+      <c r="AS19" s="33"/>
+      <c r="AT19" s="33"/>
+      <c r="AU19" s="33"/>
+      <c r="AV19" s="33"/>
+      <c r="AW19" s="33"/>
+      <c r="AX19" s="33"/>
+      <c r="AY19" s="33"/>
+      <c r="AZ19" s="33"/>
+      <c r="BA19" s="33"/>
+      <c r="BB19" s="33"/>
+      <c r="BC19" s="33"/>
+      <c r="BD19" s="33"/>
+      <c r="BE19" s="33"/>
+      <c r="BF19" s="33"/>
+      <c r="BG19" s="33"/>
+      <c r="BH19" s="33"/>
+      <c r="BI19" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="A14:BI19"/>
+    <mergeCell ref="A13:BI13"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="U10:AD10"/>
+    <mergeCell ref="AE10:AN10"/>
+    <mergeCell ref="AO10:BI10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="K11:T11"/>
+    <mergeCell ref="U11:AD11"/>
+    <mergeCell ref="AE11:AN11"/>
+    <mergeCell ref="AO11:BI11"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="U8:AD8"/>
+    <mergeCell ref="AE8:AN8"/>
+    <mergeCell ref="AO8:BI8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="K9:T9"/>
+    <mergeCell ref="U9:AD9"/>
+    <mergeCell ref="AE9:AN9"/>
+    <mergeCell ref="AO9:BI9"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
@@ -2710,29 +2681,14 @@
     <mergeCell ref="R2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="K9:T9"/>
-    <mergeCell ref="U9:AD9"/>
-    <mergeCell ref="AE9:AN9"/>
-    <mergeCell ref="AO9:BI9"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:T8"/>
-    <mergeCell ref="U8:AD8"/>
-    <mergeCell ref="AE8:AN8"/>
-    <mergeCell ref="AO8:BI8"/>
-    <mergeCell ref="A14:BI19"/>
-    <mergeCell ref="A13:BI13"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K10:T10"/>
-    <mergeCell ref="U10:AD10"/>
-    <mergeCell ref="AE10:AN10"/>
-    <mergeCell ref="AO10:BI10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="K11:T11"/>
-    <mergeCell ref="U11:AD11"/>
-    <mergeCell ref="AE11:AN11"/>
-    <mergeCell ref="AO11:BI11"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -2744,93 +2700,93 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IX41"/>
+  <dimension ref="A1:IX28"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="2.453125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="32" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="31" t="s">
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
-      <c r="AB1" s="32" t="s">
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="31" t="str">
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="25" t="str">
         <f>クラス仕様!AE1</f>
         <v>商品検索</v>
       </c>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
-      <c r="AJ1" s="31"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
-      <c r="AM1" s="31"/>
-      <c r="AN1" s="31"/>
-      <c r="AO1" s="31"/>
-      <c r="AP1" s="31"/>
-      <c r="AQ1" s="32" t="s">
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
+      <c r="AK1" s="25"/>
+      <c r="AL1" s="25"/>
+      <c r="AM1" s="25"/>
+      <c r="AN1" s="25"/>
+      <c r="AO1" s="25"/>
+      <c r="AP1" s="25"/>
+      <c r="AQ1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="31" t="s">
+      <c r="AR1" s="24"/>
+      <c r="AS1" s="24"/>
+      <c r="AT1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" s="31"/>
-      <c r="AV1" s="31"/>
-      <c r="AW1" s="31"/>
-      <c r="AX1" s="31"/>
-      <c r="AY1" s="31"/>
-      <c r="AZ1" s="31"/>
-      <c r="BA1" s="32" t="s">
+      <c r="AU1" s="25"/>
+      <c r="AV1" s="25"/>
+      <c r="AW1" s="25"/>
+      <c r="AX1" s="25"/>
+      <c r="AY1" s="25"/>
+      <c r="AZ1" s="25"/>
+      <c r="BA1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-      <c r="BD1" s="43">
+      <c r="BB1" s="24"/>
+      <c r="BC1" s="24"/>
+      <c r="BD1" s="37">
         <v>45553</v>
       </c>
-      <c r="BE1" s="43"/>
-      <c r="BF1" s="43"/>
-      <c r="BG1" s="43"/>
-      <c r="BH1" s="43"/>
-      <c r="BI1" s="43"/>
+      <c r="BE1" s="37"/>
+      <c r="BF1" s="37"/>
+      <c r="BG1" s="37"/>
+      <c r="BH1" s="37"/>
+      <c r="BI1" s="37"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -3030,82 +2986,82 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="32" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="32" t="s">
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="31" t="str">
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="25" t="str">
         <f>クラス仕様!G5</f>
         <v>SplitKeywordUtil</v>
       </c>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="31"/>
-      <c r="AN2" s="31"/>
-      <c r="AO2" s="31"/>
-      <c r="AP2" s="31"/>
-      <c r="AQ2" s="32" t="s">
+      <c r="AF2" s="25"/>
+      <c r="AG2" s="25"/>
+      <c r="AH2" s="25"/>
+      <c r="AI2" s="25"/>
+      <c r="AJ2" s="25"/>
+      <c r="AK2" s="25"/>
+      <c r="AL2" s="25"/>
+      <c r="AM2" s="25"/>
+      <c r="AN2" s="25"/>
+      <c r="AO2" s="25"/>
+      <c r="AP2" s="25"/>
+      <c r="AQ2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="31" t="s">
-        <v>62</v>
+      <c r="AR2" s="24"/>
+      <c r="AS2" s="24"/>
+      <c r="AT2" s="25" t="s">
+        <v>41</v>
       </c>
-      <c r="AU2" s="31"/>
-      <c r="AV2" s="31"/>
-      <c r="AW2" s="31"/>
-      <c r="AX2" s="31"/>
-      <c r="AY2" s="31"/>
-      <c r="AZ2" s="31"/>
-      <c r="BA2" s="32" t="s">
+      <c r="AU2" s="25"/>
+      <c r="AV2" s="25"/>
+      <c r="AW2" s="25"/>
+      <c r="AX2" s="25"/>
+      <c r="AY2" s="25"/>
+      <c r="AZ2" s="25"/>
+      <c r="BA2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-      <c r="BD2" s="40">
-        <v>45566</v>
+      <c r="BB2" s="24"/>
+      <c r="BC2" s="24"/>
+      <c r="BD2" s="34">
+        <v>45583</v>
       </c>
-      <c r="BE2" s="41"/>
-      <c r="BF2" s="41"/>
-      <c r="BG2" s="41"/>
-      <c r="BH2" s="41"/>
-      <c r="BI2" s="42"/>
+      <c r="BE2" s="35"/>
+      <c r="BF2" s="35"/>
+      <c r="BG2" s="35"/>
+      <c r="BH2" s="35"/>
+      <c r="BI2" s="36"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3368,71 +3324,71 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="26" t="s">
-        <v>66</v>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="28" t="s">
+        <v>58</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="26"/>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="26"/>
-      <c r="AH4" s="26"/>
-      <c r="AI4" s="26"/>
-      <c r="AJ4" s="26"/>
-      <c r="AK4" s="26"/>
-      <c r="AL4" s="26"/>
-      <c r="AM4" s="26"/>
-      <c r="AN4" s="26"/>
-      <c r="AO4" s="26"/>
-      <c r="AP4" s="26"/>
-      <c r="AQ4" s="26"/>
-      <c r="AR4" s="26"/>
-      <c r="AS4" s="26"/>
-      <c r="AT4" s="26"/>
-      <c r="AU4" s="26"/>
-      <c r="AV4" s="26"/>
-      <c r="AW4" s="26"/>
-      <c r="AX4" s="26"/>
-      <c r="AY4" s="26"/>
-      <c r="AZ4" s="26"/>
-      <c r="BA4" s="26"/>
-      <c r="BB4" s="26"/>
-      <c r="BC4" s="26"/>
-      <c r="BD4" s="26"/>
-      <c r="BE4" s="26"/>
-      <c r="BF4" s="26"/>
-      <c r="BG4" s="26"/>
-      <c r="BH4" s="26"/>
-      <c r="BI4" s="26"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -3632,71 +3588,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="26" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="26"/>
-      <c r="Y5" s="26"/>
-      <c r="Z5" s="26"/>
-      <c r="AA5" s="26"/>
-      <c r="AB5" s="26"/>
-      <c r="AC5" s="26"/>
-      <c r="AD5" s="26"/>
-      <c r="AE5" s="26"/>
-      <c r="AF5" s="26"/>
-      <c r="AG5" s="26"/>
-      <c r="AH5" s="26"/>
-      <c r="AI5" s="26"/>
-      <c r="AJ5" s="26"/>
-      <c r="AK5" s="26"/>
-      <c r="AL5" s="26"/>
-      <c r="AM5" s="26"/>
-      <c r="AN5" s="26"/>
-      <c r="AO5" s="26"/>
-      <c r="AP5" s="26"/>
-      <c r="AQ5" s="26"/>
-      <c r="AR5" s="26"/>
-      <c r="AS5" s="26"/>
-      <c r="AT5" s="26"/>
-      <c r="AU5" s="26"/>
-      <c r="AV5" s="26"/>
-      <c r="AW5" s="26"/>
-      <c r="AX5" s="26"/>
-      <c r="AY5" s="26"/>
-      <c r="AZ5" s="26"/>
-      <c r="BA5" s="26"/>
-      <c r="BB5" s="26"/>
-      <c r="BC5" s="26"/>
-      <c r="BD5" s="26"/>
-      <c r="BE5" s="26"/>
-      <c r="BF5" s="26"/>
-      <c r="BG5" s="26"/>
-      <c r="BH5" s="26"/>
-      <c r="BI5" s="26"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -4156,75 +4112,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36" t="s">
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="36"/>
-      <c r="AD7" s="36"/>
-      <c r="AE7" s="36" t="s">
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="41"/>
+      <c r="Z7" s="41"/>
+      <c r="AA7" s="41"/>
+      <c r="AB7" s="41"/>
+      <c r="AC7" s="41"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="36"/>
-      <c r="AG7" s="36"/>
-      <c r="AH7" s="36"/>
-      <c r="AI7" s="36"/>
-      <c r="AJ7" s="36"/>
-      <c r="AK7" s="36"/>
-      <c r="AL7" s="36"/>
-      <c r="AM7" s="36"/>
-      <c r="AN7" s="36"/>
-      <c r="AO7" s="36"/>
-      <c r="AP7" s="36"/>
-      <c r="AQ7" s="36"/>
-      <c r="AR7" s="36"/>
-      <c r="AS7" s="36"/>
-      <c r="AT7" s="36"/>
-      <c r="AU7" s="36"/>
-      <c r="AV7" s="36"/>
-      <c r="AW7" s="36"/>
-      <c r="AX7" s="36"/>
-      <c r="AY7" s="36"/>
-      <c r="AZ7" s="36"/>
-      <c r="BA7" s="36"/>
-      <c r="BB7" s="36"/>
-      <c r="BC7" s="36"/>
-      <c r="BD7" s="36"/>
-      <c r="BE7" s="36"/>
-      <c r="BF7" s="36"/>
-      <c r="BG7" s="36"/>
-      <c r="BH7" s="36"/>
-      <c r="BI7" s="36"/>
+      <c r="AF7" s="41"/>
+      <c r="AG7" s="41"/>
+      <c r="AH7" s="41"/>
+      <c r="AI7" s="41"/>
+      <c r="AJ7" s="41"/>
+      <c r="AK7" s="41"/>
+      <c r="AL7" s="41"/>
+      <c r="AM7" s="41"/>
+      <c r="AN7" s="41"/>
+      <c r="AO7" s="41"/>
+      <c r="AP7" s="41"/>
+      <c r="AQ7" s="41"/>
+      <c r="AR7" s="41"/>
+      <c r="AS7" s="41"/>
+      <c r="AT7" s="41"/>
+      <c r="AU7" s="41"/>
+      <c r="AV7" s="41"/>
+      <c r="AW7" s="41"/>
+      <c r="AX7" s="41"/>
+      <c r="AY7" s="41"/>
+      <c r="AZ7" s="41"/>
+      <c r="BA7" s="41"/>
+      <c r="BB7" s="41"/>
+      <c r="BC7" s="41"/>
+      <c r="BD7" s="41"/>
+      <c r="BE7" s="41"/>
+      <c r="BF7" s="41"/>
+      <c r="BG7" s="41"/>
+      <c r="BH7" s="41"/>
+      <c r="BI7" s="41"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -4424,75 +4380,75 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="37" t="s">
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="37" t="s">
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="38"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="38"/>
-      <c r="AC8" s="38"/>
-      <c r="AD8" s="39"/>
-      <c r="AE8" s="37" t="s">
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="39"/>
+      <c r="V8" s="39"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="39"/>
+      <c r="AB8" s="39"/>
+      <c r="AC8" s="39"/>
+      <c r="AD8" s="40"/>
+      <c r="AE8" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="AF8" s="38"/>
-      <c r="AG8" s="38"/>
-      <c r="AH8" s="38"/>
-      <c r="AI8" s="38"/>
-      <c r="AJ8" s="38"/>
-      <c r="AK8" s="38"/>
-      <c r="AL8" s="38"/>
-      <c r="AM8" s="38"/>
-      <c r="AN8" s="38"/>
-      <c r="AO8" s="38"/>
-      <c r="AP8" s="38"/>
-      <c r="AQ8" s="38"/>
-      <c r="AR8" s="38"/>
-      <c r="AS8" s="38"/>
-      <c r="AT8" s="38"/>
-      <c r="AU8" s="38"/>
-      <c r="AV8" s="38"/>
-      <c r="AW8" s="38"/>
-      <c r="AX8" s="38"/>
-      <c r="AY8" s="38"/>
-      <c r="AZ8" s="38"/>
-      <c r="BA8" s="38"/>
-      <c r="BB8" s="38"/>
-      <c r="BC8" s="38"/>
-      <c r="BD8" s="38"/>
-      <c r="BE8" s="38"/>
-      <c r="BF8" s="38"/>
-      <c r="BG8" s="38"/>
-      <c r="BH8" s="38"/>
-      <c r="BI8" s="39"/>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="39"/>
+      <c r="AH8" s="39"/>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="39"/>
+      <c r="AK8" s="39"/>
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="39"/>
+      <c r="AN8" s="39"/>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="39"/>
+      <c r="AQ8" s="39"/>
+      <c r="AR8" s="39"/>
+      <c r="AS8" s="39"/>
+      <c r="AT8" s="39"/>
+      <c r="AU8" s="39"/>
+      <c r="AV8" s="39"/>
+      <c r="AW8" s="39"/>
+      <c r="AX8" s="39"/>
+      <c r="AY8" s="39"/>
+      <c r="AZ8" s="39"/>
+      <c r="BA8" s="39"/>
+      <c r="BB8" s="39"/>
+      <c r="BC8" s="39"/>
+      <c r="BD8" s="39"/>
+      <c r="BE8" s="39"/>
+      <c r="BF8" s="39"/>
+      <c r="BG8" s="39"/>
+      <c r="BH8" s="39"/>
+      <c r="BI8" s="40"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -4692,75 +4648,75 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="35" t="s">
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35" t="s">
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="35"/>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="35"/>
-      <c r="AE9" s="35" t="s">
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="43"/>
+      <c r="Y9" s="43"/>
+      <c r="Z9" s="43"/>
+      <c r="AA9" s="43"/>
+      <c r="AB9" s="43"/>
+      <c r="AC9" s="43"/>
+      <c r="AD9" s="43"/>
+      <c r="AE9" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AF9" s="35"/>
-      <c r="AG9" s="35"/>
-      <c r="AH9" s="35"/>
-      <c r="AI9" s="35"/>
-      <c r="AJ9" s="35"/>
-      <c r="AK9" s="35"/>
-      <c r="AL9" s="35"/>
-      <c r="AM9" s="35"/>
-      <c r="AN9" s="35"/>
-      <c r="AO9" s="35"/>
-      <c r="AP9" s="35"/>
-      <c r="AQ9" s="35"/>
-      <c r="AR9" s="35"/>
-      <c r="AS9" s="35"/>
-      <c r="AT9" s="35"/>
-      <c r="AU9" s="35"/>
-      <c r="AV9" s="35"/>
-      <c r="AW9" s="35"/>
-      <c r="AX9" s="35"/>
-      <c r="AY9" s="35"/>
-      <c r="AZ9" s="35"/>
-      <c r="BA9" s="35"/>
-      <c r="BB9" s="35"/>
-      <c r="BC9" s="35"/>
-      <c r="BD9" s="35"/>
-      <c r="BE9" s="35"/>
-      <c r="BF9" s="35"/>
-      <c r="BG9" s="35"/>
-      <c r="BH9" s="35"/>
-      <c r="BI9" s="35"/>
+      <c r="AF9" s="43"/>
+      <c r="AG9" s="43"/>
+      <c r="AH9" s="43"/>
+      <c r="AI9" s="43"/>
+      <c r="AJ9" s="43"/>
+      <c r="AK9" s="43"/>
+      <c r="AL9" s="43"/>
+      <c r="AM9" s="43"/>
+      <c r="AN9" s="43"/>
+      <c r="AO9" s="43"/>
+      <c r="AP9" s="43"/>
+      <c r="AQ9" s="43"/>
+      <c r="AR9" s="43"/>
+      <c r="AS9" s="43"/>
+      <c r="AT9" s="43"/>
+      <c r="AU9" s="43"/>
+      <c r="AV9" s="43"/>
+      <c r="AW9" s="43"/>
+      <c r="AX9" s="43"/>
+      <c r="AY9" s="43"/>
+      <c r="AZ9" s="43"/>
+      <c r="BA9" s="43"/>
+      <c r="BB9" s="43"/>
+      <c r="BC9" s="43"/>
+      <c r="BD9" s="43"/>
+      <c r="BE9" s="43"/>
+      <c r="BF9" s="43"/>
+      <c r="BG9" s="43"/>
+      <c r="BH9" s="43"/>
+      <c r="BI9" s="43"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -4960,67 +4916,67 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
-      <c r="AA10" s="27"/>
-      <c r="AB10" s="27"/>
-      <c r="AC10" s="27"/>
-      <c r="AD10" s="27"/>
-      <c r="AE10" s="27"/>
-      <c r="AF10" s="27"/>
-      <c r="AG10" s="27"/>
-      <c r="AH10" s="27"/>
-      <c r="AI10" s="27"/>
-      <c r="AJ10" s="27"/>
-      <c r="AK10" s="27"/>
-      <c r="AL10" s="27"/>
-      <c r="AM10" s="27"/>
-      <c r="AN10" s="27"/>
-      <c r="AO10" s="27"/>
-      <c r="AP10" s="27"/>
-      <c r="AQ10" s="27"/>
-      <c r="AR10" s="27"/>
-      <c r="AS10" s="27"/>
-      <c r="AT10" s="27"/>
-      <c r="AU10" s="27"/>
-      <c r="AV10" s="27"/>
-      <c r="AW10" s="27"/>
-      <c r="AX10" s="27"/>
-      <c r="AY10" s="27"/>
-      <c r="AZ10" s="27"/>
-      <c r="BA10" s="27"/>
-      <c r="BB10" s="27"/>
-      <c r="BC10" s="27"/>
-      <c r="BD10" s="27"/>
-      <c r="BE10" s="27"/>
-      <c r="BF10" s="27"/>
-      <c r="BG10" s="27"/>
-      <c r="BH10" s="27"/>
-      <c r="BI10" s="27"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="31"/>
+      <c r="AE10" s="31"/>
+      <c r="AF10" s="31"/>
+      <c r="AG10" s="31"/>
+      <c r="AH10" s="31"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="31"/>
+      <c r="AK10" s="31"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="31"/>
+      <c r="AN10" s="31"/>
+      <c r="AO10" s="31"/>
+      <c r="AP10" s="31"/>
+      <c r="AQ10" s="31"/>
+      <c r="AR10" s="31"/>
+      <c r="AS10" s="31"/>
+      <c r="AT10" s="31"/>
+      <c r="AU10" s="31"/>
+      <c r="AV10" s="31"/>
+      <c r="AW10" s="31"/>
+      <c r="AX10" s="31"/>
+      <c r="AY10" s="31"/>
+      <c r="AZ10" s="31"/>
+      <c r="BA10" s="31"/>
+      <c r="BB10" s="31"/>
+      <c r="BC10" s="31"/>
+      <c r="BD10" s="31"/>
+      <c r="BE10" s="31"/>
+      <c r="BF10" s="31"/>
+      <c r="BG10" s="31"/>
+      <c r="BH10" s="31"/>
+      <c r="BI10" s="31"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -5480,73 +5436,73 @@
       <c r="IX11" s="1"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36" t="s">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36"/>
-      <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="36"/>
-      <c r="AB12" s="36"/>
-      <c r="AC12" s="36"/>
-      <c r="AD12" s="36"/>
-      <c r="AE12" s="36"/>
-      <c r="AF12" s="36"/>
-      <c r="AG12" s="36"/>
-      <c r="AH12" s="36"/>
-      <c r="AI12" s="36"/>
-      <c r="AJ12" s="36"/>
-      <c r="AK12" s="36"/>
-      <c r="AL12" s="36"/>
-      <c r="AM12" s="36"/>
-      <c r="AN12" s="36"/>
-      <c r="AO12" s="36"/>
-      <c r="AP12" s="36"/>
-      <c r="AQ12" s="36"/>
-      <c r="AR12" s="36"/>
-      <c r="AS12" s="36"/>
-      <c r="AT12" s="36" t="s">
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="41"/>
+      <c r="V12" s="41"/>
+      <c r="W12" s="41"/>
+      <c r="X12" s="41"/>
+      <c r="Y12" s="41"/>
+      <c r="Z12" s="41"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="41"/>
+      <c r="AC12" s="41"/>
+      <c r="AD12" s="41"/>
+      <c r="AE12" s="41"/>
+      <c r="AF12" s="41"/>
+      <c r="AG12" s="41"/>
+      <c r="AH12" s="41"/>
+      <c r="AI12" s="41"/>
+      <c r="AJ12" s="41"/>
+      <c r="AK12" s="41"/>
+      <c r="AL12" s="41"/>
+      <c r="AM12" s="41"/>
+      <c r="AN12" s="41"/>
+      <c r="AO12" s="41"/>
+      <c r="AP12" s="41"/>
+      <c r="AQ12" s="41"/>
+      <c r="AR12" s="41"/>
+      <c r="AS12" s="41"/>
+      <c r="AT12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="AU12" s="36"/>
-      <c r="AV12" s="36"/>
-      <c r="AW12" s="36"/>
-      <c r="AX12" s="36"/>
-      <c r="AY12" s="36"/>
-      <c r="AZ12" s="36"/>
-      <c r="BA12" s="36"/>
-      <c r="BB12" s="36"/>
-      <c r="BC12" s="36"/>
-      <c r="BD12" s="36"/>
-      <c r="BE12" s="36"/>
-      <c r="BF12" s="36"/>
-      <c r="BG12" s="36"/>
-      <c r="BH12" s="36"/>
-      <c r="BI12" s="36"/>
+      <c r="AU12" s="41"/>
+      <c r="AV12" s="41"/>
+      <c r="AW12" s="41"/>
+      <c r="AX12" s="41"/>
+      <c r="AY12" s="41"/>
+      <c r="AZ12" s="41"/>
+      <c r="BA12" s="41"/>
+      <c r="BB12" s="41"/>
+      <c r="BC12" s="41"/>
+      <c r="BD12" s="41"/>
+      <c r="BE12" s="41"/>
+      <c r="BF12" s="41"/>
+      <c r="BG12" s="41"/>
+      <c r="BH12" s="41"/>
+      <c r="BI12" s="41"/>
       <c r="BJ12" s="1"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
@@ -5762,7 +5718,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="7"/>
       <c r="P13" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="Q13" s="15"/>
       <c r="R13" s="15"/>
@@ -6008,7 +5964,7 @@
       <c r="IX13" s="1"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -6025,7 +5981,7 @@
       <c r="O14" s="11"/>
       <c r="P14" s="17"/>
       <c r="Q14" s="18" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="R14" s="18"/>
       <c r="S14" s="18"/>
@@ -6270,7 +6226,6 @@
       <c r="IX14" s="1"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -6284,10 +6239,10 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
       <c r="O15" s="11"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="20" t="s">
-        <v>42</v>
+      <c r="P15" s="17" t="s">
+        <v>45</v>
       </c>
+      <c r="Q15" s="20"/>
       <c r="R15" s="20"/>
       <c r="S15" s="20"/>
       <c r="T15" s="18"/>
@@ -6531,9 +6486,7 @@
       <c r="IX15" s="1"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>60</v>
-      </c>
+      <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -6547,10 +6500,10 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="11"/>
-      <c r="P16" s="17" t="s">
-        <v>59</v>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="20" t="s">
+        <v>46</v>
       </c>
-      <c r="Q16" s="20"/>
       <c r="R16" s="20"/>
       <c r="S16" s="20"/>
       <c r="T16" s="18"/>
@@ -7071,7 +7024,7 @@
       <c r="O18" s="11"/>
       <c r="P18" s="17"/>
       <c r="Q18" s="20" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="R18" s="20"/>
       <c r="S18" s="20"/>
@@ -7316,7 +7269,9 @@
       <c r="IX18" s="1"/>
     </row>
     <row r="19" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
+      <c r="A19" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="B19" s="9"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -7330,11 +7285,11 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
       <c r="O19" s="11"/>
-      <c r="P19" s="17"/>
+      <c r="P19" s="17" t="s">
+        <v>49</v>
+      </c>
       <c r="Q19" s="20"/>
-      <c r="R19" s="20" t="s">
-        <v>45</v>
-      </c>
+      <c r="R19" s="20"/>
       <c r="S19" s="20"/>
       <c r="T19" s="18"/>
       <c r="U19" s="18"/>
@@ -7592,11 +7547,11 @@
       <c r="N20" s="10"/>
       <c r="O20" s="11"/>
       <c r="P20" s="17"/>
-      <c r="Q20" s="20"/>
+      <c r="Q20" s="20" t="s">
+        <v>50</v>
+      </c>
       <c r="R20" s="20"/>
-      <c r="S20" s="20" t="s">
-        <v>46</v>
-      </c>
+      <c r="S20" s="20"/>
       <c r="T20" s="18"/>
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
@@ -7853,14 +7808,14 @@
       <c r="N21" s="10"/>
       <c r="O21" s="11"/>
       <c r="P21" s="17"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20" t="s">
-        <v>48</v>
+      <c r="Q21" s="18" t="s">
+        <v>51</v>
       </c>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
       <c r="T21" s="18"/>
       <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
+      <c r="V21" s="20"/>
       <c r="W21" s="18"/>
       <c r="X21" s="18"/>
       <c r="Y21" s="18"/>
@@ -8101,9 +8056,10 @@
     <row r="22" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
@@ -8113,15 +8069,15 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
       <c r="O22" s="11"/>
-      <c r="P22" s="17"/>
+      <c r="P22" s="17" t="s">
+        <v>52</v>
+      </c>
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
-      <c r="S22" s="18" t="s">
-        <v>52</v>
-      </c>
+      <c r="S22" s="18"/>
       <c r="T22" s="18"/>
       <c r="U22" s="18"/>
-      <c r="V22" s="20"/>
+      <c r="V22" s="18"/>
       <c r="W22" s="18"/>
       <c r="X22" s="18"/>
       <c r="Y22" s="18"/>
@@ -8146,7 +8102,7 @@
       <c r="AR22" s="18"/>
       <c r="AS22" s="19"/>
       <c r="AT22" s="8"/>
-      <c r="AU22" s="9"/>
+      <c r="AU22" s="10"/>
       <c r="AV22" s="10"/>
       <c r="AW22" s="10"/>
       <c r="AX22" s="10"/>
@@ -8363,9 +8319,9 @@
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
@@ -8375,15 +8331,15 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
       <c r="O23" s="11"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="18"/>
-      <c r="R23" s="18" t="s">
-        <v>49</v>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="22" t="s">
+        <v>55</v>
       </c>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
-      <c r="V23" s="18"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
       <c r="W23" s="18"/>
       <c r="X23" s="18"/>
       <c r="Y23" s="18"/>
@@ -8640,7 +8596,7 @@
       <c r="P24" s="21"/>
       <c r="Q24" s="22"/>
       <c r="R24" s="20" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="S24" s="20"/>
       <c r="T24" s="20"/>
@@ -8900,14 +8856,14 @@
       <c r="N25" s="10"/>
       <c r="O25" s="11"/>
       <c r="P25" s="21" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Q25" s="22"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="23"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
       <c r="W25" s="18"/>
       <c r="X25" s="18"/>
       <c r="Y25" s="18"/>
@@ -8931,7 +8887,9 @@
       <c r="AQ25" s="18"/>
       <c r="AR25" s="18"/>
       <c r="AS25" s="19"/>
-      <c r="AT25" s="8"/>
+      <c r="AT25" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="AU25" s="10"/>
       <c r="AV25" s="10"/>
       <c r="AW25" s="10"/>
@@ -9162,14 +9120,12 @@
       <c r="N26" s="10"/>
       <c r="O26" s="11"/>
       <c r="P26" s="21"/>
-      <c r="Q26" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="20"/>
-      <c r="V26" s="20"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="23"/>
+      <c r="V26" s="23"/>
       <c r="W26" s="18"/>
       <c r="X26" s="18"/>
       <c r="Y26" s="18"/>
@@ -9425,9 +9381,7 @@
       <c r="O27" s="11"/>
       <c r="P27" s="21"/>
       <c r="Q27" s="22"/>
-      <c r="R27" s="20" t="s">
-        <v>54</v>
-      </c>
+      <c r="R27" s="20"/>
       <c r="S27" s="20"/>
       <c r="T27" s="20"/>
       <c r="U27" s="23"/>
@@ -9670,69 +9624,67 @@
       <c r="IX27" s="1"/>
     </row>
     <row r="28" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="18"/>
-      <c r="X28" s="18"/>
-      <c r="Y28" s="18"/>
-      <c r="Z28" s="18"/>
-      <c r="AA28" s="18"/>
-      <c r="AB28" s="18"/>
-      <c r="AC28" s="18"/>
-      <c r="AD28" s="18"/>
-      <c r="AE28" s="18"/>
-      <c r="AF28" s="18"/>
-      <c r="AG28" s="18"/>
-      <c r="AH28" s="18"/>
-      <c r="AI28" s="18"/>
-      <c r="AJ28" s="18"/>
-      <c r="AK28" s="18"/>
-      <c r="AL28" s="18"/>
-      <c r="AM28" s="18"/>
-      <c r="AN28" s="18"/>
-      <c r="AO28" s="18"/>
-      <c r="AP28" s="18"/>
-      <c r="AQ28" s="18"/>
-      <c r="AR28" s="18"/>
-      <c r="AS28" s="19"/>
-      <c r="AT28" s="8"/>
-      <c r="AU28" s="10"/>
-      <c r="AV28" s="10"/>
-      <c r="AW28" s="10"/>
-      <c r="AX28" s="10"/>
-      <c r="AY28" s="10"/>
-      <c r="AZ28" s="10"/>
-      <c r="BA28" s="10"/>
-      <c r="BB28" s="10"/>
-      <c r="BC28" s="10"/>
-      <c r="BD28" s="10"/>
-      <c r="BE28" s="10"/>
-      <c r="BF28" s="10"/>
-      <c r="BG28" s="10"/>
-      <c r="BH28" s="10"/>
-      <c r="BI28" s="11"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="13"/>
+      <c r="AG28" s="13"/>
+      <c r="AH28" s="13"/>
+      <c r="AI28" s="13"/>
+      <c r="AJ28" s="13"/>
+      <c r="AK28" s="13"/>
+      <c r="AL28" s="13"/>
+      <c r="AM28" s="13"/>
+      <c r="AN28" s="13"/>
+      <c r="AO28" s="13"/>
+      <c r="AP28" s="13"/>
+      <c r="AQ28" s="13"/>
+      <c r="AR28" s="13"/>
+      <c r="AS28" s="13"/>
+      <c r="AT28" s="13"/>
+      <c r="AU28" s="13"/>
+      <c r="AV28" s="13"/>
+      <c r="AW28" s="13"/>
+      <c r="AX28" s="13"/>
+      <c r="AY28" s="13"/>
+      <c r="AZ28" s="13"/>
+      <c r="BA28" s="13"/>
+      <c r="BB28" s="13"/>
+      <c r="BC28" s="13"/>
+      <c r="BD28" s="13"/>
+      <c r="BE28" s="13"/>
+      <c r="BF28" s="13"/>
+      <c r="BG28" s="13"/>
+      <c r="BH28" s="13"/>
+      <c r="BI28" s="13"/>
       <c r="BJ28" s="1"/>
       <c r="BK28" s="1"/>
       <c r="BL28" s="1"/>
@@ -9931,3395 +9883,27 @@
       <c r="IW28" s="1"/>
       <c r="IX28" s="1"/>
     </row>
-    <row r="29" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="22"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="T29" s="18"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="18"/>
-      <c r="X29" s="18"/>
-      <c r="Y29" s="18"/>
-      <c r="Z29" s="18"/>
-      <c r="AA29" s="18"/>
-      <c r="AB29" s="18"/>
-      <c r="AC29" s="18"/>
-      <c r="AD29" s="18"/>
-      <c r="AE29" s="18"/>
-      <c r="AF29" s="18"/>
-      <c r="AG29" s="18"/>
-      <c r="AH29" s="18"/>
-      <c r="AI29" s="18"/>
-      <c r="AJ29" s="18"/>
-      <c r="AK29" s="18"/>
-      <c r="AL29" s="18"/>
-      <c r="AM29" s="18"/>
-      <c r="AN29" s="18"/>
-      <c r="AO29" s="18"/>
-      <c r="AP29" s="18"/>
-      <c r="AQ29" s="18"/>
-      <c r="AR29" s="18"/>
-      <c r="AS29" s="19"/>
-      <c r="AT29" s="8"/>
-      <c r="AU29" s="10"/>
-      <c r="AV29" s="10"/>
-      <c r="AW29" s="10"/>
-      <c r="AX29" s="10"/>
-      <c r="AY29" s="10"/>
-      <c r="AZ29" s="10"/>
-      <c r="BA29" s="10"/>
-      <c r="BB29" s="10"/>
-      <c r="BC29" s="10"/>
-      <c r="BD29" s="10"/>
-      <c r="BE29" s="10"/>
-      <c r="BF29" s="10"/>
-      <c r="BG29" s="10"/>
-      <c r="BH29" s="10"/>
-      <c r="BI29" s="11"/>
-      <c r="BJ29" s="1"/>
-      <c r="BK29" s="1"/>
-      <c r="BL29" s="1"/>
-      <c r="BM29" s="1"/>
-      <c r="BN29" s="1"/>
-      <c r="BO29" s="1"/>
-      <c r="BP29" s="1"/>
-      <c r="BQ29" s="1"/>
-      <c r="BR29" s="1"/>
-      <c r="BS29" s="1"/>
-      <c r="BT29" s="1"/>
-      <c r="BU29" s="1"/>
-      <c r="BV29" s="1"/>
-      <c r="BW29" s="1"/>
-      <c r="BX29" s="1"/>
-      <c r="BY29" s="1"/>
-      <c r="BZ29" s="1"/>
-      <c r="CA29" s="1"/>
-      <c r="CB29" s="1"/>
-      <c r="CC29" s="1"/>
-      <c r="CD29" s="1"/>
-      <c r="CE29" s="1"/>
-      <c r="CF29" s="1"/>
-      <c r="CG29" s="1"/>
-      <c r="CH29" s="1"/>
-      <c r="CI29" s="1"/>
-      <c r="CJ29" s="1"/>
-      <c r="CK29" s="1"/>
-      <c r="CL29" s="1"/>
-      <c r="CM29" s="1"/>
-      <c r="CN29" s="1"/>
-      <c r="CO29" s="1"/>
-      <c r="CP29" s="1"/>
-      <c r="CQ29" s="1"/>
-      <c r="CR29" s="1"/>
-      <c r="CS29" s="1"/>
-      <c r="CT29" s="1"/>
-      <c r="CU29" s="1"/>
-      <c r="CV29" s="1"/>
-      <c r="CW29" s="1"/>
-      <c r="CX29" s="1"/>
-      <c r="CY29" s="1"/>
-      <c r="CZ29" s="1"/>
-      <c r="DA29" s="1"/>
-      <c r="DB29" s="1"/>
-      <c r="DC29" s="1"/>
-      <c r="DD29" s="1"/>
-      <c r="DE29" s="1"/>
-      <c r="DF29" s="1"/>
-      <c r="DG29" s="1"/>
-      <c r="DH29" s="1"/>
-      <c r="DI29" s="1"/>
-      <c r="DJ29" s="1"/>
-      <c r="DK29" s="1"/>
-      <c r="DL29" s="1"/>
-      <c r="DM29" s="1"/>
-      <c r="DN29" s="1"/>
-      <c r="DO29" s="1"/>
-      <c r="DP29" s="1"/>
-      <c r="DQ29" s="1"/>
-      <c r="DR29" s="1"/>
-      <c r="DS29" s="1"/>
-      <c r="DT29" s="1"/>
-      <c r="DU29" s="1"/>
-      <c r="DV29" s="1"/>
-      <c r="DW29" s="1"/>
-      <c r="DX29" s="1"/>
-      <c r="DY29" s="1"/>
-      <c r="DZ29" s="1"/>
-      <c r="EA29" s="1"/>
-      <c r="EB29" s="1"/>
-      <c r="EC29" s="1"/>
-      <c r="ED29" s="1"/>
-      <c r="EE29" s="1"/>
-      <c r="EF29" s="1"/>
-      <c r="EG29" s="1"/>
-      <c r="EH29" s="1"/>
-      <c r="EI29" s="1"/>
-      <c r="EJ29" s="1"/>
-      <c r="EK29" s="1"/>
-      <c r="EL29" s="1"/>
-      <c r="EM29" s="1"/>
-      <c r="EN29" s="1"/>
-      <c r="EO29" s="1"/>
-      <c r="EP29" s="1"/>
-      <c r="EQ29" s="1"/>
-      <c r="ER29" s="1"/>
-      <c r="ES29" s="1"/>
-      <c r="ET29" s="1"/>
-      <c r="EU29" s="1"/>
-      <c r="EV29" s="1"/>
-      <c r="EW29" s="1"/>
-      <c r="EX29" s="1"/>
-      <c r="EY29" s="1"/>
-      <c r="EZ29" s="1"/>
-      <c r="FA29" s="1"/>
-      <c r="FB29" s="1"/>
-      <c r="FC29" s="1"/>
-      <c r="FD29" s="1"/>
-      <c r="FE29" s="1"/>
-      <c r="FF29" s="1"/>
-      <c r="FG29" s="1"/>
-      <c r="FH29" s="1"/>
-      <c r="FI29" s="1"/>
-      <c r="FJ29" s="1"/>
-      <c r="FK29" s="1"/>
-      <c r="FL29" s="1"/>
-      <c r="FM29" s="1"/>
-      <c r="FN29" s="1"/>
-      <c r="FO29" s="1"/>
-      <c r="FP29" s="1"/>
-      <c r="FQ29" s="1"/>
-      <c r="FR29" s="1"/>
-      <c r="FS29" s="1"/>
-      <c r="FT29" s="1"/>
-      <c r="FU29" s="1"/>
-      <c r="FV29" s="1"/>
-      <c r="FW29" s="1"/>
-      <c r="FX29" s="1"/>
-      <c r="FY29" s="1"/>
-      <c r="FZ29" s="1"/>
-      <c r="GA29" s="1"/>
-      <c r="GB29" s="1"/>
-      <c r="GC29" s="1"/>
-      <c r="GD29" s="1"/>
-      <c r="GE29" s="1"/>
-      <c r="GF29" s="1"/>
-      <c r="GG29" s="1"/>
-      <c r="GH29" s="1"/>
-      <c r="GI29" s="1"/>
-      <c r="GJ29" s="1"/>
-      <c r="GK29" s="1"/>
-      <c r="GL29" s="1"/>
-      <c r="GM29" s="1"/>
-      <c r="GN29" s="1"/>
-      <c r="GO29" s="1"/>
-      <c r="GP29" s="1"/>
-      <c r="GQ29" s="1"/>
-      <c r="GR29" s="1"/>
-      <c r="GS29" s="1"/>
-      <c r="GT29" s="1"/>
-      <c r="GU29" s="1"/>
-      <c r="GV29" s="1"/>
-      <c r="GW29" s="1"/>
-      <c r="GX29" s="1"/>
-      <c r="GY29" s="1"/>
-      <c r="GZ29" s="1"/>
-      <c r="HA29" s="1"/>
-      <c r="HB29" s="1"/>
-      <c r="HC29" s="1"/>
-      <c r="HD29" s="1"/>
-      <c r="HE29" s="1"/>
-      <c r="HF29" s="1"/>
-      <c r="HG29" s="1"/>
-      <c r="HH29" s="1"/>
-      <c r="HI29" s="1"/>
-      <c r="HJ29" s="1"/>
-      <c r="HK29" s="1"/>
-      <c r="HL29" s="1"/>
-      <c r="HM29" s="1"/>
-      <c r="HN29" s="1"/>
-      <c r="HO29" s="1"/>
-      <c r="HP29" s="1"/>
-      <c r="HQ29" s="1"/>
-      <c r="HR29" s="1"/>
-      <c r="HS29" s="1"/>
-      <c r="HT29" s="1"/>
-      <c r="HU29" s="1"/>
-      <c r="HV29" s="1"/>
-      <c r="HW29" s="1"/>
-      <c r="HX29" s="1"/>
-      <c r="HY29" s="1"/>
-      <c r="HZ29" s="1"/>
-      <c r="IA29" s="1"/>
-      <c r="IB29" s="1"/>
-      <c r="IC29" s="1"/>
-      <c r="ID29" s="1"/>
-      <c r="IE29" s="1"/>
-      <c r="IF29" s="1"/>
-      <c r="IG29" s="1"/>
-      <c r="IH29" s="1"/>
-      <c r="II29" s="1"/>
-      <c r="IJ29" s="1"/>
-      <c r="IK29" s="1"/>
-      <c r="IL29" s="1"/>
-      <c r="IM29" s="1"/>
-      <c r="IN29" s="1"/>
-      <c r="IO29" s="1"/>
-      <c r="IP29" s="1"/>
-      <c r="IQ29" s="1"/>
-      <c r="IR29" s="1"/>
-      <c r="IS29" s="1"/>
-      <c r="IT29" s="1"/>
-      <c r="IU29" s="1"/>
-      <c r="IV29" s="1"/>
-      <c r="IW29" s="1"/>
-      <c r="IX29" s="1"/>
-    </row>
-    <row r="30" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="22"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="T30" s="18"/>
-      <c r="U30" s="20"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="18"/>
-      <c r="AD30" s="18"/>
-      <c r="AE30" s="18"/>
-      <c r="AF30" s="18"/>
-      <c r="AG30" s="18"/>
-      <c r="AH30" s="18"/>
-      <c r="AI30" s="18"/>
-      <c r="AJ30" s="18"/>
-      <c r="AK30" s="18"/>
-      <c r="AL30" s="18"/>
-      <c r="AM30" s="18"/>
-      <c r="AN30" s="18"/>
-      <c r="AO30" s="18"/>
-      <c r="AP30" s="18"/>
-      <c r="AQ30" s="18"/>
-      <c r="AR30" s="18"/>
-      <c r="AS30" s="19"/>
-      <c r="AT30" s="8"/>
-      <c r="AU30" s="10"/>
-      <c r="AV30" s="10"/>
-      <c r="AW30" s="10"/>
-      <c r="AX30" s="10"/>
-      <c r="AY30" s="10"/>
-      <c r="AZ30" s="10"/>
-      <c r="BA30" s="10"/>
-      <c r="BB30" s="10"/>
-      <c r="BC30" s="10"/>
-      <c r="BD30" s="10"/>
-      <c r="BE30" s="10"/>
-      <c r="BF30" s="10"/>
-      <c r="BG30" s="10"/>
-      <c r="BH30" s="10"/>
-      <c r="BI30" s="11"/>
-      <c r="BJ30" s="1"/>
-      <c r="BK30" s="1"/>
-      <c r="BL30" s="1"/>
-      <c r="BM30" s="1"/>
-      <c r="BN30" s="1"/>
-      <c r="BO30" s="1"/>
-      <c r="BP30" s="1"/>
-      <c r="BQ30" s="1"/>
-      <c r="BR30" s="1"/>
-      <c r="BS30" s="1"/>
-      <c r="BT30" s="1"/>
-      <c r="BU30" s="1"/>
-      <c r="BV30" s="1"/>
-      <c r="BW30" s="1"/>
-      <c r="BX30" s="1"/>
-      <c r="BY30" s="1"/>
-      <c r="BZ30" s="1"/>
-      <c r="CA30" s="1"/>
-      <c r="CB30" s="1"/>
-      <c r="CC30" s="1"/>
-      <c r="CD30" s="1"/>
-      <c r="CE30" s="1"/>
-      <c r="CF30" s="1"/>
-      <c r="CG30" s="1"/>
-      <c r="CH30" s="1"/>
-      <c r="CI30" s="1"/>
-      <c r="CJ30" s="1"/>
-      <c r="CK30" s="1"/>
-      <c r="CL30" s="1"/>
-      <c r="CM30" s="1"/>
-      <c r="CN30" s="1"/>
-      <c r="CO30" s="1"/>
-      <c r="CP30" s="1"/>
-      <c r="CQ30" s="1"/>
-      <c r="CR30" s="1"/>
-      <c r="CS30" s="1"/>
-      <c r="CT30" s="1"/>
-      <c r="CU30" s="1"/>
-      <c r="CV30" s="1"/>
-      <c r="CW30" s="1"/>
-      <c r="CX30" s="1"/>
-      <c r="CY30" s="1"/>
-      <c r="CZ30" s="1"/>
-      <c r="DA30" s="1"/>
-      <c r="DB30" s="1"/>
-      <c r="DC30" s="1"/>
-      <c r="DD30" s="1"/>
-      <c r="DE30" s="1"/>
-      <c r="DF30" s="1"/>
-      <c r="DG30" s="1"/>
-      <c r="DH30" s="1"/>
-      <c r="DI30" s="1"/>
-      <c r="DJ30" s="1"/>
-      <c r="DK30" s="1"/>
-      <c r="DL30" s="1"/>
-      <c r="DM30" s="1"/>
-      <c r="DN30" s="1"/>
-      <c r="DO30" s="1"/>
-      <c r="DP30" s="1"/>
-      <c r="DQ30" s="1"/>
-      <c r="DR30" s="1"/>
-      <c r="DS30" s="1"/>
-      <c r="DT30" s="1"/>
-      <c r="DU30" s="1"/>
-      <c r="DV30" s="1"/>
-      <c r="DW30" s="1"/>
-      <c r="DX30" s="1"/>
-      <c r="DY30" s="1"/>
-      <c r="DZ30" s="1"/>
-      <c r="EA30" s="1"/>
-      <c r="EB30" s="1"/>
-      <c r="EC30" s="1"/>
-      <c r="ED30" s="1"/>
-      <c r="EE30" s="1"/>
-      <c r="EF30" s="1"/>
-      <c r="EG30" s="1"/>
-      <c r="EH30" s="1"/>
-      <c r="EI30" s="1"/>
-      <c r="EJ30" s="1"/>
-      <c r="EK30" s="1"/>
-      <c r="EL30" s="1"/>
-      <c r="EM30" s="1"/>
-      <c r="EN30" s="1"/>
-      <c r="EO30" s="1"/>
-      <c r="EP30" s="1"/>
-      <c r="EQ30" s="1"/>
-      <c r="ER30" s="1"/>
-      <c r="ES30" s="1"/>
-      <c r="ET30" s="1"/>
-      <c r="EU30" s="1"/>
-      <c r="EV30" s="1"/>
-      <c r="EW30" s="1"/>
-      <c r="EX30" s="1"/>
-      <c r="EY30" s="1"/>
-      <c r="EZ30" s="1"/>
-      <c r="FA30" s="1"/>
-      <c r="FB30" s="1"/>
-      <c r="FC30" s="1"/>
-      <c r="FD30" s="1"/>
-      <c r="FE30" s="1"/>
-      <c r="FF30" s="1"/>
-      <c r="FG30" s="1"/>
-      <c r="FH30" s="1"/>
-      <c r="FI30" s="1"/>
-      <c r="FJ30" s="1"/>
-      <c r="FK30" s="1"/>
-      <c r="FL30" s="1"/>
-      <c r="FM30" s="1"/>
-      <c r="FN30" s="1"/>
-      <c r="FO30" s="1"/>
-      <c r="FP30" s="1"/>
-      <c r="FQ30" s="1"/>
-      <c r="FR30" s="1"/>
-      <c r="FS30" s="1"/>
-      <c r="FT30" s="1"/>
-      <c r="FU30" s="1"/>
-      <c r="FV30" s="1"/>
-      <c r="FW30" s="1"/>
-      <c r="FX30" s="1"/>
-      <c r="FY30" s="1"/>
-      <c r="FZ30" s="1"/>
-      <c r="GA30" s="1"/>
-      <c r="GB30" s="1"/>
-      <c r="GC30" s="1"/>
-      <c r="GD30" s="1"/>
-      <c r="GE30" s="1"/>
-      <c r="GF30" s="1"/>
-      <c r="GG30" s="1"/>
-      <c r="GH30" s="1"/>
-      <c r="GI30" s="1"/>
-      <c r="GJ30" s="1"/>
-      <c r="GK30" s="1"/>
-      <c r="GL30" s="1"/>
-      <c r="GM30" s="1"/>
-      <c r="GN30" s="1"/>
-      <c r="GO30" s="1"/>
-      <c r="GP30" s="1"/>
-      <c r="GQ30" s="1"/>
-      <c r="GR30" s="1"/>
-      <c r="GS30" s="1"/>
-      <c r="GT30" s="1"/>
-      <c r="GU30" s="1"/>
-      <c r="GV30" s="1"/>
-      <c r="GW30" s="1"/>
-      <c r="GX30" s="1"/>
-      <c r="GY30" s="1"/>
-      <c r="GZ30" s="1"/>
-      <c r="HA30" s="1"/>
-      <c r="HB30" s="1"/>
-      <c r="HC30" s="1"/>
-      <c r="HD30" s="1"/>
-      <c r="HE30" s="1"/>
-      <c r="HF30" s="1"/>
-      <c r="HG30" s="1"/>
-      <c r="HH30" s="1"/>
-      <c r="HI30" s="1"/>
-      <c r="HJ30" s="1"/>
-      <c r="HK30" s="1"/>
-      <c r="HL30" s="1"/>
-      <c r="HM30" s="1"/>
-      <c r="HN30" s="1"/>
-      <c r="HO30" s="1"/>
-      <c r="HP30" s="1"/>
-      <c r="HQ30" s="1"/>
-      <c r="HR30" s="1"/>
-      <c r="HS30" s="1"/>
-      <c r="HT30" s="1"/>
-      <c r="HU30" s="1"/>
-      <c r="HV30" s="1"/>
-      <c r="HW30" s="1"/>
-      <c r="HX30" s="1"/>
-      <c r="HY30" s="1"/>
-      <c r="HZ30" s="1"/>
-      <c r="IA30" s="1"/>
-      <c r="IB30" s="1"/>
-      <c r="IC30" s="1"/>
-      <c r="ID30" s="1"/>
-      <c r="IE30" s="1"/>
-      <c r="IF30" s="1"/>
-      <c r="IG30" s="1"/>
-      <c r="IH30" s="1"/>
-      <c r="II30" s="1"/>
-      <c r="IJ30" s="1"/>
-      <c r="IK30" s="1"/>
-      <c r="IL30" s="1"/>
-      <c r="IM30" s="1"/>
-      <c r="IN30" s="1"/>
-      <c r="IO30" s="1"/>
-      <c r="IP30" s="1"/>
-      <c r="IQ30" s="1"/>
-      <c r="IR30" s="1"/>
-      <c r="IS30" s="1"/>
-      <c r="IT30" s="1"/>
-      <c r="IU30" s="1"/>
-      <c r="IV30" s="1"/>
-      <c r="IW30" s="1"/>
-      <c r="IX30" s="1"/>
-    </row>
-    <row r="31" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q31" s="22"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="18"/>
-      <c r="AA31" s="18"/>
-      <c r="AB31" s="18"/>
-      <c r="AC31" s="18"/>
-      <c r="AD31" s="18"/>
-      <c r="AE31" s="18"/>
-      <c r="AF31" s="18"/>
-      <c r="AG31" s="18"/>
-      <c r="AH31" s="18"/>
-      <c r="AI31" s="18"/>
-      <c r="AJ31" s="18"/>
-      <c r="AK31" s="18"/>
-      <c r="AL31" s="18"/>
-      <c r="AM31" s="18"/>
-      <c r="AN31" s="18"/>
-      <c r="AO31" s="18"/>
-      <c r="AP31" s="18"/>
-      <c r="AQ31" s="18"/>
-      <c r="AR31" s="18"/>
-      <c r="AS31" s="19"/>
-      <c r="AT31" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AU31" s="10"/>
-      <c r="AV31" s="10"/>
-      <c r="AW31" s="10"/>
-      <c r="AX31" s="10"/>
-      <c r="AY31" s="10"/>
-      <c r="AZ31" s="10"/>
-      <c r="BA31" s="10"/>
-      <c r="BB31" s="10"/>
-      <c r="BC31" s="10"/>
-      <c r="BD31" s="10"/>
-      <c r="BE31" s="10"/>
-      <c r="BF31" s="10"/>
-      <c r="BG31" s="10"/>
-      <c r="BH31" s="10"/>
-      <c r="BI31" s="11"/>
-      <c r="BJ31" s="1"/>
-      <c r="BK31" s="1"/>
-      <c r="BL31" s="1"/>
-      <c r="BM31" s="1"/>
-      <c r="BN31" s="1"/>
-      <c r="BO31" s="1"/>
-      <c r="BP31" s="1"/>
-      <c r="BQ31" s="1"/>
-      <c r="BR31" s="1"/>
-      <c r="BS31" s="1"/>
-      <c r="BT31" s="1"/>
-      <c r="BU31" s="1"/>
-      <c r="BV31" s="1"/>
-      <c r="BW31" s="1"/>
-      <c r="BX31" s="1"/>
-      <c r="BY31" s="1"/>
-      <c r="BZ31" s="1"/>
-      <c r="CA31" s="1"/>
-      <c r="CB31" s="1"/>
-      <c r="CC31" s="1"/>
-      <c r="CD31" s="1"/>
-      <c r="CE31" s="1"/>
-      <c r="CF31" s="1"/>
-      <c r="CG31" s="1"/>
-      <c r="CH31" s="1"/>
-      <c r="CI31" s="1"/>
-      <c r="CJ31" s="1"/>
-      <c r="CK31" s="1"/>
-      <c r="CL31" s="1"/>
-      <c r="CM31" s="1"/>
-      <c r="CN31" s="1"/>
-      <c r="CO31" s="1"/>
-      <c r="CP31" s="1"/>
-      <c r="CQ31" s="1"/>
-      <c r="CR31" s="1"/>
-      <c r="CS31" s="1"/>
-      <c r="CT31" s="1"/>
-      <c r="CU31" s="1"/>
-      <c r="CV31" s="1"/>
-      <c r="CW31" s="1"/>
-      <c r="CX31" s="1"/>
-      <c r="CY31" s="1"/>
-      <c r="CZ31" s="1"/>
-      <c r="DA31" s="1"/>
-      <c r="DB31" s="1"/>
-      <c r="DC31" s="1"/>
-      <c r="DD31" s="1"/>
-      <c r="DE31" s="1"/>
-      <c r="DF31" s="1"/>
-      <c r="DG31" s="1"/>
-      <c r="DH31" s="1"/>
-      <c r="DI31" s="1"/>
-      <c r="DJ31" s="1"/>
-      <c r="DK31" s="1"/>
-      <c r="DL31" s="1"/>
-      <c r="DM31" s="1"/>
-      <c r="DN31" s="1"/>
-      <c r="DO31" s="1"/>
-      <c r="DP31" s="1"/>
-      <c r="DQ31" s="1"/>
-      <c r="DR31" s="1"/>
-      <c r="DS31" s="1"/>
-      <c r="DT31" s="1"/>
-      <c r="DU31" s="1"/>
-      <c r="DV31" s="1"/>
-      <c r="DW31" s="1"/>
-      <c r="DX31" s="1"/>
-      <c r="DY31" s="1"/>
-      <c r="DZ31" s="1"/>
-      <c r="EA31" s="1"/>
-      <c r="EB31" s="1"/>
-      <c r="EC31" s="1"/>
-      <c r="ED31" s="1"/>
-      <c r="EE31" s="1"/>
-      <c r="EF31" s="1"/>
-      <c r="EG31" s="1"/>
-      <c r="EH31" s="1"/>
-      <c r="EI31" s="1"/>
-      <c r="EJ31" s="1"/>
-      <c r="EK31" s="1"/>
-      <c r="EL31" s="1"/>
-      <c r="EM31" s="1"/>
-      <c r="EN31" s="1"/>
-      <c r="EO31" s="1"/>
-      <c r="EP31" s="1"/>
-      <c r="EQ31" s="1"/>
-      <c r="ER31" s="1"/>
-      <c r="ES31" s="1"/>
-      <c r="ET31" s="1"/>
-      <c r="EU31" s="1"/>
-      <c r="EV31" s="1"/>
-      <c r="EW31" s="1"/>
-      <c r="EX31" s="1"/>
-      <c r="EY31" s="1"/>
-      <c r="EZ31" s="1"/>
-      <c r="FA31" s="1"/>
-      <c r="FB31" s="1"/>
-      <c r="FC31" s="1"/>
-      <c r="FD31" s="1"/>
-      <c r="FE31" s="1"/>
-      <c r="FF31" s="1"/>
-      <c r="FG31" s="1"/>
-      <c r="FH31" s="1"/>
-      <c r="FI31" s="1"/>
-      <c r="FJ31" s="1"/>
-      <c r="FK31" s="1"/>
-      <c r="FL31" s="1"/>
-      <c r="FM31" s="1"/>
-      <c r="FN31" s="1"/>
-      <c r="FO31" s="1"/>
-      <c r="FP31" s="1"/>
-      <c r="FQ31" s="1"/>
-      <c r="FR31" s="1"/>
-      <c r="FS31" s="1"/>
-      <c r="FT31" s="1"/>
-      <c r="FU31" s="1"/>
-      <c r="FV31" s="1"/>
-      <c r="FW31" s="1"/>
-      <c r="FX31" s="1"/>
-      <c r="FY31" s="1"/>
-      <c r="FZ31" s="1"/>
-      <c r="GA31" s="1"/>
-      <c r="GB31" s="1"/>
-      <c r="GC31" s="1"/>
-      <c r="GD31" s="1"/>
-      <c r="GE31" s="1"/>
-      <c r="GF31" s="1"/>
-      <c r="GG31" s="1"/>
-      <c r="GH31" s="1"/>
-      <c r="GI31" s="1"/>
-      <c r="GJ31" s="1"/>
-      <c r="GK31" s="1"/>
-      <c r="GL31" s="1"/>
-      <c r="GM31" s="1"/>
-      <c r="GN31" s="1"/>
-      <c r="GO31" s="1"/>
-      <c r="GP31" s="1"/>
-      <c r="GQ31" s="1"/>
-      <c r="GR31" s="1"/>
-      <c r="GS31" s="1"/>
-      <c r="GT31" s="1"/>
-      <c r="GU31" s="1"/>
-      <c r="GV31" s="1"/>
-      <c r="GW31" s="1"/>
-      <c r="GX31" s="1"/>
-      <c r="GY31" s="1"/>
-      <c r="GZ31" s="1"/>
-      <c r="HA31" s="1"/>
-      <c r="HB31" s="1"/>
-      <c r="HC31" s="1"/>
-      <c r="HD31" s="1"/>
-      <c r="HE31" s="1"/>
-      <c r="HF31" s="1"/>
-      <c r="HG31" s="1"/>
-      <c r="HH31" s="1"/>
-      <c r="HI31" s="1"/>
-      <c r="HJ31" s="1"/>
-      <c r="HK31" s="1"/>
-      <c r="HL31" s="1"/>
-      <c r="HM31" s="1"/>
-      <c r="HN31" s="1"/>
-      <c r="HO31" s="1"/>
-      <c r="HP31" s="1"/>
-      <c r="HQ31" s="1"/>
-      <c r="HR31" s="1"/>
-      <c r="HS31" s="1"/>
-      <c r="HT31" s="1"/>
-      <c r="HU31" s="1"/>
-      <c r="HV31" s="1"/>
-      <c r="HW31" s="1"/>
-      <c r="HX31" s="1"/>
-      <c r="HY31" s="1"/>
-      <c r="HZ31" s="1"/>
-      <c r="IA31" s="1"/>
-      <c r="IB31" s="1"/>
-      <c r="IC31" s="1"/>
-      <c r="ID31" s="1"/>
-      <c r="IE31" s="1"/>
-      <c r="IF31" s="1"/>
-      <c r="IG31" s="1"/>
-      <c r="IH31" s="1"/>
-      <c r="II31" s="1"/>
-      <c r="IJ31" s="1"/>
-      <c r="IK31" s="1"/>
-      <c r="IL31" s="1"/>
-      <c r="IM31" s="1"/>
-      <c r="IN31" s="1"/>
-      <c r="IO31" s="1"/>
-      <c r="IP31" s="1"/>
-      <c r="IQ31" s="1"/>
-      <c r="IR31" s="1"/>
-      <c r="IS31" s="1"/>
-      <c r="IT31" s="1"/>
-      <c r="IU31" s="1"/>
-      <c r="IV31" s="1"/>
-      <c r="IW31" s="1"/>
-      <c r="IX31" s="1"/>
-    </row>
-    <row r="32" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="20"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="18"/>
-      <c r="AA32" s="18"/>
-      <c r="AB32" s="18"/>
-      <c r="AC32" s="18"/>
-      <c r="AD32" s="18"/>
-      <c r="AE32" s="18"/>
-      <c r="AF32" s="18"/>
-      <c r="AG32" s="18"/>
-      <c r="AH32" s="18"/>
-      <c r="AI32" s="18"/>
-      <c r="AJ32" s="18"/>
-      <c r="AK32" s="18"/>
-      <c r="AL32" s="18"/>
-      <c r="AM32" s="18"/>
-      <c r="AN32" s="18"/>
-      <c r="AO32" s="18"/>
-      <c r="AP32" s="18"/>
-      <c r="AQ32" s="18"/>
-      <c r="AR32" s="18"/>
-      <c r="AS32" s="19"/>
-      <c r="AT32" s="8"/>
-      <c r="AU32" s="10"/>
-      <c r="AV32" s="10"/>
-      <c r="AW32" s="10"/>
-      <c r="AX32" s="10"/>
-      <c r="AY32" s="10"/>
-      <c r="AZ32" s="10"/>
-      <c r="BA32" s="10"/>
-      <c r="BB32" s="10"/>
-      <c r="BC32" s="10"/>
-      <c r="BD32" s="10"/>
-      <c r="BE32" s="10"/>
-      <c r="BF32" s="10"/>
-      <c r="BG32" s="10"/>
-      <c r="BH32" s="10"/>
-      <c r="BI32" s="11"/>
-      <c r="BJ32" s="1"/>
-      <c r="BK32" s="1"/>
-      <c r="BL32" s="1"/>
-      <c r="BM32" s="1"/>
-      <c r="BN32" s="1"/>
-      <c r="BO32" s="1"/>
-      <c r="BP32" s="1"/>
-      <c r="BQ32" s="1"/>
-      <c r="BR32" s="1"/>
-      <c r="BS32" s="1"/>
-      <c r="BT32" s="1"/>
-      <c r="BU32" s="1"/>
-      <c r="BV32" s="1"/>
-      <c r="BW32" s="1"/>
-      <c r="BX32" s="1"/>
-      <c r="BY32" s="1"/>
-      <c r="BZ32" s="1"/>
-      <c r="CA32" s="1"/>
-      <c r="CB32" s="1"/>
-      <c r="CC32" s="1"/>
-      <c r="CD32" s="1"/>
-      <c r="CE32" s="1"/>
-      <c r="CF32" s="1"/>
-      <c r="CG32" s="1"/>
-      <c r="CH32" s="1"/>
-      <c r="CI32" s="1"/>
-      <c r="CJ32" s="1"/>
-      <c r="CK32" s="1"/>
-      <c r="CL32" s="1"/>
-      <c r="CM32" s="1"/>
-      <c r="CN32" s="1"/>
-      <c r="CO32" s="1"/>
-      <c r="CP32" s="1"/>
-      <c r="CQ32" s="1"/>
-      <c r="CR32" s="1"/>
-      <c r="CS32" s="1"/>
-      <c r="CT32" s="1"/>
-      <c r="CU32" s="1"/>
-      <c r="CV32" s="1"/>
-      <c r="CW32" s="1"/>
-      <c r="CX32" s="1"/>
-      <c r="CY32" s="1"/>
-      <c r="CZ32" s="1"/>
-      <c r="DA32" s="1"/>
-      <c r="DB32" s="1"/>
-      <c r="DC32" s="1"/>
-      <c r="DD32" s="1"/>
-      <c r="DE32" s="1"/>
-      <c r="DF32" s="1"/>
-      <c r="DG32" s="1"/>
-      <c r="DH32" s="1"/>
-      <c r="DI32" s="1"/>
-      <c r="DJ32" s="1"/>
-      <c r="DK32" s="1"/>
-      <c r="DL32" s="1"/>
-      <c r="DM32" s="1"/>
-      <c r="DN32" s="1"/>
-      <c r="DO32" s="1"/>
-      <c r="DP32" s="1"/>
-      <c r="DQ32" s="1"/>
-      <c r="DR32" s="1"/>
-      <c r="DS32" s="1"/>
-      <c r="DT32" s="1"/>
-      <c r="DU32" s="1"/>
-      <c r="DV32" s="1"/>
-      <c r="DW32" s="1"/>
-      <c r="DX32" s="1"/>
-      <c r="DY32" s="1"/>
-      <c r="DZ32" s="1"/>
-      <c r="EA32" s="1"/>
-      <c r="EB32" s="1"/>
-      <c r="EC32" s="1"/>
-      <c r="ED32" s="1"/>
-      <c r="EE32" s="1"/>
-      <c r="EF32" s="1"/>
-      <c r="EG32" s="1"/>
-      <c r="EH32" s="1"/>
-      <c r="EI32" s="1"/>
-      <c r="EJ32" s="1"/>
-      <c r="EK32" s="1"/>
-      <c r="EL32" s="1"/>
-      <c r="EM32" s="1"/>
-      <c r="EN32" s="1"/>
-      <c r="EO32" s="1"/>
-      <c r="EP32" s="1"/>
-      <c r="EQ32" s="1"/>
-      <c r="ER32" s="1"/>
-      <c r="ES32" s="1"/>
-      <c r="ET32" s="1"/>
-      <c r="EU32" s="1"/>
-      <c r="EV32" s="1"/>
-      <c r="EW32" s="1"/>
-      <c r="EX32" s="1"/>
-      <c r="EY32" s="1"/>
-      <c r="EZ32" s="1"/>
-      <c r="FA32" s="1"/>
-      <c r="FB32" s="1"/>
-      <c r="FC32" s="1"/>
-      <c r="FD32" s="1"/>
-      <c r="FE32" s="1"/>
-      <c r="FF32" s="1"/>
-      <c r="FG32" s="1"/>
-      <c r="FH32" s="1"/>
-      <c r="FI32" s="1"/>
-      <c r="FJ32" s="1"/>
-      <c r="FK32" s="1"/>
-      <c r="FL32" s="1"/>
-      <c r="FM32" s="1"/>
-      <c r="FN32" s="1"/>
-      <c r="FO32" s="1"/>
-      <c r="FP32" s="1"/>
-      <c r="FQ32" s="1"/>
-      <c r="FR32" s="1"/>
-      <c r="FS32" s="1"/>
-      <c r="FT32" s="1"/>
-      <c r="FU32" s="1"/>
-      <c r="FV32" s="1"/>
-      <c r="FW32" s="1"/>
-      <c r="FX32" s="1"/>
-      <c r="FY32" s="1"/>
-      <c r="FZ32" s="1"/>
-      <c r="GA32" s="1"/>
-      <c r="GB32" s="1"/>
-      <c r="GC32" s="1"/>
-      <c r="GD32" s="1"/>
-      <c r="GE32" s="1"/>
-      <c r="GF32" s="1"/>
-      <c r="GG32" s="1"/>
-      <c r="GH32" s="1"/>
-      <c r="GI32" s="1"/>
-      <c r="GJ32" s="1"/>
-      <c r="GK32" s="1"/>
-      <c r="GL32" s="1"/>
-      <c r="GM32" s="1"/>
-      <c r="GN32" s="1"/>
-      <c r="GO32" s="1"/>
-      <c r="GP32" s="1"/>
-      <c r="GQ32" s="1"/>
-      <c r="GR32" s="1"/>
-      <c r="GS32" s="1"/>
-      <c r="GT32" s="1"/>
-      <c r="GU32" s="1"/>
-      <c r="GV32" s="1"/>
-      <c r="GW32" s="1"/>
-      <c r="GX32" s="1"/>
-      <c r="GY32" s="1"/>
-      <c r="GZ32" s="1"/>
-      <c r="HA32" s="1"/>
-      <c r="HB32" s="1"/>
-      <c r="HC32" s="1"/>
-      <c r="HD32" s="1"/>
-      <c r="HE32" s="1"/>
-      <c r="HF32" s="1"/>
-      <c r="HG32" s="1"/>
-      <c r="HH32" s="1"/>
-      <c r="HI32" s="1"/>
-      <c r="HJ32" s="1"/>
-      <c r="HK32" s="1"/>
-      <c r="HL32" s="1"/>
-      <c r="HM32" s="1"/>
-      <c r="HN32" s="1"/>
-      <c r="HO32" s="1"/>
-      <c r="HP32" s="1"/>
-      <c r="HQ32" s="1"/>
-      <c r="HR32" s="1"/>
-      <c r="HS32" s="1"/>
-      <c r="HT32" s="1"/>
-      <c r="HU32" s="1"/>
-      <c r="HV32" s="1"/>
-      <c r="HW32" s="1"/>
-      <c r="HX32" s="1"/>
-      <c r="HY32" s="1"/>
-      <c r="HZ32" s="1"/>
-      <c r="IA32" s="1"/>
-      <c r="IB32" s="1"/>
-      <c r="IC32" s="1"/>
-      <c r="ID32" s="1"/>
-      <c r="IE32" s="1"/>
-      <c r="IF32" s="1"/>
-      <c r="IG32" s="1"/>
-      <c r="IH32" s="1"/>
-      <c r="II32" s="1"/>
-      <c r="IJ32" s="1"/>
-      <c r="IK32" s="1"/>
-      <c r="IL32" s="1"/>
-      <c r="IM32" s="1"/>
-      <c r="IN32" s="1"/>
-      <c r="IO32" s="1"/>
-      <c r="IP32" s="1"/>
-      <c r="IQ32" s="1"/>
-      <c r="IR32" s="1"/>
-      <c r="IS32" s="1"/>
-      <c r="IT32" s="1"/>
-      <c r="IU32" s="1"/>
-      <c r="IV32" s="1"/>
-      <c r="IW32" s="1"/>
-      <c r="IX32" s="1"/>
-    </row>
-    <row r="33" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="18"/>
-      <c r="R33" s="18"/>
-      <c r="S33" s="18"/>
-      <c r="T33" s="18"/>
-      <c r="U33" s="20"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="18"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
-      <c r="Z33" s="18"/>
-      <c r="AA33" s="18"/>
-      <c r="AB33" s="18"/>
-      <c r="AC33" s="18"/>
-      <c r="AD33" s="18"/>
-      <c r="AE33" s="18"/>
-      <c r="AF33" s="18"/>
-      <c r="AG33" s="18"/>
-      <c r="AH33" s="18"/>
-      <c r="AI33" s="18"/>
-      <c r="AJ33" s="18"/>
-      <c r="AK33" s="18"/>
-      <c r="AL33" s="18"/>
-      <c r="AM33" s="18"/>
-      <c r="AN33" s="18"/>
-      <c r="AO33" s="18"/>
-      <c r="AP33" s="18"/>
-      <c r="AQ33" s="18"/>
-      <c r="AR33" s="18"/>
-      <c r="AS33" s="19"/>
-      <c r="AT33" s="8"/>
-      <c r="AU33" s="10"/>
-      <c r="AV33" s="10"/>
-      <c r="AW33" s="10"/>
-      <c r="AX33" s="10"/>
-      <c r="AY33" s="10"/>
-      <c r="AZ33" s="10"/>
-      <c r="BA33" s="10"/>
-      <c r="BB33" s="10"/>
-      <c r="BC33" s="10"/>
-      <c r="BD33" s="10"/>
-      <c r="BE33" s="10"/>
-      <c r="BF33" s="10"/>
-      <c r="BG33" s="10"/>
-      <c r="BH33" s="10"/>
-      <c r="BI33" s="11"/>
-      <c r="BJ33" s="1"/>
-      <c r="BK33" s="1"/>
-      <c r="BL33" s="1"/>
-      <c r="BM33" s="1"/>
-      <c r="BN33" s="1"/>
-      <c r="BO33" s="1"/>
-      <c r="BP33" s="1"/>
-      <c r="BQ33" s="1"/>
-      <c r="BR33" s="1"/>
-      <c r="BS33" s="1"/>
-      <c r="BT33" s="1"/>
-      <c r="BU33" s="1"/>
-      <c r="BV33" s="1"/>
-      <c r="BW33" s="1"/>
-      <c r="BX33" s="1"/>
-      <c r="BY33" s="1"/>
-      <c r="BZ33" s="1"/>
-      <c r="CA33" s="1"/>
-      <c r="CB33" s="1"/>
-      <c r="CC33" s="1"/>
-      <c r="CD33" s="1"/>
-      <c r="CE33" s="1"/>
-      <c r="CF33" s="1"/>
-      <c r="CG33" s="1"/>
-      <c r="CH33" s="1"/>
-      <c r="CI33" s="1"/>
-      <c r="CJ33" s="1"/>
-      <c r="CK33" s="1"/>
-      <c r="CL33" s="1"/>
-      <c r="CM33" s="1"/>
-      <c r="CN33" s="1"/>
-      <c r="CO33" s="1"/>
-      <c r="CP33" s="1"/>
-      <c r="CQ33" s="1"/>
-      <c r="CR33" s="1"/>
-      <c r="CS33" s="1"/>
-      <c r="CT33" s="1"/>
-      <c r="CU33" s="1"/>
-      <c r="CV33" s="1"/>
-      <c r="CW33" s="1"/>
-      <c r="CX33" s="1"/>
-      <c r="CY33" s="1"/>
-      <c r="CZ33" s="1"/>
-      <c r="DA33" s="1"/>
-      <c r="DB33" s="1"/>
-      <c r="DC33" s="1"/>
-      <c r="DD33" s="1"/>
-      <c r="DE33" s="1"/>
-      <c r="DF33" s="1"/>
-      <c r="DG33" s="1"/>
-      <c r="DH33" s="1"/>
-      <c r="DI33" s="1"/>
-      <c r="DJ33" s="1"/>
-      <c r="DK33" s="1"/>
-      <c r="DL33" s="1"/>
-      <c r="DM33" s="1"/>
-      <c r="DN33" s="1"/>
-      <c r="DO33" s="1"/>
-      <c r="DP33" s="1"/>
-      <c r="DQ33" s="1"/>
-      <c r="DR33" s="1"/>
-      <c r="DS33" s="1"/>
-      <c r="DT33" s="1"/>
-      <c r="DU33" s="1"/>
-      <c r="DV33" s="1"/>
-      <c r="DW33" s="1"/>
-      <c r="DX33" s="1"/>
-      <c r="DY33" s="1"/>
-      <c r="DZ33" s="1"/>
-      <c r="EA33" s="1"/>
-      <c r="EB33" s="1"/>
-      <c r="EC33" s="1"/>
-      <c r="ED33" s="1"/>
-      <c r="EE33" s="1"/>
-      <c r="EF33" s="1"/>
-      <c r="EG33" s="1"/>
-      <c r="EH33" s="1"/>
-      <c r="EI33" s="1"/>
-      <c r="EJ33" s="1"/>
-      <c r="EK33" s="1"/>
-      <c r="EL33" s="1"/>
-      <c r="EM33" s="1"/>
-      <c r="EN33" s="1"/>
-      <c r="EO33" s="1"/>
-      <c r="EP33" s="1"/>
-      <c r="EQ33" s="1"/>
-      <c r="ER33" s="1"/>
-      <c r="ES33" s="1"/>
-      <c r="ET33" s="1"/>
-      <c r="EU33" s="1"/>
-      <c r="EV33" s="1"/>
-      <c r="EW33" s="1"/>
-      <c r="EX33" s="1"/>
-      <c r="EY33" s="1"/>
-      <c r="EZ33" s="1"/>
-      <c r="FA33" s="1"/>
-      <c r="FB33" s="1"/>
-      <c r="FC33" s="1"/>
-      <c r="FD33" s="1"/>
-      <c r="FE33" s="1"/>
-      <c r="FF33" s="1"/>
-      <c r="FG33" s="1"/>
-      <c r="FH33" s="1"/>
-      <c r="FI33" s="1"/>
-      <c r="FJ33" s="1"/>
-      <c r="FK33" s="1"/>
-      <c r="FL33" s="1"/>
-      <c r="FM33" s="1"/>
-      <c r="FN33" s="1"/>
-      <c r="FO33" s="1"/>
-      <c r="FP33" s="1"/>
-      <c r="FQ33" s="1"/>
-      <c r="FR33" s="1"/>
-      <c r="FS33" s="1"/>
-      <c r="FT33" s="1"/>
-      <c r="FU33" s="1"/>
-      <c r="FV33" s="1"/>
-      <c r="FW33" s="1"/>
-      <c r="FX33" s="1"/>
-      <c r="FY33" s="1"/>
-      <c r="FZ33" s="1"/>
-      <c r="GA33" s="1"/>
-      <c r="GB33" s="1"/>
-      <c r="GC33" s="1"/>
-      <c r="GD33" s="1"/>
-      <c r="GE33" s="1"/>
-      <c r="GF33" s="1"/>
-      <c r="GG33" s="1"/>
-      <c r="GH33" s="1"/>
-      <c r="GI33" s="1"/>
-      <c r="GJ33" s="1"/>
-      <c r="GK33" s="1"/>
-      <c r="GL33" s="1"/>
-      <c r="GM33" s="1"/>
-      <c r="GN33" s="1"/>
-      <c r="GO33" s="1"/>
-      <c r="GP33" s="1"/>
-      <c r="GQ33" s="1"/>
-      <c r="GR33" s="1"/>
-      <c r="GS33" s="1"/>
-      <c r="GT33" s="1"/>
-      <c r="GU33" s="1"/>
-      <c r="GV33" s="1"/>
-      <c r="GW33" s="1"/>
-      <c r="GX33" s="1"/>
-      <c r="GY33" s="1"/>
-      <c r="GZ33" s="1"/>
-      <c r="HA33" s="1"/>
-      <c r="HB33" s="1"/>
-      <c r="HC33" s="1"/>
-      <c r="HD33" s="1"/>
-      <c r="HE33" s="1"/>
-      <c r="HF33" s="1"/>
-      <c r="HG33" s="1"/>
-      <c r="HH33" s="1"/>
-      <c r="HI33" s="1"/>
-      <c r="HJ33" s="1"/>
-      <c r="HK33" s="1"/>
-      <c r="HL33" s="1"/>
-      <c r="HM33" s="1"/>
-      <c r="HN33" s="1"/>
-      <c r="HO33" s="1"/>
-      <c r="HP33" s="1"/>
-      <c r="HQ33" s="1"/>
-      <c r="HR33" s="1"/>
-      <c r="HS33" s="1"/>
-      <c r="HT33" s="1"/>
-      <c r="HU33" s="1"/>
-      <c r="HV33" s="1"/>
-      <c r="HW33" s="1"/>
-      <c r="HX33" s="1"/>
-      <c r="HY33" s="1"/>
-      <c r="HZ33" s="1"/>
-      <c r="IA33" s="1"/>
-      <c r="IB33" s="1"/>
-      <c r="IC33" s="1"/>
-      <c r="ID33" s="1"/>
-      <c r="IE33" s="1"/>
-      <c r="IF33" s="1"/>
-      <c r="IG33" s="1"/>
-      <c r="IH33" s="1"/>
-      <c r="II33" s="1"/>
-      <c r="IJ33" s="1"/>
-      <c r="IK33" s="1"/>
-      <c r="IL33" s="1"/>
-      <c r="IM33" s="1"/>
-      <c r="IN33" s="1"/>
-      <c r="IO33" s="1"/>
-      <c r="IP33" s="1"/>
-      <c r="IQ33" s="1"/>
-      <c r="IR33" s="1"/>
-      <c r="IS33" s="1"/>
-      <c r="IT33" s="1"/>
-      <c r="IU33" s="1"/>
-      <c r="IV33" s="1"/>
-      <c r="IW33" s="1"/>
-      <c r="IX33" s="1"/>
-    </row>
-    <row r="34" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="24"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
-      <c r="W34" s="18"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
-      <c r="Z34" s="18"/>
-      <c r="AA34" s="18"/>
-      <c r="AB34" s="18"/>
-      <c r="AC34" s="18"/>
-      <c r="AD34" s="18"/>
-      <c r="AE34" s="18"/>
-      <c r="AF34" s="18"/>
-      <c r="AG34" s="18"/>
-      <c r="AH34" s="18"/>
-      <c r="AI34" s="18"/>
-      <c r="AJ34" s="18"/>
-      <c r="AK34" s="18"/>
-      <c r="AL34" s="18"/>
-      <c r="AM34" s="18"/>
-      <c r="AN34" s="18"/>
-      <c r="AO34" s="18"/>
-      <c r="AP34" s="18"/>
-      <c r="AQ34" s="18"/>
-      <c r="AR34" s="18"/>
-      <c r="AS34" s="19"/>
-      <c r="AT34" s="8"/>
-      <c r="AU34" s="10"/>
-      <c r="AV34" s="10"/>
-      <c r="AW34" s="10"/>
-      <c r="AX34" s="10"/>
-      <c r="AY34" s="10"/>
-      <c r="AZ34" s="10"/>
-      <c r="BA34" s="10"/>
-      <c r="BB34" s="10"/>
-      <c r="BC34" s="10"/>
-      <c r="BD34" s="10"/>
-      <c r="BE34" s="10"/>
-      <c r="BF34" s="10"/>
-      <c r="BG34" s="10"/>
-      <c r="BH34" s="10"/>
-      <c r="BI34" s="11"/>
-      <c r="BJ34" s="1"/>
-      <c r="BK34" s="1"/>
-      <c r="BL34" s="1"/>
-      <c r="BM34" s="1"/>
-      <c r="BN34" s="1"/>
-      <c r="BO34" s="1"/>
-      <c r="BP34" s="1"/>
-      <c r="BQ34" s="1"/>
-      <c r="BR34" s="1"/>
-      <c r="BS34" s="1"/>
-      <c r="BT34" s="1"/>
-      <c r="BU34" s="1"/>
-      <c r="BV34" s="1"/>
-      <c r="BW34" s="1"/>
-      <c r="BX34" s="1"/>
-      <c r="BY34" s="1"/>
-      <c r="BZ34" s="1"/>
-      <c r="CA34" s="1"/>
-      <c r="CB34" s="1"/>
-      <c r="CC34" s="1"/>
-      <c r="CD34" s="1"/>
-      <c r="CE34" s="1"/>
-      <c r="CF34" s="1"/>
-      <c r="CG34" s="1"/>
-      <c r="CH34" s="1"/>
-      <c r="CI34" s="1"/>
-      <c r="CJ34" s="1"/>
-      <c r="CK34" s="1"/>
-      <c r="CL34" s="1"/>
-      <c r="CM34" s="1"/>
-      <c r="CN34" s="1"/>
-      <c r="CO34" s="1"/>
-      <c r="CP34" s="1"/>
-      <c r="CQ34" s="1"/>
-      <c r="CR34" s="1"/>
-      <c r="CS34" s="1"/>
-      <c r="CT34" s="1"/>
-      <c r="CU34" s="1"/>
-      <c r="CV34" s="1"/>
-      <c r="CW34" s="1"/>
-      <c r="CX34" s="1"/>
-      <c r="CY34" s="1"/>
-      <c r="CZ34" s="1"/>
-      <c r="DA34" s="1"/>
-      <c r="DB34" s="1"/>
-      <c r="DC34" s="1"/>
-      <c r="DD34" s="1"/>
-      <c r="DE34" s="1"/>
-      <c r="DF34" s="1"/>
-      <c r="DG34" s="1"/>
-      <c r="DH34" s="1"/>
-      <c r="DI34" s="1"/>
-      <c r="DJ34" s="1"/>
-      <c r="DK34" s="1"/>
-      <c r="DL34" s="1"/>
-      <c r="DM34" s="1"/>
-      <c r="DN34" s="1"/>
-      <c r="DO34" s="1"/>
-      <c r="DP34" s="1"/>
-      <c r="DQ34" s="1"/>
-      <c r="DR34" s="1"/>
-      <c r="DS34" s="1"/>
-      <c r="DT34" s="1"/>
-      <c r="DU34" s="1"/>
-      <c r="DV34" s="1"/>
-      <c r="DW34" s="1"/>
-      <c r="DX34" s="1"/>
-      <c r="DY34" s="1"/>
-      <c r="DZ34" s="1"/>
-      <c r="EA34" s="1"/>
-      <c r="EB34" s="1"/>
-      <c r="EC34" s="1"/>
-      <c r="ED34" s="1"/>
-      <c r="EE34" s="1"/>
-      <c r="EF34" s="1"/>
-      <c r="EG34" s="1"/>
-      <c r="EH34" s="1"/>
-      <c r="EI34" s="1"/>
-      <c r="EJ34" s="1"/>
-      <c r="EK34" s="1"/>
-      <c r="EL34" s="1"/>
-      <c r="EM34" s="1"/>
-      <c r="EN34" s="1"/>
-      <c r="EO34" s="1"/>
-      <c r="EP34" s="1"/>
-      <c r="EQ34" s="1"/>
-      <c r="ER34" s="1"/>
-      <c r="ES34" s="1"/>
-      <c r="ET34" s="1"/>
-      <c r="EU34" s="1"/>
-      <c r="EV34" s="1"/>
-      <c r="EW34" s="1"/>
-      <c r="EX34" s="1"/>
-      <c r="EY34" s="1"/>
-      <c r="EZ34" s="1"/>
-      <c r="FA34" s="1"/>
-      <c r="FB34" s="1"/>
-      <c r="FC34" s="1"/>
-      <c r="FD34" s="1"/>
-      <c r="FE34" s="1"/>
-      <c r="FF34" s="1"/>
-      <c r="FG34" s="1"/>
-      <c r="FH34" s="1"/>
-      <c r="FI34" s="1"/>
-      <c r="FJ34" s="1"/>
-      <c r="FK34" s="1"/>
-      <c r="FL34" s="1"/>
-      <c r="FM34" s="1"/>
-      <c r="FN34" s="1"/>
-      <c r="FO34" s="1"/>
-      <c r="FP34" s="1"/>
-      <c r="FQ34" s="1"/>
-      <c r="FR34" s="1"/>
-      <c r="FS34" s="1"/>
-      <c r="FT34" s="1"/>
-      <c r="FU34" s="1"/>
-      <c r="FV34" s="1"/>
-      <c r="FW34" s="1"/>
-      <c r="FX34" s="1"/>
-      <c r="FY34" s="1"/>
-      <c r="FZ34" s="1"/>
-      <c r="GA34" s="1"/>
-      <c r="GB34" s="1"/>
-      <c r="GC34" s="1"/>
-      <c r="GD34" s="1"/>
-      <c r="GE34" s="1"/>
-      <c r="GF34" s="1"/>
-      <c r="GG34" s="1"/>
-      <c r="GH34" s="1"/>
-      <c r="GI34" s="1"/>
-      <c r="GJ34" s="1"/>
-      <c r="GK34" s="1"/>
-      <c r="GL34" s="1"/>
-      <c r="GM34" s="1"/>
-      <c r="GN34" s="1"/>
-      <c r="GO34" s="1"/>
-      <c r="GP34" s="1"/>
-      <c r="GQ34" s="1"/>
-      <c r="GR34" s="1"/>
-      <c r="GS34" s="1"/>
-      <c r="GT34" s="1"/>
-      <c r="GU34" s="1"/>
-      <c r="GV34" s="1"/>
-      <c r="GW34" s="1"/>
-      <c r="GX34" s="1"/>
-      <c r="GY34" s="1"/>
-      <c r="GZ34" s="1"/>
-      <c r="HA34" s="1"/>
-      <c r="HB34" s="1"/>
-      <c r="HC34" s="1"/>
-      <c r="HD34" s="1"/>
-      <c r="HE34" s="1"/>
-      <c r="HF34" s="1"/>
-      <c r="HG34" s="1"/>
-      <c r="HH34" s="1"/>
-      <c r="HI34" s="1"/>
-      <c r="HJ34" s="1"/>
-      <c r="HK34" s="1"/>
-      <c r="HL34" s="1"/>
-      <c r="HM34" s="1"/>
-      <c r="HN34" s="1"/>
-      <c r="HO34" s="1"/>
-      <c r="HP34" s="1"/>
-      <c r="HQ34" s="1"/>
-      <c r="HR34" s="1"/>
-      <c r="HS34" s="1"/>
-      <c r="HT34" s="1"/>
-      <c r="HU34" s="1"/>
-      <c r="HV34" s="1"/>
-      <c r="HW34" s="1"/>
-      <c r="HX34" s="1"/>
-      <c r="HY34" s="1"/>
-      <c r="HZ34" s="1"/>
-      <c r="IA34" s="1"/>
-      <c r="IB34" s="1"/>
-      <c r="IC34" s="1"/>
-      <c r="ID34" s="1"/>
-      <c r="IE34" s="1"/>
-      <c r="IF34" s="1"/>
-      <c r="IG34" s="1"/>
-      <c r="IH34" s="1"/>
-      <c r="II34" s="1"/>
-      <c r="IJ34" s="1"/>
-      <c r="IK34" s="1"/>
-      <c r="IL34" s="1"/>
-      <c r="IM34" s="1"/>
-      <c r="IN34" s="1"/>
-      <c r="IO34" s="1"/>
-      <c r="IP34" s="1"/>
-      <c r="IQ34" s="1"/>
-      <c r="IR34" s="1"/>
-      <c r="IS34" s="1"/>
-      <c r="IT34" s="1"/>
-      <c r="IU34" s="1"/>
-      <c r="IV34" s="1"/>
-      <c r="IW34" s="1"/>
-      <c r="IX34" s="1"/>
-    </row>
-    <row r="35" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="18"/>
-      <c r="R35" s="18"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="18"/>
-      <c r="X35" s="20"/>
-      <c r="Y35" s="18"/>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="18"/>
-      <c r="AB35" s="18"/>
-      <c r="AC35" s="18"/>
-      <c r="AD35" s="18"/>
-      <c r="AE35" s="18"/>
-      <c r="AF35" s="18"/>
-      <c r="AG35" s="18"/>
-      <c r="AH35" s="18"/>
-      <c r="AI35" s="18"/>
-      <c r="AJ35" s="18"/>
-      <c r="AK35" s="18"/>
-      <c r="AL35" s="18"/>
-      <c r="AM35" s="18"/>
-      <c r="AN35" s="18"/>
-      <c r="AO35" s="18"/>
-      <c r="AP35" s="18"/>
-      <c r="AQ35" s="18"/>
-      <c r="AR35" s="18"/>
-      <c r="AS35" s="19"/>
-      <c r="AT35" s="8"/>
-      <c r="AU35" s="10"/>
-      <c r="AV35" s="10"/>
-      <c r="AW35" s="10"/>
-      <c r="AX35" s="10"/>
-      <c r="AY35" s="10"/>
-      <c r="AZ35" s="10"/>
-      <c r="BA35" s="10"/>
-      <c r="BB35" s="10"/>
-      <c r="BC35" s="10"/>
-      <c r="BD35" s="10"/>
-      <c r="BE35" s="10"/>
-      <c r="BF35" s="10"/>
-      <c r="BG35" s="10"/>
-      <c r="BH35" s="10"/>
-      <c r="BI35" s="11"/>
-      <c r="BJ35" s="1"/>
-      <c r="BK35" s="1"/>
-      <c r="BL35" s="1"/>
-      <c r="BM35" s="1"/>
-      <c r="BN35" s="1"/>
-      <c r="BO35" s="1"/>
-      <c r="BP35" s="1"/>
-      <c r="BQ35" s="1"/>
-      <c r="BR35" s="1"/>
-      <c r="BS35" s="1"/>
-      <c r="BT35" s="1"/>
-      <c r="BU35" s="1"/>
-      <c r="BV35" s="1"/>
-      <c r="BW35" s="1"/>
-      <c r="BX35" s="1"/>
-      <c r="BY35" s="1"/>
-      <c r="BZ35" s="1"/>
-      <c r="CA35" s="1"/>
-      <c r="CB35" s="1"/>
-      <c r="CC35" s="1"/>
-      <c r="CD35" s="1"/>
-      <c r="CE35" s="1"/>
-      <c r="CF35" s="1"/>
-      <c r="CG35" s="1"/>
-      <c r="CH35" s="1"/>
-      <c r="CI35" s="1"/>
-      <c r="CJ35" s="1"/>
-      <c r="CK35" s="1"/>
-      <c r="CL35" s="1"/>
-      <c r="CM35" s="1"/>
-      <c r="CN35" s="1"/>
-      <c r="CO35" s="1"/>
-      <c r="CP35" s="1"/>
-      <c r="CQ35" s="1"/>
-      <c r="CR35" s="1"/>
-      <c r="CS35" s="1"/>
-      <c r="CT35" s="1"/>
-      <c r="CU35" s="1"/>
-      <c r="CV35" s="1"/>
-      <c r="CW35" s="1"/>
-      <c r="CX35" s="1"/>
-      <c r="CY35" s="1"/>
-      <c r="CZ35" s="1"/>
-      <c r="DA35" s="1"/>
-      <c r="DB35" s="1"/>
-      <c r="DC35" s="1"/>
-      <c r="DD35" s="1"/>
-      <c r="DE35" s="1"/>
-      <c r="DF35" s="1"/>
-      <c r="DG35" s="1"/>
-      <c r="DH35" s="1"/>
-      <c r="DI35" s="1"/>
-      <c r="DJ35" s="1"/>
-      <c r="DK35" s="1"/>
-      <c r="DL35" s="1"/>
-      <c r="DM35" s="1"/>
-      <c r="DN35" s="1"/>
-      <c r="DO35" s="1"/>
-      <c r="DP35" s="1"/>
-      <c r="DQ35" s="1"/>
-      <c r="DR35" s="1"/>
-      <c r="DS35" s="1"/>
-      <c r="DT35" s="1"/>
-      <c r="DU35" s="1"/>
-      <c r="DV35" s="1"/>
-      <c r="DW35" s="1"/>
-      <c r="DX35" s="1"/>
-      <c r="DY35" s="1"/>
-      <c r="DZ35" s="1"/>
-      <c r="EA35" s="1"/>
-      <c r="EB35" s="1"/>
-      <c r="EC35" s="1"/>
-      <c r="ED35" s="1"/>
-      <c r="EE35" s="1"/>
-      <c r="EF35" s="1"/>
-      <c r="EG35" s="1"/>
-      <c r="EH35" s="1"/>
-      <c r="EI35" s="1"/>
-      <c r="EJ35" s="1"/>
-      <c r="EK35" s="1"/>
-      <c r="EL35" s="1"/>
-      <c r="EM35" s="1"/>
-      <c r="EN35" s="1"/>
-      <c r="EO35" s="1"/>
-      <c r="EP35" s="1"/>
-      <c r="EQ35" s="1"/>
-      <c r="ER35" s="1"/>
-      <c r="ES35" s="1"/>
-      <c r="ET35" s="1"/>
-      <c r="EU35" s="1"/>
-      <c r="EV35" s="1"/>
-      <c r="EW35" s="1"/>
-      <c r="EX35" s="1"/>
-      <c r="EY35" s="1"/>
-      <c r="EZ35" s="1"/>
-      <c r="FA35" s="1"/>
-      <c r="FB35" s="1"/>
-      <c r="FC35" s="1"/>
-      <c r="FD35" s="1"/>
-      <c r="FE35" s="1"/>
-      <c r="FF35" s="1"/>
-      <c r="FG35" s="1"/>
-      <c r="FH35" s="1"/>
-      <c r="FI35" s="1"/>
-      <c r="FJ35" s="1"/>
-      <c r="FK35" s="1"/>
-      <c r="FL35" s="1"/>
-      <c r="FM35" s="1"/>
-      <c r="FN35" s="1"/>
-      <c r="FO35" s="1"/>
-      <c r="FP35" s="1"/>
-      <c r="FQ35" s="1"/>
-      <c r="FR35" s="1"/>
-      <c r="FS35" s="1"/>
-      <c r="FT35" s="1"/>
-      <c r="FU35" s="1"/>
-      <c r="FV35" s="1"/>
-      <c r="FW35" s="1"/>
-      <c r="FX35" s="1"/>
-      <c r="FY35" s="1"/>
-      <c r="FZ35" s="1"/>
-      <c r="GA35" s="1"/>
-      <c r="GB35" s="1"/>
-      <c r="GC35" s="1"/>
-      <c r="GD35" s="1"/>
-      <c r="GE35" s="1"/>
-      <c r="GF35" s="1"/>
-      <c r="GG35" s="1"/>
-      <c r="GH35" s="1"/>
-      <c r="GI35" s="1"/>
-      <c r="GJ35" s="1"/>
-      <c r="GK35" s="1"/>
-      <c r="GL35" s="1"/>
-      <c r="GM35" s="1"/>
-      <c r="GN35" s="1"/>
-      <c r="GO35" s="1"/>
-      <c r="GP35" s="1"/>
-      <c r="GQ35" s="1"/>
-      <c r="GR35" s="1"/>
-      <c r="GS35" s="1"/>
-      <c r="GT35" s="1"/>
-      <c r="GU35" s="1"/>
-      <c r="GV35" s="1"/>
-      <c r="GW35" s="1"/>
-      <c r="GX35" s="1"/>
-      <c r="GY35" s="1"/>
-      <c r="GZ35" s="1"/>
-      <c r="HA35" s="1"/>
-      <c r="HB35" s="1"/>
-      <c r="HC35" s="1"/>
-      <c r="HD35" s="1"/>
-      <c r="HE35" s="1"/>
-      <c r="HF35" s="1"/>
-      <c r="HG35" s="1"/>
-      <c r="HH35" s="1"/>
-      <c r="HI35" s="1"/>
-      <c r="HJ35" s="1"/>
-      <c r="HK35" s="1"/>
-      <c r="HL35" s="1"/>
-      <c r="HM35" s="1"/>
-      <c r="HN35" s="1"/>
-      <c r="HO35" s="1"/>
-      <c r="HP35" s="1"/>
-      <c r="HQ35" s="1"/>
-      <c r="HR35" s="1"/>
-      <c r="HS35" s="1"/>
-      <c r="HT35" s="1"/>
-      <c r="HU35" s="1"/>
-      <c r="HV35" s="1"/>
-      <c r="HW35" s="1"/>
-      <c r="HX35" s="1"/>
-      <c r="HY35" s="1"/>
-      <c r="HZ35" s="1"/>
-      <c r="IA35" s="1"/>
-      <c r="IB35" s="1"/>
-      <c r="IC35" s="1"/>
-      <c r="ID35" s="1"/>
-      <c r="IE35" s="1"/>
-      <c r="IF35" s="1"/>
-      <c r="IG35" s="1"/>
-      <c r="IH35" s="1"/>
-      <c r="II35" s="1"/>
-      <c r="IJ35" s="1"/>
-      <c r="IK35" s="1"/>
-      <c r="IL35" s="1"/>
-      <c r="IM35" s="1"/>
-      <c r="IN35" s="1"/>
-      <c r="IO35" s="1"/>
-      <c r="IP35" s="1"/>
-      <c r="IQ35" s="1"/>
-      <c r="IR35" s="1"/>
-      <c r="IS35" s="1"/>
-      <c r="IT35" s="1"/>
-      <c r="IU35" s="1"/>
-      <c r="IV35" s="1"/>
-      <c r="IW35" s="1"/>
-      <c r="IX35" s="1"/>
-    </row>
-    <row r="36" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="18"/>
-      <c r="R36" s="18"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="18"/>
-      <c r="U36" s="18"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="18"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="18"/>
-      <c r="Z36" s="18"/>
-      <c r="AA36" s="18"/>
-      <c r="AB36" s="18"/>
-      <c r="AC36" s="18"/>
-      <c r="AD36" s="18"/>
-      <c r="AE36" s="18"/>
-      <c r="AF36" s="18"/>
-      <c r="AG36" s="18"/>
-      <c r="AH36" s="18"/>
-      <c r="AI36" s="18"/>
-      <c r="AJ36" s="18"/>
-      <c r="AK36" s="18"/>
-      <c r="AL36" s="18"/>
-      <c r="AM36" s="18"/>
-      <c r="AN36" s="18"/>
-      <c r="AO36" s="18"/>
-      <c r="AP36" s="18"/>
-      <c r="AQ36" s="18"/>
-      <c r="AR36" s="18"/>
-      <c r="AS36" s="19"/>
-      <c r="AT36" s="8"/>
-      <c r="AU36" s="10"/>
-      <c r="AV36" s="10"/>
-      <c r="AW36" s="10"/>
-      <c r="AX36" s="10"/>
-      <c r="AY36" s="10"/>
-      <c r="AZ36" s="10"/>
-      <c r="BA36" s="10"/>
-      <c r="BB36" s="10"/>
-      <c r="BC36" s="10"/>
-      <c r="BD36" s="10"/>
-      <c r="BE36" s="10"/>
-      <c r="BF36" s="10"/>
-      <c r="BG36" s="10"/>
-      <c r="BH36" s="10"/>
-      <c r="BI36" s="11"/>
-      <c r="BJ36" s="1"/>
-      <c r="BK36" s="1"/>
-      <c r="BL36" s="1"/>
-      <c r="BM36" s="1"/>
-      <c r="BN36" s="1"/>
-      <c r="BO36" s="1"/>
-      <c r="BP36" s="1"/>
-      <c r="BQ36" s="1"/>
-      <c r="BR36" s="1"/>
-      <c r="BS36" s="1"/>
-      <c r="BT36" s="1"/>
-      <c r="BU36" s="1"/>
-      <c r="BV36" s="1"/>
-      <c r="BW36" s="1"/>
-      <c r="BX36" s="1"/>
-      <c r="BY36" s="1"/>
-      <c r="BZ36" s="1"/>
-      <c r="CA36" s="1"/>
-      <c r="CB36" s="1"/>
-      <c r="CC36" s="1"/>
-      <c r="CD36" s="1"/>
-      <c r="CE36" s="1"/>
-      <c r="CF36" s="1"/>
-      <c r="CG36" s="1"/>
-      <c r="CH36" s="1"/>
-      <c r="CI36" s="1"/>
-      <c r="CJ36" s="1"/>
-      <c r="CK36" s="1"/>
-      <c r="CL36" s="1"/>
-      <c r="CM36" s="1"/>
-      <c r="CN36" s="1"/>
-      <c r="CO36" s="1"/>
-      <c r="CP36" s="1"/>
-      <c r="CQ36" s="1"/>
-      <c r="CR36" s="1"/>
-      <c r="CS36" s="1"/>
-      <c r="CT36" s="1"/>
-      <c r="CU36" s="1"/>
-      <c r="CV36" s="1"/>
-      <c r="CW36" s="1"/>
-      <c r="CX36" s="1"/>
-      <c r="CY36" s="1"/>
-      <c r="CZ36" s="1"/>
-      <c r="DA36" s="1"/>
-      <c r="DB36" s="1"/>
-      <c r="DC36" s="1"/>
-      <c r="DD36" s="1"/>
-      <c r="DE36" s="1"/>
-      <c r="DF36" s="1"/>
-      <c r="DG36" s="1"/>
-      <c r="DH36" s="1"/>
-      <c r="DI36" s="1"/>
-      <c r="DJ36" s="1"/>
-      <c r="DK36" s="1"/>
-      <c r="DL36" s="1"/>
-      <c r="DM36" s="1"/>
-      <c r="DN36" s="1"/>
-      <c r="DO36" s="1"/>
-      <c r="DP36" s="1"/>
-      <c r="DQ36" s="1"/>
-      <c r="DR36" s="1"/>
-      <c r="DS36" s="1"/>
-      <c r="DT36" s="1"/>
-      <c r="DU36" s="1"/>
-      <c r="DV36" s="1"/>
-      <c r="DW36" s="1"/>
-      <c r="DX36" s="1"/>
-      <c r="DY36" s="1"/>
-      <c r="DZ36" s="1"/>
-      <c r="EA36" s="1"/>
-      <c r="EB36" s="1"/>
-      <c r="EC36" s="1"/>
-      <c r="ED36" s="1"/>
-      <c r="EE36" s="1"/>
-      <c r="EF36" s="1"/>
-      <c r="EG36" s="1"/>
-      <c r="EH36" s="1"/>
-      <c r="EI36" s="1"/>
-      <c r="EJ36" s="1"/>
-      <c r="EK36" s="1"/>
-      <c r="EL36" s="1"/>
-      <c r="EM36" s="1"/>
-      <c r="EN36" s="1"/>
-      <c r="EO36" s="1"/>
-      <c r="EP36" s="1"/>
-      <c r="EQ36" s="1"/>
-      <c r="ER36" s="1"/>
-      <c r="ES36" s="1"/>
-      <c r="ET36" s="1"/>
-      <c r="EU36" s="1"/>
-      <c r="EV36" s="1"/>
-      <c r="EW36" s="1"/>
-      <c r="EX36" s="1"/>
-      <c r="EY36" s="1"/>
-      <c r="EZ36" s="1"/>
-      <c r="FA36" s="1"/>
-      <c r="FB36" s="1"/>
-      <c r="FC36" s="1"/>
-      <c r="FD36" s="1"/>
-      <c r="FE36" s="1"/>
-      <c r="FF36" s="1"/>
-      <c r="FG36" s="1"/>
-      <c r="FH36" s="1"/>
-      <c r="FI36" s="1"/>
-      <c r="FJ36" s="1"/>
-      <c r="FK36" s="1"/>
-      <c r="FL36" s="1"/>
-      <c r="FM36" s="1"/>
-      <c r="FN36" s="1"/>
-      <c r="FO36" s="1"/>
-      <c r="FP36" s="1"/>
-      <c r="FQ36" s="1"/>
-      <c r="FR36" s="1"/>
-      <c r="FS36" s="1"/>
-      <c r="FT36" s="1"/>
-      <c r="FU36" s="1"/>
-      <c r="FV36" s="1"/>
-      <c r="FW36" s="1"/>
-      <c r="FX36" s="1"/>
-      <c r="FY36" s="1"/>
-      <c r="FZ36" s="1"/>
-      <c r="GA36" s="1"/>
-      <c r="GB36" s="1"/>
-      <c r="GC36" s="1"/>
-      <c r="GD36" s="1"/>
-      <c r="GE36" s="1"/>
-      <c r="GF36" s="1"/>
-      <c r="GG36" s="1"/>
-      <c r="GH36" s="1"/>
-      <c r="GI36" s="1"/>
-      <c r="GJ36" s="1"/>
-      <c r="GK36" s="1"/>
-      <c r="GL36" s="1"/>
-      <c r="GM36" s="1"/>
-      <c r="GN36" s="1"/>
-      <c r="GO36" s="1"/>
-      <c r="GP36" s="1"/>
-      <c r="GQ36" s="1"/>
-      <c r="GR36" s="1"/>
-      <c r="GS36" s="1"/>
-      <c r="GT36" s="1"/>
-      <c r="GU36" s="1"/>
-      <c r="GV36" s="1"/>
-      <c r="GW36" s="1"/>
-      <c r="GX36" s="1"/>
-      <c r="GY36" s="1"/>
-      <c r="GZ36" s="1"/>
-      <c r="HA36" s="1"/>
-      <c r="HB36" s="1"/>
-      <c r="HC36" s="1"/>
-      <c r="HD36" s="1"/>
-      <c r="HE36" s="1"/>
-      <c r="HF36" s="1"/>
-      <c r="HG36" s="1"/>
-      <c r="HH36" s="1"/>
-      <c r="HI36" s="1"/>
-      <c r="HJ36" s="1"/>
-      <c r="HK36" s="1"/>
-      <c r="HL36" s="1"/>
-      <c r="HM36" s="1"/>
-      <c r="HN36" s="1"/>
-      <c r="HO36" s="1"/>
-      <c r="HP36" s="1"/>
-      <c r="HQ36" s="1"/>
-      <c r="HR36" s="1"/>
-      <c r="HS36" s="1"/>
-      <c r="HT36" s="1"/>
-      <c r="HU36" s="1"/>
-      <c r="HV36" s="1"/>
-      <c r="HW36" s="1"/>
-      <c r="HX36" s="1"/>
-      <c r="HY36" s="1"/>
-      <c r="HZ36" s="1"/>
-      <c r="IA36" s="1"/>
-      <c r="IB36" s="1"/>
-      <c r="IC36" s="1"/>
-      <c r="ID36" s="1"/>
-      <c r="IE36" s="1"/>
-      <c r="IF36" s="1"/>
-      <c r="IG36" s="1"/>
-      <c r="IH36" s="1"/>
-      <c r="II36" s="1"/>
-      <c r="IJ36" s="1"/>
-      <c r="IK36" s="1"/>
-      <c r="IL36" s="1"/>
-      <c r="IM36" s="1"/>
-      <c r="IN36" s="1"/>
-      <c r="IO36" s="1"/>
-      <c r="IP36" s="1"/>
-      <c r="IQ36" s="1"/>
-      <c r="IR36" s="1"/>
-      <c r="IS36" s="1"/>
-      <c r="IT36" s="1"/>
-      <c r="IU36" s="1"/>
-      <c r="IV36" s="1"/>
-      <c r="IW36" s="1"/>
-      <c r="IX36" s="1"/>
-    </row>
-    <row r="37" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="18"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
-      <c r="Z37" s="18"/>
-      <c r="AA37" s="18"/>
-      <c r="AB37" s="18"/>
-      <c r="AC37" s="18"/>
-      <c r="AD37" s="18"/>
-      <c r="AE37" s="18"/>
-      <c r="AF37" s="18"/>
-      <c r="AG37" s="18"/>
-      <c r="AH37" s="18"/>
-      <c r="AI37" s="18"/>
-      <c r="AJ37" s="18"/>
-      <c r="AK37" s="18"/>
-      <c r="AL37" s="18"/>
-      <c r="AM37" s="18"/>
-      <c r="AN37" s="18"/>
-      <c r="AO37" s="18"/>
-      <c r="AP37" s="18"/>
-      <c r="AQ37" s="18"/>
-      <c r="AR37" s="18"/>
-      <c r="AS37" s="19"/>
-      <c r="AT37" s="8"/>
-      <c r="AU37" s="10"/>
-      <c r="AV37" s="9"/>
-      <c r="AW37" s="10"/>
-      <c r="AX37" s="10"/>
-      <c r="AY37" s="10"/>
-      <c r="AZ37" s="10"/>
-      <c r="BA37" s="10"/>
-      <c r="BB37" s="10"/>
-      <c r="BC37" s="10"/>
-      <c r="BD37" s="10"/>
-      <c r="BE37" s="10"/>
-      <c r="BF37" s="10"/>
-      <c r="BG37" s="10"/>
-      <c r="BH37" s="10"/>
-      <c r="BI37" s="11"/>
-      <c r="BJ37" s="1"/>
-      <c r="BK37" s="1"/>
-      <c r="BL37" s="1"/>
-      <c r="BM37" s="1"/>
-      <c r="BN37" s="1"/>
-      <c r="BO37" s="1"/>
-      <c r="BP37" s="1"/>
-      <c r="BQ37" s="1"/>
-      <c r="BR37" s="1"/>
-      <c r="BS37" s="1"/>
-      <c r="BT37" s="1"/>
-      <c r="BU37" s="1"/>
-      <c r="BV37" s="1"/>
-      <c r="BW37" s="1"/>
-      <c r="BX37" s="1"/>
-      <c r="BY37" s="1"/>
-      <c r="BZ37" s="1"/>
-      <c r="CA37" s="1"/>
-      <c r="CB37" s="1"/>
-      <c r="CC37" s="1"/>
-      <c r="CD37" s="1"/>
-      <c r="CE37" s="1"/>
-      <c r="CF37" s="1"/>
-      <c r="CG37" s="1"/>
-      <c r="CH37" s="1"/>
-      <c r="CI37" s="1"/>
-      <c r="CJ37" s="1"/>
-      <c r="CK37" s="1"/>
-      <c r="CL37" s="1"/>
-      <c r="CM37" s="1"/>
-      <c r="CN37" s="1"/>
-      <c r="CO37" s="1"/>
-      <c r="CP37" s="1"/>
-      <c r="CQ37" s="1"/>
-      <c r="CR37" s="1"/>
-      <c r="CS37" s="1"/>
-      <c r="CT37" s="1"/>
-      <c r="CU37" s="1"/>
-      <c r="CV37" s="1"/>
-      <c r="CW37" s="1"/>
-      <c r="CX37" s="1"/>
-      <c r="CY37" s="1"/>
-      <c r="CZ37" s="1"/>
-      <c r="DA37" s="1"/>
-      <c r="DB37" s="1"/>
-      <c r="DC37" s="1"/>
-      <c r="DD37" s="1"/>
-      <c r="DE37" s="1"/>
-      <c r="DF37" s="1"/>
-      <c r="DG37" s="1"/>
-      <c r="DH37" s="1"/>
-      <c r="DI37" s="1"/>
-      <c r="DJ37" s="1"/>
-      <c r="DK37" s="1"/>
-      <c r="DL37" s="1"/>
-      <c r="DM37" s="1"/>
-      <c r="DN37" s="1"/>
-      <c r="DO37" s="1"/>
-      <c r="DP37" s="1"/>
-      <c r="DQ37" s="1"/>
-      <c r="DR37" s="1"/>
-      <c r="DS37" s="1"/>
-      <c r="DT37" s="1"/>
-      <c r="DU37" s="1"/>
-      <c r="DV37" s="1"/>
-      <c r="DW37" s="1"/>
-      <c r="DX37" s="1"/>
-      <c r="DY37" s="1"/>
-      <c r="DZ37" s="1"/>
-      <c r="EA37" s="1"/>
-      <c r="EB37" s="1"/>
-      <c r="EC37" s="1"/>
-      <c r="ED37" s="1"/>
-      <c r="EE37" s="1"/>
-      <c r="EF37" s="1"/>
-      <c r="EG37" s="1"/>
-      <c r="EH37" s="1"/>
-      <c r="EI37" s="1"/>
-      <c r="EJ37" s="1"/>
-      <c r="EK37" s="1"/>
-      <c r="EL37" s="1"/>
-      <c r="EM37" s="1"/>
-      <c r="EN37" s="1"/>
-      <c r="EO37" s="1"/>
-      <c r="EP37" s="1"/>
-      <c r="EQ37" s="1"/>
-      <c r="ER37" s="1"/>
-      <c r="ES37" s="1"/>
-      <c r="ET37" s="1"/>
-      <c r="EU37" s="1"/>
-      <c r="EV37" s="1"/>
-      <c r="EW37" s="1"/>
-      <c r="EX37" s="1"/>
-      <c r="EY37" s="1"/>
-      <c r="EZ37" s="1"/>
-      <c r="FA37" s="1"/>
-      <c r="FB37" s="1"/>
-      <c r="FC37" s="1"/>
-      <c r="FD37" s="1"/>
-      <c r="FE37" s="1"/>
-      <c r="FF37" s="1"/>
-      <c r="FG37" s="1"/>
-      <c r="FH37" s="1"/>
-      <c r="FI37" s="1"/>
-      <c r="FJ37" s="1"/>
-      <c r="FK37" s="1"/>
-      <c r="FL37" s="1"/>
-      <c r="FM37" s="1"/>
-      <c r="FN37" s="1"/>
-      <c r="FO37" s="1"/>
-      <c r="FP37" s="1"/>
-      <c r="FQ37" s="1"/>
-      <c r="FR37" s="1"/>
-      <c r="FS37" s="1"/>
-      <c r="FT37" s="1"/>
-      <c r="FU37" s="1"/>
-      <c r="FV37" s="1"/>
-      <c r="FW37" s="1"/>
-      <c r="FX37" s="1"/>
-      <c r="FY37" s="1"/>
-      <c r="FZ37" s="1"/>
-      <c r="GA37" s="1"/>
-      <c r="GB37" s="1"/>
-      <c r="GC37" s="1"/>
-      <c r="GD37" s="1"/>
-      <c r="GE37" s="1"/>
-      <c r="GF37" s="1"/>
-      <c r="GG37" s="1"/>
-      <c r="GH37" s="1"/>
-      <c r="GI37" s="1"/>
-      <c r="GJ37" s="1"/>
-      <c r="GK37" s="1"/>
-      <c r="GL37" s="1"/>
-      <c r="GM37" s="1"/>
-      <c r="GN37" s="1"/>
-      <c r="GO37" s="1"/>
-      <c r="GP37" s="1"/>
-      <c r="GQ37" s="1"/>
-      <c r="GR37" s="1"/>
-      <c r="GS37" s="1"/>
-      <c r="GT37" s="1"/>
-      <c r="GU37" s="1"/>
-      <c r="GV37" s="1"/>
-      <c r="GW37" s="1"/>
-      <c r="GX37" s="1"/>
-      <c r="GY37" s="1"/>
-      <c r="GZ37" s="1"/>
-      <c r="HA37" s="1"/>
-      <c r="HB37" s="1"/>
-      <c r="HC37" s="1"/>
-      <c r="HD37" s="1"/>
-      <c r="HE37" s="1"/>
-      <c r="HF37" s="1"/>
-      <c r="HG37" s="1"/>
-      <c r="HH37" s="1"/>
-      <c r="HI37" s="1"/>
-      <c r="HJ37" s="1"/>
-      <c r="HK37" s="1"/>
-      <c r="HL37" s="1"/>
-      <c r="HM37" s="1"/>
-      <c r="HN37" s="1"/>
-      <c r="HO37" s="1"/>
-      <c r="HP37" s="1"/>
-      <c r="HQ37" s="1"/>
-      <c r="HR37" s="1"/>
-      <c r="HS37" s="1"/>
-      <c r="HT37" s="1"/>
-      <c r="HU37" s="1"/>
-      <c r="HV37" s="1"/>
-      <c r="HW37" s="1"/>
-      <c r="HX37" s="1"/>
-      <c r="HY37" s="1"/>
-      <c r="HZ37" s="1"/>
-      <c r="IA37" s="1"/>
-      <c r="IB37" s="1"/>
-      <c r="IC37" s="1"/>
-      <c r="ID37" s="1"/>
-      <c r="IE37" s="1"/>
-      <c r="IF37" s="1"/>
-      <c r="IG37" s="1"/>
-      <c r="IH37" s="1"/>
-      <c r="II37" s="1"/>
-      <c r="IJ37" s="1"/>
-      <c r="IK37" s="1"/>
-      <c r="IL37" s="1"/>
-      <c r="IM37" s="1"/>
-      <c r="IN37" s="1"/>
-      <c r="IO37" s="1"/>
-      <c r="IP37" s="1"/>
-      <c r="IQ37" s="1"/>
-      <c r="IR37" s="1"/>
-      <c r="IS37" s="1"/>
-      <c r="IT37" s="1"/>
-      <c r="IU37" s="1"/>
-      <c r="IV37" s="1"/>
-      <c r="IW37" s="1"/>
-      <c r="IX37" s="1"/>
-    </row>
-    <row r="38" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="25"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
-      <c r="V38" s="18"/>
-      <c r="W38" s="18"/>
-      <c r="X38" s="18"/>
-      <c r="Y38" s="18"/>
-      <c r="Z38" s="18"/>
-      <c r="AA38" s="18"/>
-      <c r="AB38" s="18"/>
-      <c r="AC38" s="18"/>
-      <c r="AD38" s="18"/>
-      <c r="AE38" s="18"/>
-      <c r="AF38" s="18"/>
-      <c r="AG38" s="18"/>
-      <c r="AH38" s="18"/>
-      <c r="AI38" s="18"/>
-      <c r="AJ38" s="18"/>
-      <c r="AK38" s="18"/>
-      <c r="AL38" s="18"/>
-      <c r="AM38" s="18"/>
-      <c r="AN38" s="18"/>
-      <c r="AO38" s="18"/>
-      <c r="AP38" s="18"/>
-      <c r="AQ38" s="18"/>
-      <c r="AR38" s="18"/>
-      <c r="AS38" s="19"/>
-      <c r="AT38" s="8"/>
-      <c r="AU38" s="10"/>
-      <c r="AV38" s="10"/>
-      <c r="AW38" s="10"/>
-      <c r="AX38" s="10"/>
-      <c r="AY38" s="10"/>
-      <c r="AZ38" s="10"/>
-      <c r="BA38" s="10"/>
-      <c r="BB38" s="10"/>
-      <c r="BC38" s="10"/>
-      <c r="BD38" s="10"/>
-      <c r="BE38" s="10"/>
-      <c r="BF38" s="10"/>
-      <c r="BG38" s="10"/>
-      <c r="BH38" s="10"/>
-      <c r="BI38" s="11"/>
-      <c r="BJ38" s="1"/>
-      <c r="BK38" s="1"/>
-      <c r="BL38" s="1"/>
-      <c r="BM38" s="1"/>
-      <c r="BN38" s="1"/>
-      <c r="BO38" s="1"/>
-      <c r="BP38" s="1"/>
-      <c r="BQ38" s="1"/>
-      <c r="BR38" s="1"/>
-      <c r="BS38" s="1"/>
-      <c r="BT38" s="1"/>
-      <c r="BU38" s="1"/>
-      <c r="BV38" s="1"/>
-      <c r="BW38" s="1"/>
-      <c r="BX38" s="1"/>
-      <c r="BY38" s="1"/>
-      <c r="BZ38" s="1"/>
-      <c r="CA38" s="1"/>
-      <c r="CB38" s="1"/>
-      <c r="CC38" s="1"/>
-      <c r="CD38" s="1"/>
-      <c r="CE38" s="1"/>
-      <c r="CF38" s="1"/>
-      <c r="CG38" s="1"/>
-      <c r="CH38" s="1"/>
-      <c r="CI38" s="1"/>
-      <c r="CJ38" s="1"/>
-      <c r="CK38" s="1"/>
-      <c r="CL38" s="1"/>
-      <c r="CM38" s="1"/>
-      <c r="CN38" s="1"/>
-      <c r="CO38" s="1"/>
-      <c r="CP38" s="1"/>
-      <c r="CQ38" s="1"/>
-      <c r="CR38" s="1"/>
-      <c r="CS38" s="1"/>
-      <c r="CT38" s="1"/>
-      <c r="CU38" s="1"/>
-      <c r="CV38" s="1"/>
-      <c r="CW38" s="1"/>
-      <c r="CX38" s="1"/>
-      <c r="CY38" s="1"/>
-      <c r="CZ38" s="1"/>
-      <c r="DA38" s="1"/>
-      <c r="DB38" s="1"/>
-      <c r="DC38" s="1"/>
-      <c r="DD38" s="1"/>
-      <c r="DE38" s="1"/>
-      <c r="DF38" s="1"/>
-      <c r="DG38" s="1"/>
-      <c r="DH38" s="1"/>
-      <c r="DI38" s="1"/>
-      <c r="DJ38" s="1"/>
-      <c r="DK38" s="1"/>
-      <c r="DL38" s="1"/>
-      <c r="DM38" s="1"/>
-      <c r="DN38" s="1"/>
-      <c r="DO38" s="1"/>
-      <c r="DP38" s="1"/>
-      <c r="DQ38" s="1"/>
-      <c r="DR38" s="1"/>
-      <c r="DS38" s="1"/>
-      <c r="DT38" s="1"/>
-      <c r="DU38" s="1"/>
-      <c r="DV38" s="1"/>
-      <c r="DW38" s="1"/>
-      <c r="DX38" s="1"/>
-      <c r="DY38" s="1"/>
-      <c r="DZ38" s="1"/>
-      <c r="EA38" s="1"/>
-      <c r="EB38" s="1"/>
-      <c r="EC38" s="1"/>
-      <c r="ED38" s="1"/>
-      <c r="EE38" s="1"/>
-      <c r="EF38" s="1"/>
-      <c r="EG38" s="1"/>
-      <c r="EH38" s="1"/>
-      <c r="EI38" s="1"/>
-      <c r="EJ38" s="1"/>
-      <c r="EK38" s="1"/>
-      <c r="EL38" s="1"/>
-      <c r="EM38" s="1"/>
-      <c r="EN38" s="1"/>
-      <c r="EO38" s="1"/>
-      <c r="EP38" s="1"/>
-      <c r="EQ38" s="1"/>
-      <c r="ER38" s="1"/>
-      <c r="ES38" s="1"/>
-      <c r="ET38" s="1"/>
-      <c r="EU38" s="1"/>
-      <c r="EV38" s="1"/>
-      <c r="EW38" s="1"/>
-      <c r="EX38" s="1"/>
-      <c r="EY38" s="1"/>
-      <c r="EZ38" s="1"/>
-      <c r="FA38" s="1"/>
-      <c r="FB38" s="1"/>
-      <c r="FC38" s="1"/>
-      <c r="FD38" s="1"/>
-      <c r="FE38" s="1"/>
-      <c r="FF38" s="1"/>
-      <c r="FG38" s="1"/>
-      <c r="FH38" s="1"/>
-      <c r="FI38" s="1"/>
-      <c r="FJ38" s="1"/>
-      <c r="FK38" s="1"/>
-      <c r="FL38" s="1"/>
-      <c r="FM38" s="1"/>
-      <c r="FN38" s="1"/>
-      <c r="FO38" s="1"/>
-      <c r="FP38" s="1"/>
-      <c r="FQ38" s="1"/>
-      <c r="FR38" s="1"/>
-      <c r="FS38" s="1"/>
-      <c r="FT38" s="1"/>
-      <c r="FU38" s="1"/>
-      <c r="FV38" s="1"/>
-      <c r="FW38" s="1"/>
-      <c r="FX38" s="1"/>
-      <c r="FY38" s="1"/>
-      <c r="FZ38" s="1"/>
-      <c r="GA38" s="1"/>
-      <c r="GB38" s="1"/>
-      <c r="GC38" s="1"/>
-      <c r="GD38" s="1"/>
-      <c r="GE38" s="1"/>
-      <c r="GF38" s="1"/>
-      <c r="GG38" s="1"/>
-      <c r="GH38" s="1"/>
-      <c r="GI38" s="1"/>
-      <c r="GJ38" s="1"/>
-      <c r="GK38" s="1"/>
-      <c r="GL38" s="1"/>
-      <c r="GM38" s="1"/>
-      <c r="GN38" s="1"/>
-      <c r="GO38" s="1"/>
-      <c r="GP38" s="1"/>
-      <c r="GQ38" s="1"/>
-      <c r="GR38" s="1"/>
-      <c r="GS38" s="1"/>
-      <c r="GT38" s="1"/>
-      <c r="GU38" s="1"/>
-      <c r="GV38" s="1"/>
-      <c r="GW38" s="1"/>
-      <c r="GX38" s="1"/>
-      <c r="GY38" s="1"/>
-      <c r="GZ38" s="1"/>
-      <c r="HA38" s="1"/>
-      <c r="HB38" s="1"/>
-      <c r="HC38" s="1"/>
-      <c r="HD38" s="1"/>
-      <c r="HE38" s="1"/>
-      <c r="HF38" s="1"/>
-      <c r="HG38" s="1"/>
-      <c r="HH38" s="1"/>
-      <c r="HI38" s="1"/>
-      <c r="HJ38" s="1"/>
-      <c r="HK38" s="1"/>
-      <c r="HL38" s="1"/>
-      <c r="HM38" s="1"/>
-      <c r="HN38" s="1"/>
-      <c r="HO38" s="1"/>
-      <c r="HP38" s="1"/>
-      <c r="HQ38" s="1"/>
-      <c r="HR38" s="1"/>
-      <c r="HS38" s="1"/>
-      <c r="HT38" s="1"/>
-      <c r="HU38" s="1"/>
-      <c r="HV38" s="1"/>
-      <c r="HW38" s="1"/>
-      <c r="HX38" s="1"/>
-      <c r="HY38" s="1"/>
-      <c r="HZ38" s="1"/>
-      <c r="IA38" s="1"/>
-      <c r="IB38" s="1"/>
-      <c r="IC38" s="1"/>
-      <c r="ID38" s="1"/>
-      <c r="IE38" s="1"/>
-      <c r="IF38" s="1"/>
-      <c r="IG38" s="1"/>
-      <c r="IH38" s="1"/>
-      <c r="II38" s="1"/>
-      <c r="IJ38" s="1"/>
-      <c r="IK38" s="1"/>
-      <c r="IL38" s="1"/>
-      <c r="IM38" s="1"/>
-      <c r="IN38" s="1"/>
-      <c r="IO38" s="1"/>
-      <c r="IP38" s="1"/>
-      <c r="IQ38" s="1"/>
-      <c r="IR38" s="1"/>
-      <c r="IS38" s="1"/>
-      <c r="IT38" s="1"/>
-      <c r="IU38" s="1"/>
-      <c r="IV38" s="1"/>
-      <c r="IW38" s="1"/>
-      <c r="IX38" s="1"/>
-    </row>
-    <row r="39" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="18"/>
-      <c r="V39" s="18"/>
-      <c r="W39" s="18"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="18"/>
-      <c r="Z39" s="18"/>
-      <c r="AA39" s="18"/>
-      <c r="AB39" s="18"/>
-      <c r="AC39" s="18"/>
-      <c r="AD39" s="18"/>
-      <c r="AE39" s="18"/>
-      <c r="AF39" s="18"/>
-      <c r="AG39" s="18"/>
-      <c r="AH39" s="18"/>
-      <c r="AI39" s="18"/>
-      <c r="AJ39" s="18"/>
-      <c r="AK39" s="18"/>
-      <c r="AL39" s="18"/>
-      <c r="AM39" s="18"/>
-      <c r="AN39" s="18"/>
-      <c r="AO39" s="18"/>
-      <c r="AP39" s="18"/>
-      <c r="AQ39" s="18"/>
-      <c r="AR39" s="18"/>
-      <c r="AS39" s="19"/>
-      <c r="AT39" s="8"/>
-      <c r="AU39" s="10"/>
-      <c r="AV39" s="10"/>
-      <c r="AW39" s="10"/>
-      <c r="AX39" s="10"/>
-      <c r="AY39" s="10"/>
-      <c r="AZ39" s="10"/>
-      <c r="BA39" s="10"/>
-      <c r="BB39" s="10"/>
-      <c r="BC39" s="10"/>
-      <c r="BD39" s="10"/>
-      <c r="BE39" s="10"/>
-      <c r="BF39" s="10"/>
-      <c r="BG39" s="10"/>
-      <c r="BH39" s="10"/>
-      <c r="BI39" s="11"/>
-      <c r="BJ39" s="1"/>
-      <c r="BK39" s="1"/>
-      <c r="BL39" s="1"/>
-      <c r="BM39" s="1"/>
-      <c r="BN39" s="1"/>
-      <c r="BO39" s="1"/>
-      <c r="BP39" s="1"/>
-      <c r="BQ39" s="1"/>
-      <c r="BR39" s="1"/>
-      <c r="BS39" s="1"/>
-      <c r="BT39" s="1"/>
-      <c r="BU39" s="1"/>
-      <c r="BV39" s="1"/>
-      <c r="BW39" s="1"/>
-      <c r="BX39" s="1"/>
-      <c r="BY39" s="1"/>
-      <c r="BZ39" s="1"/>
-      <c r="CA39" s="1"/>
-      <c r="CB39" s="1"/>
-      <c r="CC39" s="1"/>
-      <c r="CD39" s="1"/>
-      <c r="CE39" s="1"/>
-      <c r="CF39" s="1"/>
-      <c r="CG39" s="1"/>
-      <c r="CH39" s="1"/>
-      <c r="CI39" s="1"/>
-      <c r="CJ39" s="1"/>
-      <c r="CK39" s="1"/>
-      <c r="CL39" s="1"/>
-      <c r="CM39" s="1"/>
-      <c r="CN39" s="1"/>
-      <c r="CO39" s="1"/>
-      <c r="CP39" s="1"/>
-      <c r="CQ39" s="1"/>
-      <c r="CR39" s="1"/>
-      <c r="CS39" s="1"/>
-      <c r="CT39" s="1"/>
-      <c r="CU39" s="1"/>
-      <c r="CV39" s="1"/>
-      <c r="CW39" s="1"/>
-      <c r="CX39" s="1"/>
-      <c r="CY39" s="1"/>
-      <c r="CZ39" s="1"/>
-      <c r="DA39" s="1"/>
-      <c r="DB39" s="1"/>
-      <c r="DC39" s="1"/>
-      <c r="DD39" s="1"/>
-      <c r="DE39" s="1"/>
-      <c r="DF39" s="1"/>
-      <c r="DG39" s="1"/>
-      <c r="DH39" s="1"/>
-      <c r="DI39" s="1"/>
-      <c r="DJ39" s="1"/>
-      <c r="DK39" s="1"/>
-      <c r="DL39" s="1"/>
-      <c r="DM39" s="1"/>
-      <c r="DN39" s="1"/>
-      <c r="DO39" s="1"/>
-      <c r="DP39" s="1"/>
-      <c r="DQ39" s="1"/>
-      <c r="DR39" s="1"/>
-      <c r="DS39" s="1"/>
-      <c r="DT39" s="1"/>
-      <c r="DU39" s="1"/>
-      <c r="DV39" s="1"/>
-      <c r="DW39" s="1"/>
-      <c r="DX39" s="1"/>
-      <c r="DY39" s="1"/>
-      <c r="DZ39" s="1"/>
-      <c r="EA39" s="1"/>
-      <c r="EB39" s="1"/>
-      <c r="EC39" s="1"/>
-      <c r="ED39" s="1"/>
-      <c r="EE39" s="1"/>
-      <c r="EF39" s="1"/>
-      <c r="EG39" s="1"/>
-      <c r="EH39" s="1"/>
-      <c r="EI39" s="1"/>
-      <c r="EJ39" s="1"/>
-      <c r="EK39" s="1"/>
-      <c r="EL39" s="1"/>
-      <c r="EM39" s="1"/>
-      <c r="EN39" s="1"/>
-      <c r="EO39" s="1"/>
-      <c r="EP39" s="1"/>
-      <c r="EQ39" s="1"/>
-      <c r="ER39" s="1"/>
-      <c r="ES39" s="1"/>
-      <c r="ET39" s="1"/>
-      <c r="EU39" s="1"/>
-      <c r="EV39" s="1"/>
-      <c r="EW39" s="1"/>
-      <c r="EX39" s="1"/>
-      <c r="EY39" s="1"/>
-      <c r="EZ39" s="1"/>
-      <c r="FA39" s="1"/>
-      <c r="FB39" s="1"/>
-      <c r="FC39" s="1"/>
-      <c r="FD39" s="1"/>
-      <c r="FE39" s="1"/>
-      <c r="FF39" s="1"/>
-      <c r="FG39" s="1"/>
-      <c r="FH39" s="1"/>
-      <c r="FI39" s="1"/>
-      <c r="FJ39" s="1"/>
-      <c r="FK39" s="1"/>
-      <c r="FL39" s="1"/>
-      <c r="FM39" s="1"/>
-      <c r="FN39" s="1"/>
-      <c r="FO39" s="1"/>
-      <c r="FP39" s="1"/>
-      <c r="FQ39" s="1"/>
-      <c r="FR39" s="1"/>
-      <c r="FS39" s="1"/>
-      <c r="FT39" s="1"/>
-      <c r="FU39" s="1"/>
-      <c r="FV39" s="1"/>
-      <c r="FW39" s="1"/>
-      <c r="FX39" s="1"/>
-      <c r="FY39" s="1"/>
-      <c r="FZ39" s="1"/>
-      <c r="GA39" s="1"/>
-      <c r="GB39" s="1"/>
-      <c r="GC39" s="1"/>
-      <c r="GD39" s="1"/>
-      <c r="GE39" s="1"/>
-      <c r="GF39" s="1"/>
-      <c r="GG39" s="1"/>
-      <c r="GH39" s="1"/>
-      <c r="GI39" s="1"/>
-      <c r="GJ39" s="1"/>
-      <c r="GK39" s="1"/>
-      <c r="GL39" s="1"/>
-      <c r="GM39" s="1"/>
-      <c r="GN39" s="1"/>
-      <c r="GO39" s="1"/>
-      <c r="GP39" s="1"/>
-      <c r="GQ39" s="1"/>
-      <c r="GR39" s="1"/>
-      <c r="GS39" s="1"/>
-      <c r="GT39" s="1"/>
-      <c r="GU39" s="1"/>
-      <c r="GV39" s="1"/>
-      <c r="GW39" s="1"/>
-      <c r="GX39" s="1"/>
-      <c r="GY39" s="1"/>
-      <c r="GZ39" s="1"/>
-      <c r="HA39" s="1"/>
-      <c r="HB39" s="1"/>
-      <c r="HC39" s="1"/>
-      <c r="HD39" s="1"/>
-      <c r="HE39" s="1"/>
-      <c r="HF39" s="1"/>
-      <c r="HG39" s="1"/>
-      <c r="HH39" s="1"/>
-      <c r="HI39" s="1"/>
-      <c r="HJ39" s="1"/>
-      <c r="HK39" s="1"/>
-      <c r="HL39" s="1"/>
-      <c r="HM39" s="1"/>
-      <c r="HN39" s="1"/>
-      <c r="HO39" s="1"/>
-      <c r="HP39" s="1"/>
-      <c r="HQ39" s="1"/>
-      <c r="HR39" s="1"/>
-      <c r="HS39" s="1"/>
-      <c r="HT39" s="1"/>
-      <c r="HU39" s="1"/>
-      <c r="HV39" s="1"/>
-      <c r="HW39" s="1"/>
-      <c r="HX39" s="1"/>
-      <c r="HY39" s="1"/>
-      <c r="HZ39" s="1"/>
-      <c r="IA39" s="1"/>
-      <c r="IB39" s="1"/>
-      <c r="IC39" s="1"/>
-      <c r="ID39" s="1"/>
-      <c r="IE39" s="1"/>
-      <c r="IF39" s="1"/>
-      <c r="IG39" s="1"/>
-      <c r="IH39" s="1"/>
-      <c r="II39" s="1"/>
-      <c r="IJ39" s="1"/>
-      <c r="IK39" s="1"/>
-      <c r="IL39" s="1"/>
-      <c r="IM39" s="1"/>
-      <c r="IN39" s="1"/>
-      <c r="IO39" s="1"/>
-      <c r="IP39" s="1"/>
-      <c r="IQ39" s="1"/>
-      <c r="IR39" s="1"/>
-      <c r="IS39" s="1"/>
-      <c r="IT39" s="1"/>
-      <c r="IU39" s="1"/>
-      <c r="IV39" s="1"/>
-      <c r="IW39" s="1"/>
-      <c r="IX39" s="1"/>
-    </row>
-    <row r="40" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="18"/>
-      <c r="W40" s="18"/>
-      <c r="X40" s="18"/>
-      <c r="Y40" s="18"/>
-      <c r="Z40" s="18"/>
-      <c r="AA40" s="18"/>
-      <c r="AB40" s="18"/>
-      <c r="AC40" s="18"/>
-      <c r="AD40" s="18"/>
-      <c r="AE40" s="18"/>
-      <c r="AF40" s="18"/>
-      <c r="AG40" s="18"/>
-      <c r="AH40" s="18"/>
-      <c r="AI40" s="18"/>
-      <c r="AJ40" s="18"/>
-      <c r="AK40" s="18"/>
-      <c r="AL40" s="18"/>
-      <c r="AM40" s="18"/>
-      <c r="AN40" s="18"/>
-      <c r="AO40" s="18"/>
-      <c r="AP40" s="18"/>
-      <c r="AQ40" s="18"/>
-      <c r="AR40" s="18"/>
-      <c r="AS40" s="19"/>
-      <c r="AT40" s="8"/>
-      <c r="AU40" s="10"/>
-      <c r="AV40" s="10"/>
-      <c r="AW40" s="10"/>
-      <c r="AX40" s="10"/>
-      <c r="AY40" s="10"/>
-      <c r="AZ40" s="10"/>
-      <c r="BA40" s="10"/>
-      <c r="BB40" s="10"/>
-      <c r="BC40" s="10"/>
-      <c r="BD40" s="10"/>
-      <c r="BE40" s="10"/>
-      <c r="BF40" s="10"/>
-      <c r="BG40" s="10"/>
-      <c r="BH40" s="10"/>
-      <c r="BI40" s="11"/>
-      <c r="BJ40" s="1"/>
-      <c r="BK40" s="1"/>
-      <c r="BL40" s="1"/>
-      <c r="BM40" s="1"/>
-      <c r="BN40" s="1"/>
-      <c r="BO40" s="1"/>
-      <c r="BP40" s="1"/>
-      <c r="BQ40" s="1"/>
-      <c r="BR40" s="1"/>
-      <c r="BS40" s="1"/>
-      <c r="BT40" s="1"/>
-      <c r="BU40" s="1"/>
-      <c r="BV40" s="1"/>
-      <c r="BW40" s="1"/>
-      <c r="BX40" s="1"/>
-      <c r="BY40" s="1"/>
-      <c r="BZ40" s="1"/>
-      <c r="CA40" s="1"/>
-      <c r="CB40" s="1"/>
-      <c r="CC40" s="1"/>
-      <c r="CD40" s="1"/>
-      <c r="CE40" s="1"/>
-      <c r="CF40" s="1"/>
-      <c r="CG40" s="1"/>
-      <c r="CH40" s="1"/>
-      <c r="CI40" s="1"/>
-      <c r="CJ40" s="1"/>
-      <c r="CK40" s="1"/>
-      <c r="CL40" s="1"/>
-      <c r="CM40" s="1"/>
-      <c r="CN40" s="1"/>
-      <c r="CO40" s="1"/>
-      <c r="CP40" s="1"/>
-      <c r="CQ40" s="1"/>
-      <c r="CR40" s="1"/>
-      <c r="CS40" s="1"/>
-      <c r="CT40" s="1"/>
-      <c r="CU40" s="1"/>
-      <c r="CV40" s="1"/>
-      <c r="CW40" s="1"/>
-      <c r="CX40" s="1"/>
-      <c r="CY40" s="1"/>
-      <c r="CZ40" s="1"/>
-      <c r="DA40" s="1"/>
-      <c r="DB40" s="1"/>
-      <c r="DC40" s="1"/>
-      <c r="DD40" s="1"/>
-      <c r="DE40" s="1"/>
-      <c r="DF40" s="1"/>
-      <c r="DG40" s="1"/>
-      <c r="DH40" s="1"/>
-      <c r="DI40" s="1"/>
-      <c r="DJ40" s="1"/>
-      <c r="DK40" s="1"/>
-      <c r="DL40" s="1"/>
-      <c r="DM40" s="1"/>
-      <c r="DN40" s="1"/>
-      <c r="DO40" s="1"/>
-      <c r="DP40" s="1"/>
-      <c r="DQ40" s="1"/>
-      <c r="DR40" s="1"/>
-      <c r="DS40" s="1"/>
-      <c r="DT40" s="1"/>
-      <c r="DU40" s="1"/>
-      <c r="DV40" s="1"/>
-      <c r="DW40" s="1"/>
-      <c r="DX40" s="1"/>
-      <c r="DY40" s="1"/>
-      <c r="DZ40" s="1"/>
-      <c r="EA40" s="1"/>
-      <c r="EB40" s="1"/>
-      <c r="EC40" s="1"/>
-      <c r="ED40" s="1"/>
-      <c r="EE40" s="1"/>
-      <c r="EF40" s="1"/>
-      <c r="EG40" s="1"/>
-      <c r="EH40" s="1"/>
-      <c r="EI40" s="1"/>
-      <c r="EJ40" s="1"/>
-      <c r="EK40" s="1"/>
-      <c r="EL40" s="1"/>
-      <c r="EM40" s="1"/>
-      <c r="EN40" s="1"/>
-      <c r="EO40" s="1"/>
-      <c r="EP40" s="1"/>
-      <c r="EQ40" s="1"/>
-      <c r="ER40" s="1"/>
-      <c r="ES40" s="1"/>
-      <c r="ET40" s="1"/>
-      <c r="EU40" s="1"/>
-      <c r="EV40" s="1"/>
-      <c r="EW40" s="1"/>
-      <c r="EX40" s="1"/>
-      <c r="EY40" s="1"/>
-      <c r="EZ40" s="1"/>
-      <c r="FA40" s="1"/>
-      <c r="FB40" s="1"/>
-      <c r="FC40" s="1"/>
-      <c r="FD40" s="1"/>
-      <c r="FE40" s="1"/>
-      <c r="FF40" s="1"/>
-      <c r="FG40" s="1"/>
-      <c r="FH40" s="1"/>
-      <c r="FI40" s="1"/>
-      <c r="FJ40" s="1"/>
-      <c r="FK40" s="1"/>
-      <c r="FL40" s="1"/>
-      <c r="FM40" s="1"/>
-      <c r="FN40" s="1"/>
-      <c r="FO40" s="1"/>
-      <c r="FP40" s="1"/>
-      <c r="FQ40" s="1"/>
-      <c r="FR40" s="1"/>
-      <c r="FS40" s="1"/>
-      <c r="FT40" s="1"/>
-      <c r="FU40" s="1"/>
-      <c r="FV40" s="1"/>
-      <c r="FW40" s="1"/>
-      <c r="FX40" s="1"/>
-      <c r="FY40" s="1"/>
-      <c r="FZ40" s="1"/>
-      <c r="GA40" s="1"/>
-      <c r="GB40" s="1"/>
-      <c r="GC40" s="1"/>
-      <c r="GD40" s="1"/>
-      <c r="GE40" s="1"/>
-      <c r="GF40" s="1"/>
-      <c r="GG40" s="1"/>
-      <c r="GH40" s="1"/>
-      <c r="GI40" s="1"/>
-      <c r="GJ40" s="1"/>
-      <c r="GK40" s="1"/>
-      <c r="GL40" s="1"/>
-      <c r="GM40" s="1"/>
-      <c r="GN40" s="1"/>
-      <c r="GO40" s="1"/>
-      <c r="GP40" s="1"/>
-      <c r="GQ40" s="1"/>
-      <c r="GR40" s="1"/>
-      <c r="GS40" s="1"/>
-      <c r="GT40" s="1"/>
-      <c r="GU40" s="1"/>
-      <c r="GV40" s="1"/>
-      <c r="GW40" s="1"/>
-      <c r="GX40" s="1"/>
-      <c r="GY40" s="1"/>
-      <c r="GZ40" s="1"/>
-      <c r="HA40" s="1"/>
-      <c r="HB40" s="1"/>
-      <c r="HC40" s="1"/>
-      <c r="HD40" s="1"/>
-      <c r="HE40" s="1"/>
-      <c r="HF40" s="1"/>
-      <c r="HG40" s="1"/>
-      <c r="HH40" s="1"/>
-      <c r="HI40" s="1"/>
-      <c r="HJ40" s="1"/>
-      <c r="HK40" s="1"/>
-      <c r="HL40" s="1"/>
-      <c r="HM40" s="1"/>
-      <c r="HN40" s="1"/>
-      <c r="HO40" s="1"/>
-      <c r="HP40" s="1"/>
-      <c r="HQ40" s="1"/>
-      <c r="HR40" s="1"/>
-      <c r="HS40" s="1"/>
-      <c r="HT40" s="1"/>
-      <c r="HU40" s="1"/>
-      <c r="HV40" s="1"/>
-      <c r="HW40" s="1"/>
-      <c r="HX40" s="1"/>
-      <c r="HY40" s="1"/>
-      <c r="HZ40" s="1"/>
-      <c r="IA40" s="1"/>
-      <c r="IB40" s="1"/>
-      <c r="IC40" s="1"/>
-      <c r="ID40" s="1"/>
-      <c r="IE40" s="1"/>
-      <c r="IF40" s="1"/>
-      <c r="IG40" s="1"/>
-      <c r="IH40" s="1"/>
-      <c r="II40" s="1"/>
-      <c r="IJ40" s="1"/>
-      <c r="IK40" s="1"/>
-      <c r="IL40" s="1"/>
-      <c r="IM40" s="1"/>
-      <c r="IN40" s="1"/>
-      <c r="IO40" s="1"/>
-      <c r="IP40" s="1"/>
-      <c r="IQ40" s="1"/>
-      <c r="IR40" s="1"/>
-      <c r="IS40" s="1"/>
-      <c r="IT40" s="1"/>
-      <c r="IU40" s="1"/>
-      <c r="IV40" s="1"/>
-      <c r="IW40" s="1"/>
-      <c r="IX40" s="1"/>
-    </row>
-    <row r="41" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
-      <c r="N41" s="13"/>
-      <c r="O41" s="13"/>
-      <c r="P41" s="13"/>
-      <c r="Q41" s="13"/>
-      <c r="R41" s="13"/>
-      <c r="S41" s="13"/>
-      <c r="T41" s="13"/>
-      <c r="U41" s="13"/>
-      <c r="V41" s="13"/>
-      <c r="W41" s="13"/>
-      <c r="X41" s="13"/>
-      <c r="Y41" s="13"/>
-      <c r="Z41" s="13"/>
-      <c r="AA41" s="13"/>
-      <c r="AB41" s="13"/>
-      <c r="AC41" s="13"/>
-      <c r="AD41" s="13"/>
-      <c r="AE41" s="13"/>
-      <c r="AF41" s="13"/>
-      <c r="AG41" s="13"/>
-      <c r="AH41" s="13"/>
-      <c r="AI41" s="13"/>
-      <c r="AJ41" s="13"/>
-      <c r="AK41" s="13"/>
-      <c r="AL41" s="13"/>
-      <c r="AM41" s="13"/>
-      <c r="AN41" s="13"/>
-      <c r="AO41" s="13"/>
-      <c r="AP41" s="13"/>
-      <c r="AQ41" s="13"/>
-      <c r="AR41" s="13"/>
-      <c r="AS41" s="13"/>
-      <c r="AT41" s="13"/>
-      <c r="AU41" s="13"/>
-      <c r="AV41" s="13"/>
-      <c r="AW41" s="13"/>
-      <c r="AX41" s="13"/>
-      <c r="AY41" s="13"/>
-      <c r="AZ41" s="13"/>
-      <c r="BA41" s="13"/>
-      <c r="BB41" s="13"/>
-      <c r="BC41" s="13"/>
-      <c r="BD41" s="13"/>
-      <c r="BE41" s="13"/>
-      <c r="BF41" s="13"/>
-      <c r="BG41" s="13"/>
-      <c r="BH41" s="13"/>
-      <c r="BI41" s="13"/>
-      <c r="BJ41" s="1"/>
-      <c r="BK41" s="1"/>
-      <c r="BL41" s="1"/>
-      <c r="BM41" s="1"/>
-      <c r="BN41" s="1"/>
-      <c r="BO41" s="1"/>
-      <c r="BP41" s="1"/>
-      <c r="BQ41" s="1"/>
-      <c r="BR41" s="1"/>
-      <c r="BS41" s="1"/>
-      <c r="BT41" s="1"/>
-      <c r="BU41" s="1"/>
-      <c r="BV41" s="1"/>
-      <c r="BW41" s="1"/>
-      <c r="BX41" s="1"/>
-      <c r="BY41" s="1"/>
-      <c r="BZ41" s="1"/>
-      <c r="CA41" s="1"/>
-      <c r="CB41" s="1"/>
-      <c r="CC41" s="1"/>
-      <c r="CD41" s="1"/>
-      <c r="CE41" s="1"/>
-      <c r="CF41" s="1"/>
-      <c r="CG41" s="1"/>
-      <c r="CH41" s="1"/>
-      <c r="CI41" s="1"/>
-      <c r="CJ41" s="1"/>
-      <c r="CK41" s="1"/>
-      <c r="CL41" s="1"/>
-      <c r="CM41" s="1"/>
-      <c r="CN41" s="1"/>
-      <c r="CO41" s="1"/>
-      <c r="CP41" s="1"/>
-      <c r="CQ41" s="1"/>
-      <c r="CR41" s="1"/>
-      <c r="CS41" s="1"/>
-      <c r="CT41" s="1"/>
-      <c r="CU41" s="1"/>
-      <c r="CV41" s="1"/>
-      <c r="CW41" s="1"/>
-      <c r="CX41" s="1"/>
-      <c r="CY41" s="1"/>
-      <c r="CZ41" s="1"/>
-      <c r="DA41" s="1"/>
-      <c r="DB41" s="1"/>
-      <c r="DC41" s="1"/>
-      <c r="DD41" s="1"/>
-      <c r="DE41" s="1"/>
-      <c r="DF41" s="1"/>
-      <c r="DG41" s="1"/>
-      <c r="DH41" s="1"/>
-      <c r="DI41" s="1"/>
-      <c r="DJ41" s="1"/>
-      <c r="DK41" s="1"/>
-      <c r="DL41" s="1"/>
-      <c r="DM41" s="1"/>
-      <c r="DN41" s="1"/>
-      <c r="DO41" s="1"/>
-      <c r="DP41" s="1"/>
-      <c r="DQ41" s="1"/>
-      <c r="DR41" s="1"/>
-      <c r="DS41" s="1"/>
-      <c r="DT41" s="1"/>
-      <c r="DU41" s="1"/>
-      <c r="DV41" s="1"/>
-      <c r="DW41" s="1"/>
-      <c r="DX41" s="1"/>
-      <c r="DY41" s="1"/>
-      <c r="DZ41" s="1"/>
-      <c r="EA41" s="1"/>
-      <c r="EB41" s="1"/>
-      <c r="EC41" s="1"/>
-      <c r="ED41" s="1"/>
-      <c r="EE41" s="1"/>
-      <c r="EF41" s="1"/>
-      <c r="EG41" s="1"/>
-      <c r="EH41" s="1"/>
-      <c r="EI41" s="1"/>
-      <c r="EJ41" s="1"/>
-      <c r="EK41" s="1"/>
-      <c r="EL41" s="1"/>
-      <c r="EM41" s="1"/>
-      <c r="EN41" s="1"/>
-      <c r="EO41" s="1"/>
-      <c r="EP41" s="1"/>
-      <c r="EQ41" s="1"/>
-      <c r="ER41" s="1"/>
-      <c r="ES41" s="1"/>
-      <c r="ET41" s="1"/>
-      <c r="EU41" s="1"/>
-      <c r="EV41" s="1"/>
-      <c r="EW41" s="1"/>
-      <c r="EX41" s="1"/>
-      <c r="EY41" s="1"/>
-      <c r="EZ41" s="1"/>
-      <c r="FA41" s="1"/>
-      <c r="FB41" s="1"/>
-      <c r="FC41" s="1"/>
-      <c r="FD41" s="1"/>
-      <c r="FE41" s="1"/>
-      <c r="FF41" s="1"/>
-      <c r="FG41" s="1"/>
-      <c r="FH41" s="1"/>
-      <c r="FI41" s="1"/>
-      <c r="FJ41" s="1"/>
-      <c r="FK41" s="1"/>
-      <c r="FL41" s="1"/>
-      <c r="FM41" s="1"/>
-      <c r="FN41" s="1"/>
-      <c r="FO41" s="1"/>
-      <c r="FP41" s="1"/>
-      <c r="FQ41" s="1"/>
-      <c r="FR41" s="1"/>
-      <c r="FS41" s="1"/>
-      <c r="FT41" s="1"/>
-      <c r="FU41" s="1"/>
-      <c r="FV41" s="1"/>
-      <c r="FW41" s="1"/>
-      <c r="FX41" s="1"/>
-      <c r="FY41" s="1"/>
-      <c r="FZ41" s="1"/>
-      <c r="GA41" s="1"/>
-      <c r="GB41" s="1"/>
-      <c r="GC41" s="1"/>
-      <c r="GD41" s="1"/>
-      <c r="GE41" s="1"/>
-      <c r="GF41" s="1"/>
-      <c r="GG41" s="1"/>
-      <c r="GH41" s="1"/>
-      <c r="GI41" s="1"/>
-      <c r="GJ41" s="1"/>
-      <c r="GK41" s="1"/>
-      <c r="GL41" s="1"/>
-      <c r="GM41" s="1"/>
-      <c r="GN41" s="1"/>
-      <c r="GO41" s="1"/>
-      <c r="GP41" s="1"/>
-      <c r="GQ41" s="1"/>
-      <c r="GR41" s="1"/>
-      <c r="GS41" s="1"/>
-      <c r="GT41" s="1"/>
-      <c r="GU41" s="1"/>
-      <c r="GV41" s="1"/>
-      <c r="GW41" s="1"/>
-      <c r="GX41" s="1"/>
-      <c r="GY41" s="1"/>
-      <c r="GZ41" s="1"/>
-      <c r="HA41" s="1"/>
-      <c r="HB41" s="1"/>
-      <c r="HC41" s="1"/>
-      <c r="HD41" s="1"/>
-      <c r="HE41" s="1"/>
-      <c r="HF41" s="1"/>
-      <c r="HG41" s="1"/>
-      <c r="HH41" s="1"/>
-      <c r="HI41" s="1"/>
-      <c r="HJ41" s="1"/>
-      <c r="HK41" s="1"/>
-      <c r="HL41" s="1"/>
-      <c r="HM41" s="1"/>
-      <c r="HN41" s="1"/>
-      <c r="HO41" s="1"/>
-      <c r="HP41" s="1"/>
-      <c r="HQ41" s="1"/>
-      <c r="HR41" s="1"/>
-      <c r="HS41" s="1"/>
-      <c r="HT41" s="1"/>
-      <c r="HU41" s="1"/>
-      <c r="HV41" s="1"/>
-      <c r="HW41" s="1"/>
-      <c r="HX41" s="1"/>
-      <c r="HY41" s="1"/>
-      <c r="HZ41" s="1"/>
-      <c r="IA41" s="1"/>
-      <c r="IB41" s="1"/>
-      <c r="IC41" s="1"/>
-      <c r="ID41" s="1"/>
-      <c r="IE41" s="1"/>
-      <c r="IF41" s="1"/>
-      <c r="IG41" s="1"/>
-      <c r="IH41" s="1"/>
-      <c r="II41" s="1"/>
-      <c r="IJ41" s="1"/>
-      <c r="IK41" s="1"/>
-      <c r="IL41" s="1"/>
-      <c r="IM41" s="1"/>
-      <c r="IN41" s="1"/>
-      <c r="IO41" s="1"/>
-      <c r="IP41" s="1"/>
-      <c r="IQ41" s="1"/>
-      <c r="IR41" s="1"/>
-      <c r="IS41" s="1"/>
-      <c r="IT41" s="1"/>
-      <c r="IU41" s="1"/>
-      <c r="IV41" s="1"/>
-      <c r="IW41" s="1"/>
-      <c r="IX41" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="P12:AS12"/>
+    <mergeCell ref="AT12:BI12"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="P10:AD10"/>
+    <mergeCell ref="AE10:BI10"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:O8"/>
+    <mergeCell ref="P8:AD8"/>
+    <mergeCell ref="AE8:BI8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
     <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:BI4"/>
@@ -13336,25 +9920,11 @@
     <mergeCell ref="AT1:AZ1"/>
     <mergeCell ref="BA1:BC1"/>
     <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:O8"/>
-    <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="AE8:BI8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:O9"/>
-    <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="P12:AS12"/>
-    <mergeCell ref="AT12:BI12"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="P10:AD10"/>
-    <mergeCell ref="AE10:BI10"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
@@ -13370,12 +9940,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F5656D937027614D93C88AB71AE3D10C" ma:contentTypeVersion="2" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="b60c200d0ae5f270a77b0ce61d313f15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="75fae816-41bf-471e-909f-5205fc9f8b57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="893732230ae29545b6addaf499a489b1" ns2:_="">
     <xsd:import namespace="75fae816-41bf-471e-909f-5205fc9f8b57"/>
@@ -13507,6 +10071,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -13517,15 +10087,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7560E91F-1ABF-4BEF-A078-A8FA5AD9AA18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13543,6 +10104,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
   <ds:schemaRefs>

--- a/03_内部設計/022-クラス仕様書/util/SplitKeywordUtilのクラス仕様書.xlsx
+++ b/03_内部設計/022-クラス仕様書/util/SplitKeywordUtilのクラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AD484F-9949-4BFE-896D-25627C6204CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E221ABF-4762-4467-A0A4-25F3C98E8D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">クラス仕様!$A$1:$BI$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（splitKeyword）'!$A$1:$BI$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（splitKeyword）'!$A$1:$BI$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -331,22 +331,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4) 正規表現と一致した文字列を、文字列型のリストに格納する。</t>
-    <rPh sb="3" eb="5">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>モジレツ</t>
-    </rPh>
-    <rPh sb="17" eb="21">
-      <t>モジレツガタ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>カクノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.1) String型のArrayList、resultを作成する。</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -370,25 +354,6 @@
     <t>4.1) 正規表現と一致するとき、while文で繰り返し処理を行う。</t>
     <rPh sb="22" eb="23">
       <t>ブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>4.1.1) Matcherクラスのgroupメソッドで一致した文字列を取り出し、resultに追加する。</t>
-    <rPh sb="28" eb="30">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="32" eb="35">
-      <t>モジレツ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -430,6 +395,96 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>4.1.1) 下記メソッドを順次呼び出し、戻り値をString型の変数、strに代入する。</t>
+    <rPh sb="7" eb="9">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ジュンジヨ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ダイニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.1.2) strをresultに追加する。</t>
+    <rPh sb="18" eb="20">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.1.1.1) Matcherクラスのgroupメソッドを呼び出す。</t>
+    <rPh sb="30" eb="31">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.1.1.2) Stringクラスのreplaceメソッドを呼び出し、引数に"%"、"\\%"を渡す。</t>
+    <rPh sb="31" eb="32">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.1.1.3) Stringクラスのreplaceメソッドを呼び出し、引数に"_"、"\\_"を渡す。</t>
+    <rPh sb="49" eb="50">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4) 正規表現と一致した文字列から特殊文字を置換し、文字列型のリストに格納する。</t>
+    <rPh sb="3" eb="5">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>トクシュモジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>チカン</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>モジレツガタ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -439,7 +494,7 @@
     <numFmt numFmtId="176" formatCode="[$-411]yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -469,6 +524,13 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10.5"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
@@ -630,7 +692,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -673,9 +735,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -704,34 +763,52 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -745,23 +822,14 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1127,71 +1195,71 @@
       <c r="J1" s="29"/>
       <c r="K1" s="29"/>
       <c r="L1" s="29"/>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="25" t="s">
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="24" t="s">
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="25" t="s">
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="25"/>
-      <c r="AL1" s="25"/>
-      <c r="AM1" s="25"/>
-      <c r="AN1" s="25"/>
-      <c r="AO1" s="25"/>
-      <c r="AP1" s="25"/>
-      <c r="AQ1" s="24" t="s">
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="30"/>
+      <c r="AJ1" s="30"/>
+      <c r="AK1" s="30"/>
+      <c r="AL1" s="30"/>
+      <c r="AM1" s="30"/>
+      <c r="AN1" s="30"/>
+      <c r="AO1" s="30"/>
+      <c r="AP1" s="30"/>
+      <c r="AQ1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="24"/>
-      <c r="AS1" s="24"/>
-      <c r="AT1" s="25" t="s">
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+      <c r="AT1" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" s="25"/>
-      <c r="AV1" s="25"/>
-      <c r="AW1" s="25"/>
-      <c r="AX1" s="25"/>
-      <c r="AY1" s="25"/>
-      <c r="AZ1" s="25"/>
-      <c r="BA1" s="24" t="s">
+      <c r="AU1" s="30"/>
+      <c r="AV1" s="30"/>
+      <c r="AW1" s="30"/>
+      <c r="AX1" s="30"/>
+      <c r="AY1" s="30"/>
+      <c r="AZ1" s="30"/>
+      <c r="BA1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="24"/>
-      <c r="BC1" s="24"/>
-      <c r="BD1" s="26">
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="31"/>
+      <c r="BD1" s="28">
         <v>45553</v>
       </c>
-      <c r="BE1" s="26"/>
-      <c r="BF1" s="26"/>
-      <c r="BG1" s="26"/>
-      <c r="BH1" s="26"/>
-      <c r="BI1" s="26"/>
+      <c r="BE1" s="28"/>
+      <c r="BF1" s="28"/>
+      <c r="BG1" s="28"/>
+      <c r="BH1" s="28"/>
+      <c r="BI1" s="28"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1403,70 +1471,70 @@
       <c r="J2" s="29"/>
       <c r="K2" s="29"/>
       <c r="L2" s="29"/>
-      <c r="M2" s="24" t="s">
+      <c r="M2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="24" t="s">
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="25" t="str">
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="30" t="str">
         <f>G5</f>
         <v>SplitKeywordUtil</v>
       </c>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="25"/>
-      <c r="AP2" s="25"/>
-      <c r="AQ2" s="24" t="s">
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="24"/>
-      <c r="AS2" s="24"/>
-      <c r="AT2" s="25" t="s">
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31"/>
+      <c r="AT2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="AU2" s="25"/>
-      <c r="AV2" s="25"/>
-      <c r="AW2" s="25"/>
-      <c r="AX2" s="25"/>
-      <c r="AY2" s="25"/>
-      <c r="AZ2" s="25"/>
-      <c r="BA2" s="24" t="s">
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="24"/>
-      <c r="BC2" s="24"/>
-      <c r="BD2" s="26">
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="31"/>
+      <c r="BD2" s="28">
         <v>45566</v>
       </c>
-      <c r="BE2" s="26"/>
-      <c r="BF2" s="26"/>
-      <c r="BG2" s="26"/>
-      <c r="BH2" s="26"/>
-      <c r="BI2" s="26"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -1729,942 +1797,927 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="28" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
+      <c r="AM4" s="27"/>
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
+      <c r="AQ4" s="27"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="27"/>
+      <c r="AT4" s="27"/>
+      <c r="AU4" s="27"/>
+      <c r="AV4" s="27"/>
+      <c r="AW4" s="27"/>
+      <c r="AX4" s="27"/>
+      <c r="AY4" s="27"/>
+      <c r="AZ4" s="27"/>
+      <c r="BA4" s="27"/>
+      <c r="BB4" s="27"/>
+      <c r="BC4" s="27"/>
+      <c r="BD4" s="27"/>
+      <c r="BE4" s="27"/>
+      <c r="BF4" s="27"/>
+      <c r="BG4" s="27"/>
+      <c r="BH4" s="27"/>
+      <c r="BI4" s="27"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="28" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="27"/>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="27"/>
+      <c r="AK5" s="27"/>
+      <c r="AL5" s="27"/>
+      <c r="AM5" s="27"/>
+      <c r="AN5" s="27"/>
+      <c r="AO5" s="27"/>
+      <c r="AP5" s="27"/>
+      <c r="AQ5" s="27"/>
+      <c r="AR5" s="27"/>
+      <c r="AS5" s="27"/>
+      <c r="AT5" s="27"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="27"/>
+      <c r="AW5" s="27"/>
+      <c r="AX5" s="27"/>
+      <c r="AY5" s="27"/>
+      <c r="AZ5" s="27"/>
+      <c r="BA5" s="27"/>
+      <c r="BB5" s="27"/>
+      <c r="BC5" s="27"/>
+      <c r="BD5" s="27"/>
+      <c r="BE5" s="27"/>
+      <c r="BF5" s="27"/>
+      <c r="BG5" s="27"/>
+      <c r="BH5" s="27"/>
+      <c r="BI5" s="27"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="28" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="27" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="27"/>
+      <c r="AC6" s="27"/>
+      <c r="AD6" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="AE6" s="27"/>
-      <c r="AF6" s="27"/>
-      <c r="AG6" s="27"/>
-      <c r="AH6" s="27"/>
-      <c r="AI6" s="27"/>
-      <c r="AJ6" s="28" t="s">
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="AK6" s="28"/>
-      <c r="AL6" s="28"/>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="28"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="28"/>
-      <c r="AT6" s="28"/>
-      <c r="AU6" s="28"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="28"/>
-      <c r="BA6" s="28"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="28"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="28"/>
-      <c r="BH6" s="28"/>
-      <c r="BI6" s="28"/>
+      <c r="AK6" s="27"/>
+      <c r="AL6" s="27"/>
+      <c r="AM6" s="27"/>
+      <c r="AN6" s="27"/>
+      <c r="AO6" s="27"/>
+      <c r="AP6" s="27"/>
+      <c r="AQ6" s="27"/>
+      <c r="AR6" s="27"/>
+      <c r="AS6" s="27"/>
+      <c r="AT6" s="27"/>
+      <c r="AU6" s="27"/>
+      <c r="AV6" s="27"/>
+      <c r="AW6" s="27"/>
+      <c r="AX6" s="27"/>
+      <c r="AY6" s="27"/>
+      <c r="AZ6" s="27"/>
+      <c r="BA6" s="27"/>
+      <c r="BB6" s="27"/>
+      <c r="BC6" s="27"/>
+      <c r="BD6" s="27"/>
+      <c r="BE6" s="27"/>
+      <c r="BF6" s="27"/>
+      <c r="BG6" s="27"/>
+      <c r="BH6" s="27"/>
+      <c r="BI6" s="27"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="27" t="s">
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="V8" s="27"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="27"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
-      <c r="AA8" s="27"/>
-      <c r="AB8" s="27"/>
-      <c r="AC8" s="27"/>
-      <c r="AD8" s="27"/>
-      <c r="AE8" s="27" t="s">
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="AF8" s="27"/>
-      <c r="AG8" s="27"/>
-      <c r="AH8" s="27"/>
-      <c r="AI8" s="27"/>
-      <c r="AJ8" s="27"/>
-      <c r="AK8" s="27"/>
-      <c r="AL8" s="27"/>
-      <c r="AM8" s="27"/>
-      <c r="AN8" s="27"/>
-      <c r="AO8" s="27" t="s">
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="25"/>
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="25"/>
+      <c r="AJ8" s="25"/>
+      <c r="AK8" s="25"/>
+      <c r="AL8" s="25"/>
+      <c r="AM8" s="25"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="AP8" s="27"/>
-      <c r="AQ8" s="27"/>
-      <c r="AR8" s="27"/>
-      <c r="AS8" s="27"/>
-      <c r="AT8" s="27"/>
-      <c r="AU8" s="27"/>
-      <c r="AV8" s="27"/>
-      <c r="AW8" s="27"/>
-      <c r="AX8" s="27"/>
-      <c r="AY8" s="27"/>
-      <c r="AZ8" s="27"/>
-      <c r="BA8" s="27"/>
-      <c r="BB8" s="27"/>
-      <c r="BC8" s="27"/>
-      <c r="BD8" s="27"/>
-      <c r="BE8" s="27"/>
-      <c r="BF8" s="27"/>
-      <c r="BG8" s="27"/>
-      <c r="BH8" s="27"/>
-      <c r="BI8" s="27"/>
+      <c r="AP8" s="25"/>
+      <c r="AQ8" s="25"/>
+      <c r="AR8" s="25"/>
+      <c r="AS8" s="25"/>
+      <c r="AT8" s="25"/>
+      <c r="AU8" s="25"/>
+      <c r="AV8" s="25"/>
+      <c r="AW8" s="25"/>
+      <c r="AX8" s="25"/>
+      <c r="AY8" s="25"/>
+      <c r="AZ8" s="25"/>
+      <c r="BA8" s="25"/>
+      <c r="BB8" s="25"/>
+      <c r="BC8" s="25"/>
+      <c r="BD8" s="25"/>
+      <c r="BE8" s="25"/>
+      <c r="BF8" s="25"/>
+      <c r="BG8" s="25"/>
+      <c r="BH8" s="25"/>
+      <c r="BI8" s="25"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="31"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="31"/>
-      <c r="Z9" s="31"/>
-      <c r="AA9" s="31"/>
-      <c r="AB9" s="31"/>
-      <c r="AC9" s="31"/>
-      <c r="AD9" s="31"/>
-      <c r="AE9" s="31"/>
-      <c r="AF9" s="31"/>
-      <c r="AG9" s="31"/>
-      <c r="AH9" s="31"/>
-      <c r="AI9" s="31"/>
-      <c r="AJ9" s="31"/>
-      <c r="AK9" s="31"/>
-      <c r="AL9" s="31"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="31"/>
-      <c r="AO9" s="31"/>
-      <c r="AP9" s="31"/>
-      <c r="AQ9" s="31"/>
-      <c r="AR9" s="31"/>
-      <c r="AS9" s="31"/>
-      <c r="AT9" s="31"/>
-      <c r="AU9" s="31"/>
-      <c r="AV9" s="31"/>
-      <c r="AW9" s="31"/>
-      <c r="AX9" s="31"/>
-      <c r="AY9" s="31"/>
-      <c r="AZ9" s="31"/>
-      <c r="BA9" s="31"/>
-      <c r="BB9" s="31"/>
-      <c r="BC9" s="31"/>
-      <c r="BD9" s="31"/>
-      <c r="BE9" s="31"/>
-      <c r="BF9" s="31"/>
-      <c r="BG9" s="31"/>
-      <c r="BH9" s="31"/>
-      <c r="BI9" s="31"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="26"/>
+      <c r="AA9" s="26"/>
+      <c r="AB9" s="26"/>
+      <c r="AC9" s="26"/>
+      <c r="AD9" s="26"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="26"/>
+      <c r="AJ9" s="26"/>
+      <c r="AK9" s="26"/>
+      <c r="AL9" s="26"/>
+      <c r="AM9" s="26"/>
+      <c r="AN9" s="26"/>
+      <c r="AO9" s="26"/>
+      <c r="AP9" s="26"/>
+      <c r="AQ9" s="26"/>
+      <c r="AR9" s="26"/>
+      <c r="AS9" s="26"/>
+      <c r="AT9" s="26"/>
+      <c r="AU9" s="26"/>
+      <c r="AV9" s="26"/>
+      <c r="AW9" s="26"/>
+      <c r="AX9" s="26"/>
+      <c r="AY9" s="26"/>
+      <c r="AZ9" s="26"/>
+      <c r="BA9" s="26"/>
+      <c r="BB9" s="26"/>
+      <c r="BC9" s="26"/>
+      <c r="BD9" s="26"/>
+      <c r="BE9" s="26"/>
+      <c r="BF9" s="26"/>
+      <c r="BG9" s="26"/>
+      <c r="BH9" s="26"/>
+      <c r="BI9" s="26"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="31"/>
-      <c r="AA10" s="31"/>
-      <c r="AB10" s="31"/>
-      <c r="AC10" s="31"/>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="31"/>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="31"/>
-      <c r="AI10" s="31"/>
-      <c r="AJ10" s="31"/>
-      <c r="AK10" s="31"/>
-      <c r="AL10" s="31"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="31"/>
-      <c r="AO10" s="31"/>
-      <c r="AP10" s="31"/>
-      <c r="AQ10" s="31"/>
-      <c r="AR10" s="31"/>
-      <c r="AS10" s="31"/>
-      <c r="AT10" s="31"/>
-      <c r="AU10" s="31"/>
-      <c r="AV10" s="31"/>
-      <c r="AW10" s="31"/>
-      <c r="AX10" s="31"/>
-      <c r="AY10" s="31"/>
-      <c r="AZ10" s="31"/>
-      <c r="BA10" s="31"/>
-      <c r="BB10" s="31"/>
-      <c r="BC10" s="31"/>
-      <c r="BD10" s="31"/>
-      <c r="BE10" s="31"/>
-      <c r="BF10" s="31"/>
-      <c r="BG10" s="31"/>
-      <c r="BH10" s="31"/>
-      <c r="BI10" s="31"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="26"/>
+      <c r="X10" s="26"/>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="26"/>
+      <c r="AA10" s="26"/>
+      <c r="AB10" s="26"/>
+      <c r="AC10" s="26"/>
+      <c r="AD10" s="26"/>
+      <c r="AE10" s="26"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="26"/>
+      <c r="AJ10" s="26"/>
+      <c r="AK10" s="26"/>
+      <c r="AL10" s="26"/>
+      <c r="AM10" s="26"/>
+      <c r="AN10" s="26"/>
+      <c r="AO10" s="26"/>
+      <c r="AP10" s="26"/>
+      <c r="AQ10" s="26"/>
+      <c r="AR10" s="26"/>
+      <c r="AS10" s="26"/>
+      <c r="AT10" s="26"/>
+      <c r="AU10" s="26"/>
+      <c r="AV10" s="26"/>
+      <c r="AW10" s="26"/>
+      <c r="AX10" s="26"/>
+      <c r="AY10" s="26"/>
+      <c r="AZ10" s="26"/>
+      <c r="BA10" s="26"/>
+      <c r="BB10" s="26"/>
+      <c r="BC10" s="26"/>
+      <c r="BD10" s="26"/>
+      <c r="BE10" s="26"/>
+      <c r="BF10" s="26"/>
+      <c r="BG10" s="26"/>
+      <c r="BH10" s="26"/>
+      <c r="BI10" s="26"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="31"/>
-      <c r="T11" s="31"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="31"/>
-      <c r="W11" s="31"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="31"/>
-      <c r="Z11" s="31"/>
-      <c r="AA11" s="31"/>
-      <c r="AB11" s="31"/>
-      <c r="AC11" s="31"/>
-      <c r="AD11" s="31"/>
-      <c r="AE11" s="31"/>
-      <c r="AF11" s="31"/>
-      <c r="AG11" s="31"/>
-      <c r="AH11" s="31"/>
-      <c r="AI11" s="31"/>
-      <c r="AJ11" s="31"/>
-      <c r="AK11" s="31"/>
-      <c r="AL11" s="31"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="31"/>
-      <c r="AO11" s="31"/>
-      <c r="AP11" s="31"/>
-      <c r="AQ11" s="31"/>
-      <c r="AR11" s="31"/>
-      <c r="AS11" s="31"/>
-      <c r="AT11" s="31"/>
-      <c r="AU11" s="31"/>
-      <c r="AV11" s="31"/>
-      <c r="AW11" s="31"/>
-      <c r="AX11" s="31"/>
-      <c r="AY11" s="31"/>
-      <c r="AZ11" s="31"/>
-      <c r="BA11" s="31"/>
-      <c r="BB11" s="31"/>
-      <c r="BC11" s="31"/>
-      <c r="BD11" s="31"/>
-      <c r="BE11" s="31"/>
-      <c r="BF11" s="31"/>
-      <c r="BG11" s="31"/>
-      <c r="BH11" s="31"/>
-      <c r="BI11" s="31"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="26"/>
+      <c r="S11" s="26"/>
+      <c r="T11" s="26"/>
+      <c r="U11" s="26"/>
+      <c r="V11" s="26"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="26"/>
+      <c r="Y11" s="26"/>
+      <c r="Z11" s="26"/>
+      <c r="AA11" s="26"/>
+      <c r="AB11" s="26"/>
+      <c r="AC11" s="26"/>
+      <c r="AD11" s="26"/>
+      <c r="AE11" s="26"/>
+      <c r="AF11" s="26"/>
+      <c r="AG11" s="26"/>
+      <c r="AH11" s="26"/>
+      <c r="AI11" s="26"/>
+      <c r="AJ11" s="26"/>
+      <c r="AK11" s="26"/>
+      <c r="AL11" s="26"/>
+      <c r="AM11" s="26"/>
+      <c r="AN11" s="26"/>
+      <c r="AO11" s="26"/>
+      <c r="AP11" s="26"/>
+      <c r="AQ11" s="26"/>
+      <c r="AR11" s="26"/>
+      <c r="AS11" s="26"/>
+      <c r="AT11" s="26"/>
+      <c r="AU11" s="26"/>
+      <c r="AV11" s="26"/>
+      <c r="AW11" s="26"/>
+      <c r="AX11" s="26"/>
+      <c r="AY11" s="26"/>
+      <c r="AZ11" s="26"/>
+      <c r="BA11" s="26"/>
+      <c r="BB11" s="26"/>
+      <c r="BC11" s="26"/>
+      <c r="BD11" s="26"/>
+      <c r="BE11" s="26"/>
+      <c r="BF11" s="26"/>
+      <c r="BG11" s="26"/>
+      <c r="BH11" s="26"/>
+      <c r="BI11" s="26"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="27"/>
-      <c r="AC13" s="27"/>
-      <c r="AD13" s="27"/>
-      <c r="AE13" s="27"/>
-      <c r="AF13" s="27"/>
-      <c r="AG13" s="27"/>
-      <c r="AH13" s="27"/>
-      <c r="AI13" s="27"/>
-      <c r="AJ13" s="27"/>
-      <c r="AK13" s="27"/>
-      <c r="AL13" s="27"/>
-      <c r="AM13" s="27"/>
-      <c r="AN13" s="27"/>
-      <c r="AO13" s="27"/>
-      <c r="AP13" s="27"/>
-      <c r="AQ13" s="27"/>
-      <c r="AR13" s="27"/>
-      <c r="AS13" s="27"/>
-      <c r="AT13" s="27"/>
-      <c r="AU13" s="27"/>
-      <c r="AV13" s="27"/>
-      <c r="AW13" s="27"/>
-      <c r="AX13" s="27"/>
-      <c r="AY13" s="27"/>
-      <c r="AZ13" s="27"/>
-      <c r="BA13" s="27"/>
-      <c r="BB13" s="27"/>
-      <c r="BC13" s="27"/>
-      <c r="BD13" s="27"/>
-      <c r="BE13" s="27"/>
-      <c r="BF13" s="27"/>
-      <c r="BG13" s="27"/>
-      <c r="BH13" s="27"/>
-      <c r="BI13" s="27"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
+      <c r="AH13" s="25"/>
+      <c r="AI13" s="25"/>
+      <c r="AJ13" s="25"/>
+      <c r="AK13" s="25"/>
+      <c r="AL13" s="25"/>
+      <c r="AM13" s="25"/>
+      <c r="AN13" s="25"/>
+      <c r="AO13" s="25"/>
+      <c r="AP13" s="25"/>
+      <c r="AQ13" s="25"/>
+      <c r="AR13" s="25"/>
+      <c r="AS13" s="25"/>
+      <c r="AT13" s="25"/>
+      <c r="AU13" s="25"/>
+      <c r="AV13" s="25"/>
+      <c r="AW13" s="25"/>
+      <c r="AX13" s="25"/>
+      <c r="AY13" s="25"/>
+      <c r="AZ13" s="25"/>
+      <c r="BA13" s="25"/>
+      <c r="BB13" s="25"/>
+      <c r="BC13" s="25"/>
+      <c r="BD13" s="25"/>
+      <c r="BE13" s="25"/>
+      <c r="BF13" s="25"/>
+      <c r="BG13" s="25"/>
+      <c r="BH13" s="25"/>
+      <c r="BI13" s="25"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
-      <c r="Z14" s="33"/>
-      <c r="AA14" s="33"/>
-      <c r="AB14" s="33"/>
-      <c r="AC14" s="33"/>
-      <c r="AD14" s="33"/>
-      <c r="AE14" s="33"/>
-      <c r="AF14" s="33"/>
-      <c r="AG14" s="33"/>
-      <c r="AH14" s="33"/>
-      <c r="AI14" s="33"/>
-      <c r="AJ14" s="33"/>
-      <c r="AK14" s="33"/>
-      <c r="AL14" s="33"/>
-      <c r="AM14" s="33"/>
-      <c r="AN14" s="33"/>
-      <c r="AO14" s="33"/>
-      <c r="AP14" s="33"/>
-      <c r="AQ14" s="33"/>
-      <c r="AR14" s="33"/>
-      <c r="AS14" s="33"/>
-      <c r="AT14" s="33"/>
-      <c r="AU14" s="33"/>
-      <c r="AV14" s="33"/>
-      <c r="AW14" s="33"/>
-      <c r="AX14" s="33"/>
-      <c r="AY14" s="33"/>
-      <c r="AZ14" s="33"/>
-      <c r="BA14" s="33"/>
-      <c r="BB14" s="33"/>
-      <c r="BC14" s="33"/>
-      <c r="BD14" s="33"/>
-      <c r="BE14" s="33"/>
-      <c r="BF14" s="33"/>
-      <c r="BG14" s="33"/>
-      <c r="BH14" s="33"/>
-      <c r="BI14" s="33"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
+      <c r="AH14" s="24"/>
+      <c r="AI14" s="24"/>
+      <c r="AJ14" s="24"/>
+      <c r="AK14" s="24"/>
+      <c r="AL14" s="24"/>
+      <c r="AM14" s="24"/>
+      <c r="AN14" s="24"/>
+      <c r="AO14" s="24"/>
+      <c r="AP14" s="24"/>
+      <c r="AQ14" s="24"/>
+      <c r="AR14" s="24"/>
+      <c r="AS14" s="24"/>
+      <c r="AT14" s="24"/>
+      <c r="AU14" s="24"/>
+      <c r="AV14" s="24"/>
+      <c r="AW14" s="24"/>
+      <c r="AX14" s="24"/>
+      <c r="AY14" s="24"/>
+      <c r="AZ14" s="24"/>
+      <c r="BA14" s="24"/>
+      <c r="BB14" s="24"/>
+      <c r="BC14" s="24"/>
+      <c r="BD14" s="24"/>
+      <c r="BE14" s="24"/>
+      <c r="BF14" s="24"/>
+      <c r="BG14" s="24"/>
+      <c r="BH14" s="24"/>
+      <c r="BI14" s="24"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="33"/>
-      <c r="AE15" s="33"/>
-      <c r="AF15" s="33"/>
-      <c r="AG15" s="33"/>
-      <c r="AH15" s="33"/>
-      <c r="AI15" s="33"/>
-      <c r="AJ15" s="33"/>
-      <c r="AK15" s="33"/>
-      <c r="AL15" s="33"/>
-      <c r="AM15" s="33"/>
-      <c r="AN15" s="33"/>
-      <c r="AO15" s="33"/>
-      <c r="AP15" s="33"/>
-      <c r="AQ15" s="33"/>
-      <c r="AR15" s="33"/>
-      <c r="AS15" s="33"/>
-      <c r="AT15" s="33"/>
-      <c r="AU15" s="33"/>
-      <c r="AV15" s="33"/>
-      <c r="AW15" s="33"/>
-      <c r="AX15" s="33"/>
-      <c r="AY15" s="33"/>
-      <c r="AZ15" s="33"/>
-      <c r="BA15" s="33"/>
-      <c r="BB15" s="33"/>
-      <c r="BC15" s="33"/>
-      <c r="BD15" s="33"/>
-      <c r="BE15" s="33"/>
-      <c r="BF15" s="33"/>
-      <c r="BG15" s="33"/>
-      <c r="BH15" s="33"/>
-      <c r="BI15" s="33"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="24"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="24"/>
+      <c r="X15" s="24"/>
+      <c r="Y15" s="24"/>
+      <c r="Z15" s="24"/>
+      <c r="AA15" s="24"/>
+      <c r="AB15" s="24"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="24"/>
+      <c r="AE15" s="24"/>
+      <c r="AF15" s="24"/>
+      <c r="AG15" s="24"/>
+      <c r="AH15" s="24"/>
+      <c r="AI15" s="24"/>
+      <c r="AJ15" s="24"/>
+      <c r="AK15" s="24"/>
+      <c r="AL15" s="24"/>
+      <c r="AM15" s="24"/>
+      <c r="AN15" s="24"/>
+      <c r="AO15" s="24"/>
+      <c r="AP15" s="24"/>
+      <c r="AQ15" s="24"/>
+      <c r="AR15" s="24"/>
+      <c r="AS15" s="24"/>
+      <c r="AT15" s="24"/>
+      <c r="AU15" s="24"/>
+      <c r="AV15" s="24"/>
+      <c r="AW15" s="24"/>
+      <c r="AX15" s="24"/>
+      <c r="AY15" s="24"/>
+      <c r="AZ15" s="24"/>
+      <c r="BA15" s="24"/>
+      <c r="BB15" s="24"/>
+      <c r="BC15" s="24"/>
+      <c r="BD15" s="24"/>
+      <c r="BE15" s="24"/>
+      <c r="BF15" s="24"/>
+      <c r="BG15" s="24"/>
+      <c r="BH15" s="24"/>
+      <c r="BI15" s="24"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="33"/>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="33"/>
-      <c r="AD16" s="33"/>
-      <c r="AE16" s="33"/>
-      <c r="AF16" s="33"/>
-      <c r="AG16" s="33"/>
-      <c r="AH16" s="33"/>
-      <c r="AI16" s="33"/>
-      <c r="AJ16" s="33"/>
-      <c r="AK16" s="33"/>
-      <c r="AL16" s="33"/>
-      <c r="AM16" s="33"/>
-      <c r="AN16" s="33"/>
-      <c r="AO16" s="33"/>
-      <c r="AP16" s="33"/>
-      <c r="AQ16" s="33"/>
-      <c r="AR16" s="33"/>
-      <c r="AS16" s="33"/>
-      <c r="AT16" s="33"/>
-      <c r="AU16" s="33"/>
-      <c r="AV16" s="33"/>
-      <c r="AW16" s="33"/>
-      <c r="AX16" s="33"/>
-      <c r="AY16" s="33"/>
-      <c r="AZ16" s="33"/>
-      <c r="BA16" s="33"/>
-      <c r="BB16" s="33"/>
-      <c r="BC16" s="33"/>
-      <c r="BD16" s="33"/>
-      <c r="BE16" s="33"/>
-      <c r="BF16" s="33"/>
-      <c r="BG16" s="33"/>
-      <c r="BH16" s="33"/>
-      <c r="BI16" s="33"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
+      <c r="AH16" s="24"/>
+      <c r="AI16" s="24"/>
+      <c r="AJ16" s="24"/>
+      <c r="AK16" s="24"/>
+      <c r="AL16" s="24"/>
+      <c r="AM16" s="24"/>
+      <c r="AN16" s="24"/>
+      <c r="AO16" s="24"/>
+      <c r="AP16" s="24"/>
+      <c r="AQ16" s="24"/>
+      <c r="AR16" s="24"/>
+      <c r="AS16" s="24"/>
+      <c r="AT16" s="24"/>
+      <c r="AU16" s="24"/>
+      <c r="AV16" s="24"/>
+      <c r="AW16" s="24"/>
+      <c r="AX16" s="24"/>
+      <c r="AY16" s="24"/>
+      <c r="AZ16" s="24"/>
+      <c r="BA16" s="24"/>
+      <c r="BB16" s="24"/>
+      <c r="BC16" s="24"/>
+      <c r="BD16" s="24"/>
+      <c r="BE16" s="24"/>
+      <c r="BF16" s="24"/>
+      <c r="BG16" s="24"/>
+      <c r="BH16" s="24"/>
+      <c r="BI16" s="24"/>
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="33"/>
-      <c r="V17" s="33"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="33"/>
-      <c r="Y17" s="33"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="33"/>
-      <c r="AB17" s="33"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="33"/>
-      <c r="AE17" s="33"/>
-      <c r="AF17" s="33"/>
-      <c r="AG17" s="33"/>
-      <c r="AH17" s="33"/>
-      <c r="AI17" s="33"/>
-      <c r="AJ17" s="33"/>
-      <c r="AK17" s="33"/>
-      <c r="AL17" s="33"/>
-      <c r="AM17" s="33"/>
-      <c r="AN17" s="33"/>
-      <c r="AO17" s="33"/>
-      <c r="AP17" s="33"/>
-      <c r="AQ17" s="33"/>
-      <c r="AR17" s="33"/>
-      <c r="AS17" s="33"/>
-      <c r="AT17" s="33"/>
-      <c r="AU17" s="33"/>
-      <c r="AV17" s="33"/>
-      <c r="AW17" s="33"/>
-      <c r="AX17" s="33"/>
-      <c r="AY17" s="33"/>
-      <c r="AZ17" s="33"/>
-      <c r="BA17" s="33"/>
-      <c r="BB17" s="33"/>
-      <c r="BC17" s="33"/>
-      <c r="BD17" s="33"/>
-      <c r="BE17" s="33"/>
-      <c r="BF17" s="33"/>
-      <c r="BG17" s="33"/>
-      <c r="BH17" s="33"/>
-      <c r="BI17" s="33"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
+      <c r="AD17" s="24"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="24"/>
+      <c r="AG17" s="24"/>
+      <c r="AH17" s="24"/>
+      <c r="AI17" s="24"/>
+      <c r="AJ17" s="24"/>
+      <c r="AK17" s="24"/>
+      <c r="AL17" s="24"/>
+      <c r="AM17" s="24"/>
+      <c r="AN17" s="24"/>
+      <c r="AO17" s="24"/>
+      <c r="AP17" s="24"/>
+      <c r="AQ17" s="24"/>
+      <c r="AR17" s="24"/>
+      <c r="AS17" s="24"/>
+      <c r="AT17" s="24"/>
+      <c r="AU17" s="24"/>
+      <c r="AV17" s="24"/>
+      <c r="AW17" s="24"/>
+      <c r="AX17" s="24"/>
+      <c r="AY17" s="24"/>
+      <c r="AZ17" s="24"/>
+      <c r="BA17" s="24"/>
+      <c r="BB17" s="24"/>
+      <c r="BC17" s="24"/>
+      <c r="BD17" s="24"/>
+      <c r="BE17" s="24"/>
+      <c r="BF17" s="24"/>
+      <c r="BG17" s="24"/>
+      <c r="BH17" s="24"/>
+      <c r="BI17" s="24"/>
     </row>
     <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="33"/>
-      <c r="V18" s="33"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="33"/>
-      <c r="Y18" s="33"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="33"/>
-      <c r="AB18" s="33"/>
-      <c r="AC18" s="33"/>
-      <c r="AD18" s="33"/>
-      <c r="AE18" s="33"/>
-      <c r="AF18" s="33"/>
-      <c r="AG18" s="33"/>
-      <c r="AH18" s="33"/>
-      <c r="AI18" s="33"/>
-      <c r="AJ18" s="33"/>
-      <c r="AK18" s="33"/>
-      <c r="AL18" s="33"/>
-      <c r="AM18" s="33"/>
-      <c r="AN18" s="33"/>
-      <c r="AO18" s="33"/>
-      <c r="AP18" s="33"/>
-      <c r="AQ18" s="33"/>
-      <c r="AR18" s="33"/>
-      <c r="AS18" s="33"/>
-      <c r="AT18" s="33"/>
-      <c r="AU18" s="33"/>
-      <c r="AV18" s="33"/>
-      <c r="AW18" s="33"/>
-      <c r="AX18" s="33"/>
-      <c r="AY18" s="33"/>
-      <c r="AZ18" s="33"/>
-      <c r="BA18" s="33"/>
-      <c r="BB18" s="33"/>
-      <c r="BC18" s="33"/>
-      <c r="BD18" s="33"/>
-      <c r="BE18" s="33"/>
-      <c r="BF18" s="33"/>
-      <c r="BG18" s="33"/>
-      <c r="BH18" s="33"/>
-      <c r="BI18" s="33"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="24"/>
+      <c r="U18" s="24"/>
+      <c r="V18" s="24"/>
+      <c r="W18" s="24"/>
+      <c r="X18" s="24"/>
+      <c r="Y18" s="24"/>
+      <c r="Z18" s="24"/>
+      <c r="AA18" s="24"/>
+      <c r="AB18" s="24"/>
+      <c r="AC18" s="24"/>
+      <c r="AD18" s="24"/>
+      <c r="AE18" s="24"/>
+      <c r="AF18" s="24"/>
+      <c r="AG18" s="24"/>
+      <c r="AH18" s="24"/>
+      <c r="AI18" s="24"/>
+      <c r="AJ18" s="24"/>
+      <c r="AK18" s="24"/>
+      <c r="AL18" s="24"/>
+      <c r="AM18" s="24"/>
+      <c r="AN18" s="24"/>
+      <c r="AO18" s="24"/>
+      <c r="AP18" s="24"/>
+      <c r="AQ18" s="24"/>
+      <c r="AR18" s="24"/>
+      <c r="AS18" s="24"/>
+      <c r="AT18" s="24"/>
+      <c r="AU18" s="24"/>
+      <c r="AV18" s="24"/>
+      <c r="AW18" s="24"/>
+      <c r="AX18" s="24"/>
+      <c r="AY18" s="24"/>
+      <c r="AZ18" s="24"/>
+      <c r="BA18" s="24"/>
+      <c r="BB18" s="24"/>
+      <c r="BC18" s="24"/>
+      <c r="BD18" s="24"/>
+      <c r="BE18" s="24"/>
+      <c r="BF18" s="24"/>
+      <c r="BG18" s="24"/>
+      <c r="BH18" s="24"/>
+      <c r="BI18" s="24"/>
     </row>
     <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="33"/>
-      <c r="V19" s="33"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="33"/>
-      <c r="Y19" s="33"/>
-      <c r="Z19" s="33"/>
-      <c r="AA19" s="33"/>
-      <c r="AB19" s="33"/>
-      <c r="AC19" s="33"/>
-      <c r="AD19" s="33"/>
-      <c r="AE19" s="33"/>
-      <c r="AF19" s="33"/>
-      <c r="AG19" s="33"/>
-      <c r="AH19" s="33"/>
-      <c r="AI19" s="33"/>
-      <c r="AJ19" s="33"/>
-      <c r="AK19" s="33"/>
-      <c r="AL19" s="33"/>
-      <c r="AM19" s="33"/>
-      <c r="AN19" s="33"/>
-      <c r="AO19" s="33"/>
-      <c r="AP19" s="33"/>
-      <c r="AQ19" s="33"/>
-      <c r="AR19" s="33"/>
-      <c r="AS19" s="33"/>
-      <c r="AT19" s="33"/>
-      <c r="AU19" s="33"/>
-      <c r="AV19" s="33"/>
-      <c r="AW19" s="33"/>
-      <c r="AX19" s="33"/>
-      <c r="AY19" s="33"/>
-      <c r="AZ19" s="33"/>
-      <c r="BA19" s="33"/>
-      <c r="BB19" s="33"/>
-      <c r="BC19" s="33"/>
-      <c r="BD19" s="33"/>
-      <c r="BE19" s="33"/>
-      <c r="BF19" s="33"/>
-      <c r="BG19" s="33"/>
-      <c r="BH19" s="33"/>
-      <c r="BI19" s="33"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="24"/>
+      <c r="V19" s="24"/>
+      <c r="W19" s="24"/>
+      <c r="X19" s="24"/>
+      <c r="Y19" s="24"/>
+      <c r="Z19" s="24"/>
+      <c r="AA19" s="24"/>
+      <c r="AB19" s="24"/>
+      <c r="AC19" s="24"/>
+      <c r="AD19" s="24"/>
+      <c r="AE19" s="24"/>
+      <c r="AF19" s="24"/>
+      <c r="AG19" s="24"/>
+      <c r="AH19" s="24"/>
+      <c r="AI19" s="24"/>
+      <c r="AJ19" s="24"/>
+      <c r="AK19" s="24"/>
+      <c r="AL19" s="24"/>
+      <c r="AM19" s="24"/>
+      <c r="AN19" s="24"/>
+      <c r="AO19" s="24"/>
+      <c r="AP19" s="24"/>
+      <c r="AQ19" s="24"/>
+      <c r="AR19" s="24"/>
+      <c r="AS19" s="24"/>
+      <c r="AT19" s="24"/>
+      <c r="AU19" s="24"/>
+      <c r="AV19" s="24"/>
+      <c r="AW19" s="24"/>
+      <c r="AX19" s="24"/>
+      <c r="AY19" s="24"/>
+      <c r="AZ19" s="24"/>
+      <c r="BA19" s="24"/>
+      <c r="BB19" s="24"/>
+      <c r="BC19" s="24"/>
+      <c r="BD19" s="24"/>
+      <c r="BE19" s="24"/>
+      <c r="BF19" s="24"/>
+      <c r="BG19" s="24"/>
+      <c r="BH19" s="24"/>
+      <c r="BI19" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A14:BI19"/>
-    <mergeCell ref="A13:BI13"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K10:T10"/>
-    <mergeCell ref="U10:AD10"/>
-    <mergeCell ref="AE10:AN10"/>
-    <mergeCell ref="AO10:BI10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="K11:T11"/>
-    <mergeCell ref="U11:AD11"/>
-    <mergeCell ref="AE11:AN11"/>
-    <mergeCell ref="AO11:BI11"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:T8"/>
-    <mergeCell ref="U8:AD8"/>
-    <mergeCell ref="AE8:AN8"/>
-    <mergeCell ref="AO8:BI8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="K9:T9"/>
-    <mergeCell ref="U9:AD9"/>
-    <mergeCell ref="AE9:AN9"/>
-    <mergeCell ref="AO9:BI9"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
@@ -2681,14 +2734,29 @@
     <mergeCell ref="R2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="K9:T9"/>
+    <mergeCell ref="U9:AD9"/>
+    <mergeCell ref="AE9:AN9"/>
+    <mergeCell ref="AO9:BI9"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="U8:AD8"/>
+    <mergeCell ref="AE8:AN8"/>
+    <mergeCell ref="AO8:BI8"/>
+    <mergeCell ref="A14:BI19"/>
+    <mergeCell ref="A13:BI13"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="U10:AD10"/>
+    <mergeCell ref="AE10:AN10"/>
+    <mergeCell ref="AO10:BI10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="K11:T11"/>
+    <mergeCell ref="U11:AD11"/>
+    <mergeCell ref="AE11:AN11"/>
+    <mergeCell ref="AO11:BI11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -2700,7 +2768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IX28"/>
+  <dimension ref="A1:IX32"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="2.453125" style="2"/>
@@ -2721,72 +2789,72 @@
       <c r="J1" s="29"/>
       <c r="K1" s="29"/>
       <c r="L1" s="29"/>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="25" t="s">
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="24" t="s">
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="25" t="str">
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="30" t="str">
         <f>クラス仕様!AE1</f>
         <v>商品検索</v>
       </c>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="25"/>
-      <c r="AL1" s="25"/>
-      <c r="AM1" s="25"/>
-      <c r="AN1" s="25"/>
-      <c r="AO1" s="25"/>
-      <c r="AP1" s="25"/>
-      <c r="AQ1" s="24" t="s">
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="30"/>
+      <c r="AJ1" s="30"/>
+      <c r="AK1" s="30"/>
+      <c r="AL1" s="30"/>
+      <c r="AM1" s="30"/>
+      <c r="AN1" s="30"/>
+      <c r="AO1" s="30"/>
+      <c r="AP1" s="30"/>
+      <c r="AQ1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="24"/>
-      <c r="AS1" s="24"/>
-      <c r="AT1" s="25" t="s">
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+      <c r="AT1" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" s="25"/>
-      <c r="AV1" s="25"/>
-      <c r="AW1" s="25"/>
-      <c r="AX1" s="25"/>
-      <c r="AY1" s="25"/>
-      <c r="AZ1" s="25"/>
-      <c r="BA1" s="24" t="s">
+      <c r="AU1" s="30"/>
+      <c r="AV1" s="30"/>
+      <c r="AW1" s="30"/>
+      <c r="AX1" s="30"/>
+      <c r="AY1" s="30"/>
+      <c r="AZ1" s="30"/>
+      <c r="BA1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="24"/>
-      <c r="BC1" s="24"/>
-      <c r="BD1" s="37">
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="31"/>
+      <c r="BD1" s="42">
         <v>45553</v>
       </c>
-      <c r="BE1" s="37"/>
-      <c r="BF1" s="37"/>
-      <c r="BG1" s="37"/>
-      <c r="BH1" s="37"/>
-      <c r="BI1" s="37"/>
+      <c r="BE1" s="42"/>
+      <c r="BF1" s="42"/>
+      <c r="BG1" s="42"/>
+      <c r="BH1" s="42"/>
+      <c r="BI1" s="42"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -2998,70 +3066,70 @@
       <c r="J2" s="29"/>
       <c r="K2" s="29"/>
       <c r="L2" s="29"/>
-      <c r="M2" s="24" t="s">
+      <c r="M2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="24" t="s">
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="25" t="str">
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="30" t="str">
         <f>クラス仕様!G5</f>
         <v>SplitKeywordUtil</v>
       </c>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="25"/>
-      <c r="AP2" s="25"/>
-      <c r="AQ2" s="24" t="s">
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="24"/>
-      <c r="AS2" s="24"/>
-      <c r="AT2" s="25" t="s">
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31"/>
+      <c r="AT2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="AU2" s="25"/>
-      <c r="AV2" s="25"/>
-      <c r="AW2" s="25"/>
-      <c r="AX2" s="25"/>
-      <c r="AY2" s="25"/>
-      <c r="AZ2" s="25"/>
-      <c r="BA2" s="24" t="s">
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="24"/>
-      <c r="BC2" s="24"/>
-      <c r="BD2" s="34">
-        <v>45583</v>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="31"/>
+      <c r="BD2" s="39">
+        <v>45587</v>
       </c>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="36"/>
+      <c r="BE2" s="40"/>
+      <c r="BF2" s="40"/>
+      <c r="BG2" s="40"/>
+      <c r="BH2" s="40"/>
+      <c r="BI2" s="41"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3324,71 +3392,71 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="28" t="s">
-        <v>58</v>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="27" t="s">
+        <v>56</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
+      <c r="AM4" s="27"/>
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
+      <c r="AQ4" s="27"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="27"/>
+      <c r="AT4" s="27"/>
+      <c r="AU4" s="27"/>
+      <c r="AV4" s="27"/>
+      <c r="AW4" s="27"/>
+      <c r="AX4" s="27"/>
+      <c r="AY4" s="27"/>
+      <c r="AZ4" s="27"/>
+      <c r="BA4" s="27"/>
+      <c r="BB4" s="27"/>
+      <c r="BC4" s="27"/>
+      <c r="BD4" s="27"/>
+      <c r="BE4" s="27"/>
+      <c r="BF4" s="27"/>
+      <c r="BG4" s="27"/>
+      <c r="BH4" s="27"/>
+      <c r="BI4" s="27"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -3588,71 +3656,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="28" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="27"/>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="27"/>
+      <c r="AK5" s="27"/>
+      <c r="AL5" s="27"/>
+      <c r="AM5" s="27"/>
+      <c r="AN5" s="27"/>
+      <c r="AO5" s="27"/>
+      <c r="AP5" s="27"/>
+      <c r="AQ5" s="27"/>
+      <c r="AR5" s="27"/>
+      <c r="AS5" s="27"/>
+      <c r="AT5" s="27"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="27"/>
+      <c r="AW5" s="27"/>
+      <c r="AX5" s="27"/>
+      <c r="AY5" s="27"/>
+      <c r="AZ5" s="27"/>
+      <c r="BA5" s="27"/>
+      <c r="BB5" s="27"/>
+      <c r="BC5" s="27"/>
+      <c r="BD5" s="27"/>
+      <c r="BE5" s="27"/>
+      <c r="BF5" s="27"/>
+      <c r="BG5" s="27"/>
+      <c r="BH5" s="27"/>
+      <c r="BI5" s="27"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -4112,75 +4180,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41" t="s">
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="41"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="41"/>
-      <c r="AB7" s="41"/>
-      <c r="AC7" s="41"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="41" t="s">
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="35"/>
+      <c r="AC7" s="35"/>
+      <c r="AD7" s="35"/>
+      <c r="AE7" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="41"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="41"/>
-      <c r="AK7" s="41"/>
-      <c r="AL7" s="41"/>
-      <c r="AM7" s="41"/>
-      <c r="AN7" s="41"/>
-      <c r="AO7" s="41"/>
-      <c r="AP7" s="41"/>
-      <c r="AQ7" s="41"/>
-      <c r="AR7" s="41"/>
-      <c r="AS7" s="41"/>
-      <c r="AT7" s="41"/>
-      <c r="AU7" s="41"/>
-      <c r="AV7" s="41"/>
-      <c r="AW7" s="41"/>
-      <c r="AX7" s="41"/>
-      <c r="AY7" s="41"/>
-      <c r="AZ7" s="41"/>
-      <c r="BA7" s="41"/>
-      <c r="BB7" s="41"/>
-      <c r="BC7" s="41"/>
-      <c r="BD7" s="41"/>
-      <c r="BE7" s="41"/>
-      <c r="BF7" s="41"/>
-      <c r="BG7" s="41"/>
-      <c r="BH7" s="41"/>
-      <c r="BI7" s="41"/>
+      <c r="AF7" s="35"/>
+      <c r="AG7" s="35"/>
+      <c r="AH7" s="35"/>
+      <c r="AI7" s="35"/>
+      <c r="AJ7" s="35"/>
+      <c r="AK7" s="35"/>
+      <c r="AL7" s="35"/>
+      <c r="AM7" s="35"/>
+      <c r="AN7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="35"/>
+      <c r="AQ7" s="35"/>
+      <c r="AR7" s="35"/>
+      <c r="AS7" s="35"/>
+      <c r="AT7" s="35"/>
+      <c r="AU7" s="35"/>
+      <c r="AV7" s="35"/>
+      <c r="AW7" s="35"/>
+      <c r="AX7" s="35"/>
+      <c r="AY7" s="35"/>
+      <c r="AZ7" s="35"/>
+      <c r="BA7" s="35"/>
+      <c r="BB7" s="35"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="35"/>
+      <c r="BE7" s="35"/>
+      <c r="BF7" s="35"/>
+      <c r="BG7" s="35"/>
+      <c r="BH7" s="35"/>
+      <c r="BI7" s="35"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -4380,75 +4448,75 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="38" t="s">
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="38" t="s">
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="39"/>
-      <c r="T8" s="39"/>
-      <c r="U8" s="39"/>
-      <c r="V8" s="39"/>
-      <c r="W8" s="39"/>
-      <c r="X8" s="39"/>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="39"/>
-      <c r="AA8" s="39"/>
-      <c r="AB8" s="39"/>
-      <c r="AC8" s="39"/>
-      <c r="AD8" s="40"/>
-      <c r="AE8" s="38" t="s">
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="37"/>
+      <c r="W8" s="37"/>
+      <c r="X8" s="37"/>
+      <c r="Y8" s="37"/>
+      <c r="Z8" s="37"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="37"/>
+      <c r="AC8" s="37"/>
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="AF8" s="39"/>
-      <c r="AG8" s="39"/>
-      <c r="AH8" s="39"/>
-      <c r="AI8" s="39"/>
-      <c r="AJ8" s="39"/>
-      <c r="AK8" s="39"/>
-      <c r="AL8" s="39"/>
-      <c r="AM8" s="39"/>
-      <c r="AN8" s="39"/>
-      <c r="AO8" s="39"/>
-      <c r="AP8" s="39"/>
-      <c r="AQ8" s="39"/>
-      <c r="AR8" s="39"/>
-      <c r="AS8" s="39"/>
-      <c r="AT8" s="39"/>
-      <c r="AU8" s="39"/>
-      <c r="AV8" s="39"/>
-      <c r="AW8" s="39"/>
-      <c r="AX8" s="39"/>
-      <c r="AY8" s="39"/>
-      <c r="AZ8" s="39"/>
-      <c r="BA8" s="39"/>
-      <c r="BB8" s="39"/>
-      <c r="BC8" s="39"/>
-      <c r="BD8" s="39"/>
-      <c r="BE8" s="39"/>
-      <c r="BF8" s="39"/>
-      <c r="BG8" s="39"/>
-      <c r="BH8" s="39"/>
-      <c r="BI8" s="40"/>
+      <c r="AF8" s="37"/>
+      <c r="AG8" s="37"/>
+      <c r="AH8" s="37"/>
+      <c r="AI8" s="37"/>
+      <c r="AJ8" s="37"/>
+      <c r="AK8" s="37"/>
+      <c r="AL8" s="37"/>
+      <c r="AM8" s="37"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="37"/>
+      <c r="AP8" s="37"/>
+      <c r="AQ8" s="37"/>
+      <c r="AR8" s="37"/>
+      <c r="AS8" s="37"/>
+      <c r="AT8" s="37"/>
+      <c r="AU8" s="37"/>
+      <c r="AV8" s="37"/>
+      <c r="AW8" s="37"/>
+      <c r="AX8" s="37"/>
+      <c r="AY8" s="37"/>
+      <c r="AZ8" s="37"/>
+      <c r="BA8" s="37"/>
+      <c r="BB8" s="37"/>
+      <c r="BC8" s="37"/>
+      <c r="BD8" s="37"/>
+      <c r="BE8" s="37"/>
+      <c r="BF8" s="37"/>
+      <c r="BG8" s="37"/>
+      <c r="BH8" s="37"/>
+      <c r="BI8" s="38"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -4648,75 +4716,75 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43" t="s">
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43" t="s">
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="43"/>
-      <c r="X9" s="43"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="43"/>
-      <c r="AA9" s="43"/>
-      <c r="AB9" s="43"/>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="43"/>
-      <c r="AE9" s="43" t="s">
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="34"/>
+      <c r="V9" s="34"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="34"/>
+      <c r="Y9" s="34"/>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="34"/>
+      <c r="AB9" s="34"/>
+      <c r="AC9" s="34"/>
+      <c r="AD9" s="34"/>
+      <c r="AE9" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="AF9" s="43"/>
-      <c r="AG9" s="43"/>
-      <c r="AH9" s="43"/>
-      <c r="AI9" s="43"/>
-      <c r="AJ9" s="43"/>
-      <c r="AK9" s="43"/>
-      <c r="AL9" s="43"/>
-      <c r="AM9" s="43"/>
-      <c r="AN9" s="43"/>
-      <c r="AO9" s="43"/>
-      <c r="AP9" s="43"/>
-      <c r="AQ9" s="43"/>
-      <c r="AR9" s="43"/>
-      <c r="AS9" s="43"/>
-      <c r="AT9" s="43"/>
-      <c r="AU9" s="43"/>
-      <c r="AV9" s="43"/>
-      <c r="AW9" s="43"/>
-      <c r="AX9" s="43"/>
-      <c r="AY9" s="43"/>
-      <c r="AZ9" s="43"/>
-      <c r="BA9" s="43"/>
-      <c r="BB9" s="43"/>
-      <c r="BC9" s="43"/>
-      <c r="BD9" s="43"/>
-      <c r="BE9" s="43"/>
-      <c r="BF9" s="43"/>
-      <c r="BG9" s="43"/>
-      <c r="BH9" s="43"/>
-      <c r="BI9" s="43"/>
+      <c r="AF9" s="34"/>
+      <c r="AG9" s="34"/>
+      <c r="AH9" s="34"/>
+      <c r="AI9" s="34"/>
+      <c r="AJ9" s="34"/>
+      <c r="AK9" s="34"/>
+      <c r="AL9" s="34"/>
+      <c r="AM9" s="34"/>
+      <c r="AN9" s="34"/>
+      <c r="AO9" s="34"/>
+      <c r="AP9" s="34"/>
+      <c r="AQ9" s="34"/>
+      <c r="AR9" s="34"/>
+      <c r="AS9" s="34"/>
+      <c r="AT9" s="34"/>
+      <c r="AU9" s="34"/>
+      <c r="AV9" s="34"/>
+      <c r="AW9" s="34"/>
+      <c r="AX9" s="34"/>
+      <c r="AY9" s="34"/>
+      <c r="AZ9" s="34"/>
+      <c r="BA9" s="34"/>
+      <c r="BB9" s="34"/>
+      <c r="BC9" s="34"/>
+      <c r="BD9" s="34"/>
+      <c r="BE9" s="34"/>
+      <c r="BF9" s="34"/>
+      <c r="BG9" s="34"/>
+      <c r="BH9" s="34"/>
+      <c r="BI9" s="34"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -4916,67 +4984,67 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="31"/>
-      <c r="AA10" s="31"/>
-      <c r="AB10" s="31"/>
-      <c r="AC10" s="31"/>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="31"/>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="31"/>
-      <c r="AI10" s="31"/>
-      <c r="AJ10" s="31"/>
-      <c r="AK10" s="31"/>
-      <c r="AL10" s="31"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="31"/>
-      <c r="AO10" s="31"/>
-      <c r="AP10" s="31"/>
-      <c r="AQ10" s="31"/>
-      <c r="AR10" s="31"/>
-      <c r="AS10" s="31"/>
-      <c r="AT10" s="31"/>
-      <c r="AU10" s="31"/>
-      <c r="AV10" s="31"/>
-      <c r="AW10" s="31"/>
-      <c r="AX10" s="31"/>
-      <c r="AY10" s="31"/>
-      <c r="AZ10" s="31"/>
-      <c r="BA10" s="31"/>
-      <c r="BB10" s="31"/>
-      <c r="BC10" s="31"/>
-      <c r="BD10" s="31"/>
-      <c r="BE10" s="31"/>
-      <c r="BF10" s="31"/>
-      <c r="BG10" s="31"/>
-      <c r="BH10" s="31"/>
-      <c r="BI10" s="31"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="26"/>
+      <c r="X10" s="26"/>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="26"/>
+      <c r="AA10" s="26"/>
+      <c r="AB10" s="26"/>
+      <c r="AC10" s="26"/>
+      <c r="AD10" s="26"/>
+      <c r="AE10" s="26"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="26"/>
+      <c r="AJ10" s="26"/>
+      <c r="AK10" s="26"/>
+      <c r="AL10" s="26"/>
+      <c r="AM10" s="26"/>
+      <c r="AN10" s="26"/>
+      <c r="AO10" s="26"/>
+      <c r="AP10" s="26"/>
+      <c r="AQ10" s="26"/>
+      <c r="AR10" s="26"/>
+      <c r="AS10" s="26"/>
+      <c r="AT10" s="26"/>
+      <c r="AU10" s="26"/>
+      <c r="AV10" s="26"/>
+      <c r="AW10" s="26"/>
+      <c r="AX10" s="26"/>
+      <c r="AY10" s="26"/>
+      <c r="AZ10" s="26"/>
+      <c r="BA10" s="26"/>
+      <c r="BB10" s="26"/>
+      <c r="BC10" s="26"/>
+      <c r="BD10" s="26"/>
+      <c r="BE10" s="26"/>
+      <c r="BF10" s="26"/>
+      <c r="BG10" s="26"/>
+      <c r="BH10" s="26"/>
+      <c r="BI10" s="26"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -5436,73 +5504,73 @@
       <c r="IX11" s="1"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41" t="s">
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="41"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="41"/>
-      <c r="Y12" s="41"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="41"/>
-      <c r="AB12" s="41"/>
-      <c r="AC12" s="41"/>
-      <c r="AD12" s="41"/>
-      <c r="AE12" s="41"/>
-      <c r="AF12" s="41"/>
-      <c r="AG12" s="41"/>
-      <c r="AH12" s="41"/>
-      <c r="AI12" s="41"/>
-      <c r="AJ12" s="41"/>
-      <c r="AK12" s="41"/>
-      <c r="AL12" s="41"/>
-      <c r="AM12" s="41"/>
-      <c r="AN12" s="41"/>
-      <c r="AO12" s="41"/>
-      <c r="AP12" s="41"/>
-      <c r="AQ12" s="41"/>
-      <c r="AR12" s="41"/>
-      <c r="AS12" s="41"/>
-      <c r="AT12" s="41" t="s">
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="35"/>
+      <c r="AC12" s="35"/>
+      <c r="AD12" s="35"/>
+      <c r="AE12" s="35"/>
+      <c r="AF12" s="35"/>
+      <c r="AG12" s="35"/>
+      <c r="AH12" s="35"/>
+      <c r="AI12" s="35"/>
+      <c r="AJ12" s="35"/>
+      <c r="AK12" s="35"/>
+      <c r="AL12" s="35"/>
+      <c r="AM12" s="35"/>
+      <c r="AN12" s="35"/>
+      <c r="AO12" s="35"/>
+      <c r="AP12" s="35"/>
+      <c r="AQ12" s="35"/>
+      <c r="AR12" s="35"/>
+      <c r="AS12" s="35"/>
+      <c r="AT12" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="AU12" s="41"/>
-      <c r="AV12" s="41"/>
-      <c r="AW12" s="41"/>
-      <c r="AX12" s="41"/>
-      <c r="AY12" s="41"/>
-      <c r="AZ12" s="41"/>
-      <c r="BA12" s="41"/>
-      <c r="BB12" s="41"/>
-      <c r="BC12" s="41"/>
-      <c r="BD12" s="41"/>
-      <c r="BE12" s="41"/>
-      <c r="BF12" s="41"/>
-      <c r="BG12" s="41"/>
-      <c r="BH12" s="41"/>
-      <c r="BI12" s="41"/>
+      <c r="AU12" s="35"/>
+      <c r="AV12" s="35"/>
+      <c r="AW12" s="35"/>
+      <c r="AX12" s="35"/>
+      <c r="AY12" s="35"/>
+      <c r="AZ12" s="35"/>
+      <c r="BA12" s="35"/>
+      <c r="BB12" s="35"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="35"/>
+      <c r="BE12" s="35"/>
+      <c r="BF12" s="35"/>
+      <c r="BG12" s="35"/>
+      <c r="BH12" s="35"/>
+      <c r="BI12" s="35"/>
       <c r="BJ12" s="1"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
@@ -5717,38 +5785,38 @@
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="7"/>
-      <c r="P13" s="14" t="s">
-        <v>54</v>
+      <c r="P13" s="45" t="s">
+        <v>53</v>
       </c>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="15"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="15"/>
-      <c r="AE13" s="15"/>
-      <c r="AF13" s="15"/>
-      <c r="AG13" s="15"/>
-      <c r="AH13" s="15"/>
-      <c r="AI13" s="15"/>
-      <c r="AJ13" s="15"/>
-      <c r="AK13" s="15"/>
-      <c r="AL13" s="15"/>
-      <c r="AM13" s="15"/>
-      <c r="AN13" s="15"/>
-      <c r="AO13" s="15"/>
-      <c r="AP13" s="15"/>
-      <c r="AQ13" s="15"/>
-      <c r="AR13" s="15"/>
-      <c r="AS13" s="16"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="14"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="14"/>
+      <c r="AJ13" s="14"/>
+      <c r="AK13" s="14"/>
+      <c r="AL13" s="14"/>
+      <c r="AM13" s="14"/>
+      <c r="AN13" s="14"/>
+      <c r="AO13" s="14"/>
+      <c r="AP13" s="14"/>
+      <c r="AQ13" s="14"/>
+      <c r="AR13" s="14"/>
+      <c r="AS13" s="15"/>
       <c r="AT13" s="5"/>
       <c r="AU13" s="6"/>
       <c r="AV13" s="6"/>
@@ -5979,38 +6047,38 @@
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="18" t="s">
-        <v>53</v>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="17" t="s">
+        <v>52</v>
       </c>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-      <c r="V14" s="18"/>
-      <c r="W14" s="18"/>
-      <c r="X14" s="18"/>
-      <c r="Y14" s="18"/>
-      <c r="Z14" s="18"/>
-      <c r="AA14" s="18"/>
-      <c r="AB14" s="18"/>
-      <c r="AC14" s="18"/>
-      <c r="AD14" s="18"/>
-      <c r="AE14" s="18"/>
-      <c r="AF14" s="18"/>
-      <c r="AG14" s="18"/>
-      <c r="AH14" s="18"/>
-      <c r="AI14" s="18"/>
-      <c r="AJ14" s="18"/>
-      <c r="AK14" s="18"/>
-      <c r="AL14" s="18"/>
-      <c r="AM14" s="18"/>
-      <c r="AN14" s="18"/>
-      <c r="AO14" s="18"/>
-      <c r="AP14" s="18"/>
-      <c r="AQ14" s="18"/>
-      <c r="AR14" s="18"/>
-      <c r="AS14" s="19"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="17"/>
+      <c r="AF14" s="17"/>
+      <c r="AG14" s="17"/>
+      <c r="AH14" s="17"/>
+      <c r="AI14" s="17"/>
+      <c r="AJ14" s="17"/>
+      <c r="AK14" s="17"/>
+      <c r="AL14" s="17"/>
+      <c r="AM14" s="17"/>
+      <c r="AN14" s="17"/>
+      <c r="AO14" s="17"/>
+      <c r="AP14" s="17"/>
+      <c r="AQ14" s="17"/>
+      <c r="AR14" s="17"/>
+      <c r="AS14" s="18"/>
       <c r="AT14" s="8"/>
       <c r="AU14" s="10"/>
       <c r="AV14" s="10"/>
@@ -6239,38 +6307,38 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
       <c r="O15" s="11"/>
-      <c r="P15" s="17" t="s">
+      <c r="P15" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="18"/>
-      <c r="W15" s="18"/>
-      <c r="X15" s="18"/>
-      <c r="Y15" s="18"/>
-      <c r="Z15" s="18"/>
-      <c r="AA15" s="18"/>
-      <c r="AB15" s="18"/>
-      <c r="AC15" s="18"/>
-      <c r="AD15" s="18"/>
-      <c r="AE15" s="18"/>
-      <c r="AF15" s="18"/>
-      <c r="AG15" s="18"/>
-      <c r="AH15" s="18"/>
-      <c r="AI15" s="18"/>
-      <c r="AJ15" s="18"/>
-      <c r="AK15" s="18"/>
-      <c r="AL15" s="18"/>
-      <c r="AM15" s="18"/>
-      <c r="AN15" s="18"/>
-      <c r="AO15" s="18"/>
-      <c r="AP15" s="18"/>
-      <c r="AQ15" s="18"/>
-      <c r="AR15" s="18"/>
-      <c r="AS15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
+      <c r="AF15" s="17"/>
+      <c r="AG15" s="17"/>
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="17"/>
+      <c r="AK15" s="17"/>
+      <c r="AL15" s="17"/>
+      <c r="AM15" s="17"/>
+      <c r="AN15" s="17"/>
+      <c r="AO15" s="17"/>
+      <c r="AP15" s="17"/>
+      <c r="AQ15" s="17"/>
+      <c r="AR15" s="17"/>
+      <c r="AS15" s="18"/>
       <c r="AT15" s="8"/>
       <c r="AU15" s="9"/>
       <c r="AV15" s="10"/>
@@ -6500,38 +6568,38 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="11"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="20" t="s">
+      <c r="P16" s="16"/>
+      <c r="Q16" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="18"/>
-      <c r="W16" s="18"/>
-      <c r="X16" s="18"/>
-      <c r="Y16" s="18"/>
-      <c r="Z16" s="18"/>
-      <c r="AA16" s="18"/>
-      <c r="AB16" s="18"/>
-      <c r="AC16" s="18"/>
-      <c r="AD16" s="18"/>
-      <c r="AE16" s="18"/>
-      <c r="AF16" s="18"/>
-      <c r="AG16" s="18"/>
-      <c r="AH16" s="18"/>
-      <c r="AI16" s="18"/>
-      <c r="AJ16" s="18"/>
-      <c r="AK16" s="18"/>
-      <c r="AL16" s="18"/>
-      <c r="AM16" s="18"/>
-      <c r="AN16" s="18"/>
-      <c r="AO16" s="18"/>
-      <c r="AP16" s="18"/>
-      <c r="AQ16" s="18"/>
-      <c r="AR16" s="18"/>
-      <c r="AS16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
+      <c r="AF16" s="17"/>
+      <c r="AG16" s="17"/>
+      <c r="AH16" s="17"/>
+      <c r="AI16" s="17"/>
+      <c r="AJ16" s="17"/>
+      <c r="AK16" s="17"/>
+      <c r="AL16" s="17"/>
+      <c r="AM16" s="17"/>
+      <c r="AN16" s="17"/>
+      <c r="AO16" s="17"/>
+      <c r="AP16" s="17"/>
+      <c r="AQ16" s="17"/>
+      <c r="AR16" s="17"/>
+      <c r="AS16" s="18"/>
       <c r="AT16" s="8"/>
       <c r="AU16" s="9"/>
       <c r="AV16" s="10"/>
@@ -6761,38 +6829,38 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
       <c r="O17" s="11"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="20" t="s">
+      <c r="P17" s="16"/>
+      <c r="Q17" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
-      <c r="V17" s="18"/>
-      <c r="W17" s="18"/>
-      <c r="X17" s="18"/>
-      <c r="Y17" s="18"/>
-      <c r="Z17" s="18"/>
-      <c r="AA17" s="18"/>
-      <c r="AB17" s="18"/>
-      <c r="AC17" s="18"/>
-      <c r="AD17" s="18"/>
-      <c r="AE17" s="18"/>
-      <c r="AF17" s="18"/>
-      <c r="AG17" s="18"/>
-      <c r="AH17" s="18"/>
-      <c r="AI17" s="18"/>
-      <c r="AJ17" s="18"/>
-      <c r="AK17" s="18"/>
-      <c r="AL17" s="18"/>
-      <c r="AM17" s="18"/>
-      <c r="AN17" s="18"/>
-      <c r="AO17" s="18"/>
-      <c r="AP17" s="18"/>
-      <c r="AQ17" s="18"/>
-      <c r="AR17" s="18"/>
-      <c r="AS17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
+      <c r="AF17" s="17"/>
+      <c r="AG17" s="17"/>
+      <c r="AH17" s="17"/>
+      <c r="AI17" s="17"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="17"/>
+      <c r="AL17" s="17"/>
+      <c r="AM17" s="17"/>
+      <c r="AN17" s="17"/>
+      <c r="AO17" s="17"/>
+      <c r="AP17" s="17"/>
+      <c r="AQ17" s="17"/>
+      <c r="AR17" s="17"/>
+      <c r="AS17" s="18"/>
       <c r="AT17" s="8"/>
       <c r="AU17" s="9"/>
       <c r="AV17" s="10"/>
@@ -7022,38 +7090,38 @@
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
       <c r="O18" s="11"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="20" t="s">
+      <c r="P18" s="16"/>
+      <c r="Q18" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="18"/>
-      <c r="W18" s="18"/>
-      <c r="X18" s="18"/>
-      <c r="Y18" s="18"/>
-      <c r="Z18" s="18"/>
-      <c r="AA18" s="18"/>
-      <c r="AB18" s="18"/>
-      <c r="AC18" s="18"/>
-      <c r="AD18" s="18"/>
-      <c r="AE18" s="18"/>
-      <c r="AF18" s="18"/>
-      <c r="AG18" s="18"/>
-      <c r="AH18" s="18"/>
-      <c r="AI18" s="18"/>
-      <c r="AJ18" s="18"/>
-      <c r="AK18" s="18"/>
-      <c r="AL18" s="18"/>
-      <c r="AM18" s="18"/>
-      <c r="AN18" s="18"/>
-      <c r="AO18" s="18"/>
-      <c r="AP18" s="18"/>
-      <c r="AQ18" s="18"/>
-      <c r="AR18" s="18"/>
-      <c r="AS18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
+      <c r="AC18" s="17"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
+      <c r="AF18" s="17"/>
+      <c r="AG18" s="17"/>
+      <c r="AH18" s="17"/>
+      <c r="AI18" s="17"/>
+      <c r="AJ18" s="17"/>
+      <c r="AK18" s="17"/>
+      <c r="AL18" s="17"/>
+      <c r="AM18" s="17"/>
+      <c r="AN18" s="17"/>
+      <c r="AO18" s="17"/>
+      <c r="AP18" s="17"/>
+      <c r="AQ18" s="17"/>
+      <c r="AR18" s="17"/>
+      <c r="AS18" s="18"/>
       <c r="AT18" s="8"/>
       <c r="AU18" s="9"/>
       <c r="AV18" s="10"/>
@@ -7285,38 +7353,38 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
       <c r="O19" s="11"/>
-      <c r="P19" s="17" t="s">
+      <c r="P19" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="18"/>
-      <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
-      <c r="Y19" s="18"/>
-      <c r="Z19" s="18"/>
-      <c r="AA19" s="18"/>
-      <c r="AB19" s="18"/>
-      <c r="AC19" s="18"/>
-      <c r="AD19" s="18"/>
-      <c r="AE19" s="18"/>
-      <c r="AF19" s="18"/>
-      <c r="AG19" s="18"/>
-      <c r="AH19" s="18"/>
-      <c r="AI19" s="18"/>
-      <c r="AJ19" s="18"/>
-      <c r="AK19" s="18"/>
-      <c r="AL19" s="18"/>
-      <c r="AM19" s="18"/>
-      <c r="AN19" s="18"/>
-      <c r="AO19" s="18"/>
-      <c r="AP19" s="18"/>
-      <c r="AQ19" s="18"/>
-      <c r="AR19" s="18"/>
-      <c r="AS19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="17"/>
+      <c r="AG19" s="17"/>
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="17"/>
+      <c r="AL19" s="17"/>
+      <c r="AM19" s="17"/>
+      <c r="AN19" s="17"/>
+      <c r="AO19" s="17"/>
+      <c r="AP19" s="17"/>
+      <c r="AQ19" s="17"/>
+      <c r="AR19" s="17"/>
+      <c r="AS19" s="18"/>
       <c r="AT19" s="8"/>
       <c r="AU19" s="9"/>
       <c r="AV19" s="10"/>
@@ -7546,38 +7614,38 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="11"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="20" t="s">
+      <c r="P20" s="16"/>
+      <c r="Q20" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-      <c r="Y20" s="18"/>
-      <c r="Z20" s="18"/>
-      <c r="AA20" s="18"/>
-      <c r="AB20" s="18"/>
-      <c r="AC20" s="18"/>
-      <c r="AD20" s="18"/>
-      <c r="AE20" s="18"/>
-      <c r="AF20" s="18"/>
-      <c r="AG20" s="18"/>
-      <c r="AH20" s="18"/>
-      <c r="AI20" s="18"/>
-      <c r="AJ20" s="18"/>
-      <c r="AK20" s="18"/>
-      <c r="AL20" s="18"/>
-      <c r="AM20" s="18"/>
-      <c r="AN20" s="18"/>
-      <c r="AO20" s="18"/>
-      <c r="AP20" s="18"/>
-      <c r="AQ20" s="18"/>
-      <c r="AR20" s="18"/>
-      <c r="AS20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="17"/>
+      <c r="AF20" s="17"/>
+      <c r="AG20" s="17"/>
+      <c r="AH20" s="17"/>
+      <c r="AI20" s="17"/>
+      <c r="AJ20" s="17"/>
+      <c r="AK20" s="17"/>
+      <c r="AL20" s="17"/>
+      <c r="AM20" s="17"/>
+      <c r="AN20" s="17"/>
+      <c r="AO20" s="17"/>
+      <c r="AP20" s="17"/>
+      <c r="AQ20" s="17"/>
+      <c r="AR20" s="17"/>
+      <c r="AS20" s="18"/>
       <c r="AT20" s="8"/>
       <c r="AU20" s="9"/>
       <c r="AV20" s="10"/>
@@ -7807,38 +7875,38 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
       <c r="O21" s="11"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="18" t="s">
+      <c r="P21" s="16"/>
+      <c r="Q21" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="18"/>
-      <c r="AB21" s="18"/>
-      <c r="AC21" s="18"/>
-      <c r="AD21" s="18"/>
-      <c r="AE21" s="18"/>
-      <c r="AF21" s="18"/>
-      <c r="AG21" s="18"/>
-      <c r="AH21" s="18"/>
-      <c r="AI21" s="18"/>
-      <c r="AJ21" s="18"/>
-      <c r="AK21" s="18"/>
-      <c r="AL21" s="18"/>
-      <c r="AM21" s="18"/>
-      <c r="AN21" s="18"/>
-      <c r="AO21" s="18"/>
-      <c r="AP21" s="18"/>
-      <c r="AQ21" s="18"/>
-      <c r="AR21" s="18"/>
-      <c r="AS21" s="19"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
+      <c r="AC21" s="17"/>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
+      <c r="AF21" s="17"/>
+      <c r="AG21" s="17"/>
+      <c r="AH21" s="17"/>
+      <c r="AI21" s="17"/>
+      <c r="AJ21" s="17"/>
+      <c r="AK21" s="17"/>
+      <c r="AL21" s="17"/>
+      <c r="AM21" s="17"/>
+      <c r="AN21" s="17"/>
+      <c r="AO21" s="17"/>
+      <c r="AP21" s="17"/>
+      <c r="AQ21" s="17"/>
+      <c r="AR21" s="17"/>
+      <c r="AS21" s="18"/>
       <c r="AT21" s="8"/>
       <c r="AU21" s="9"/>
       <c r="AV21" s="10"/>
@@ -8069,38 +8137,38 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
       <c r="O22" s="11"/>
-      <c r="P22" s="17" t="s">
-        <v>52</v>
+      <c r="P22" s="44" t="s">
+        <v>62</v>
       </c>
-      <c r="Q22" s="18"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="18"/>
-      <c r="W22" s="18"/>
-      <c r="X22" s="18"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="18"/>
-      <c r="AA22" s="18"/>
-      <c r="AB22" s="18"/>
-      <c r="AC22" s="18"/>
-      <c r="AD22" s="18"/>
-      <c r="AE22" s="18"/>
-      <c r="AF22" s="18"/>
-      <c r="AG22" s="18"/>
-      <c r="AH22" s="18"/>
-      <c r="AI22" s="18"/>
-      <c r="AJ22" s="18"/>
-      <c r="AK22" s="18"/>
-      <c r="AL22" s="18"/>
-      <c r="AM22" s="18"/>
-      <c r="AN22" s="18"/>
-      <c r="AO22" s="18"/>
-      <c r="AP22" s="18"/>
-      <c r="AQ22" s="18"/>
-      <c r="AR22" s="18"/>
-      <c r="AS22" s="19"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="17"/>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
+      <c r="AC22" s="17"/>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
+      <c r="AF22" s="17"/>
+      <c r="AG22" s="17"/>
+      <c r="AH22" s="17"/>
+      <c r="AI22" s="17"/>
+      <c r="AJ22" s="17"/>
+      <c r="AK22" s="17"/>
+      <c r="AL22" s="17"/>
+      <c r="AM22" s="17"/>
+      <c r="AN22" s="17"/>
+      <c r="AO22" s="17"/>
+      <c r="AP22" s="17"/>
+      <c r="AQ22" s="17"/>
+      <c r="AR22" s="17"/>
+      <c r="AS22" s="18"/>
       <c r="AT22" s="8"/>
       <c r="AU22" s="10"/>
       <c r="AV22" s="10"/>
@@ -8331,38 +8399,38 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
       <c r="O23" s="11"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="22" t="s">
-        <v>55</v>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="21" t="s">
+        <v>54</v>
       </c>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="18"/>
-      <c r="AA23" s="18"/>
-      <c r="AB23" s="18"/>
-      <c r="AC23" s="18"/>
-      <c r="AD23" s="18"/>
-      <c r="AE23" s="18"/>
-      <c r="AF23" s="18"/>
-      <c r="AG23" s="18"/>
-      <c r="AH23" s="18"/>
-      <c r="AI23" s="18"/>
-      <c r="AJ23" s="18"/>
-      <c r="AK23" s="18"/>
-      <c r="AL23" s="18"/>
-      <c r="AM23" s="18"/>
-      <c r="AN23" s="18"/>
-      <c r="AO23" s="18"/>
-      <c r="AP23" s="18"/>
-      <c r="AQ23" s="18"/>
-      <c r="AR23" s="18"/>
-      <c r="AS23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
+      <c r="Z23" s="17"/>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="17"/>
+      <c r="AC23" s="17"/>
+      <c r="AD23" s="17"/>
+      <c r="AE23" s="17"/>
+      <c r="AF23" s="17"/>
+      <c r="AG23" s="17"/>
+      <c r="AH23" s="17"/>
+      <c r="AI23" s="17"/>
+      <c r="AJ23" s="17"/>
+      <c r="AK23" s="17"/>
+      <c r="AL23" s="17"/>
+      <c r="AM23" s="17"/>
+      <c r="AN23" s="17"/>
+      <c r="AO23" s="17"/>
+      <c r="AP23" s="17"/>
+      <c r="AQ23" s="17"/>
+      <c r="AR23" s="17"/>
+      <c r="AS23" s="18"/>
       <c r="AT23" s="8"/>
       <c r="AU23" s="10"/>
       <c r="AV23" s="10"/>
@@ -8593,38 +8661,38 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="11"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="20" t="s">
-        <v>56</v>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="19" t="s">
+        <v>57</v>
       </c>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="18"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="18"/>
-      <c r="AB24" s="18"/>
-      <c r="AC24" s="18"/>
-      <c r="AD24" s="18"/>
-      <c r="AE24" s="18"/>
-      <c r="AF24" s="18"/>
-      <c r="AG24" s="18"/>
-      <c r="AH24" s="18"/>
-      <c r="AI24" s="18"/>
-      <c r="AJ24" s="18"/>
-      <c r="AK24" s="18"/>
-      <c r="AL24" s="18"/>
-      <c r="AM24" s="18"/>
-      <c r="AN24" s="18"/>
-      <c r="AO24" s="18"/>
-      <c r="AP24" s="18"/>
-      <c r="AQ24" s="18"/>
-      <c r="AR24" s="18"/>
-      <c r="AS24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
+      <c r="Z24" s="17"/>
+      <c r="AA24" s="17"/>
+      <c r="AB24" s="17"/>
+      <c r="AC24" s="17"/>
+      <c r="AD24" s="17"/>
+      <c r="AE24" s="17"/>
+      <c r="AF24" s="17"/>
+      <c r="AG24" s="17"/>
+      <c r="AH24" s="17"/>
+      <c r="AI24" s="17"/>
+      <c r="AJ24" s="17"/>
+      <c r="AK24" s="17"/>
+      <c r="AL24" s="17"/>
+      <c r="AM24" s="17"/>
+      <c r="AN24" s="17"/>
+      <c r="AO24" s="17"/>
+      <c r="AP24" s="17"/>
+      <c r="AQ24" s="17"/>
+      <c r="AR24" s="17"/>
+      <c r="AS24" s="18"/>
       <c r="AT24" s="8"/>
       <c r="AU24" s="10"/>
       <c r="AV24" s="10"/>
@@ -8855,41 +8923,38 @@
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
       <c r="O25" s="11"/>
-      <c r="P25" s="21" t="s">
-        <v>57</v>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="21"/>
+      <c r="S25" s="19" t="s">
+        <v>59</v>
       </c>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="18"/>
-      <c r="T25" s="18"/>
-      <c r="U25" s="20"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="18"/>
-      <c r="X25" s="18"/>
-      <c r="Y25" s="18"/>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="18"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="18"/>
-      <c r="AD25" s="18"/>
-      <c r="AE25" s="18"/>
-      <c r="AF25" s="18"/>
-      <c r="AG25" s="18"/>
-      <c r="AH25" s="18"/>
-      <c r="AI25" s="18"/>
-      <c r="AJ25" s="18"/>
-      <c r="AK25" s="18"/>
-      <c r="AL25" s="18"/>
-      <c r="AM25" s="18"/>
-      <c r="AN25" s="18"/>
-      <c r="AO25" s="18"/>
-      <c r="AP25" s="18"/>
-      <c r="AQ25" s="18"/>
-      <c r="AR25" s="18"/>
-      <c r="AS25" s="19"/>
-      <c r="AT25" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="T25" s="19"/>
+      <c r="U25" s="22"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+      <c r="Z25" s="17"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="17"/>
+      <c r="AC25" s="17"/>
+      <c r="AD25" s="17"/>
+      <c r="AE25" s="17"/>
+      <c r="AF25" s="17"/>
+      <c r="AG25" s="17"/>
+      <c r="AH25" s="17"/>
+      <c r="AI25" s="17"/>
+      <c r="AJ25" s="17"/>
+      <c r="AK25" s="17"/>
+      <c r="AL25" s="17"/>
+      <c r="AM25" s="17"/>
+      <c r="AN25" s="17"/>
+      <c r="AO25" s="17"/>
+      <c r="AP25" s="17"/>
+      <c r="AQ25" s="17"/>
+      <c r="AR25" s="17"/>
+      <c r="AS25" s="18"/>
+      <c r="AT25" s="8"/>
       <c r="AU25" s="10"/>
       <c r="AV25" s="10"/>
       <c r="AW25" s="10"/>
@@ -9119,36 +9184,38 @@
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
       <c r="O26" s="11"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="18"/>
-      <c r="AE26" s="18"/>
-      <c r="AF26" s="18"/>
-      <c r="AG26" s="18"/>
-      <c r="AH26" s="18"/>
-      <c r="AI26" s="18"/>
-      <c r="AJ26" s="18"/>
-      <c r="AK26" s="18"/>
-      <c r="AL26" s="18"/>
-      <c r="AM26" s="18"/>
-      <c r="AN26" s="18"/>
-      <c r="AO26" s="18"/>
-      <c r="AP26" s="18"/>
-      <c r="AQ26" s="18"/>
-      <c r="AR26" s="18"/>
-      <c r="AS26" s="19"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="T26" s="19"/>
+      <c r="U26" s="22"/>
+      <c r="V26" s="22"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
+      <c r="Z26" s="17"/>
+      <c r="AA26" s="17"/>
+      <c r="AB26" s="17"/>
+      <c r="AC26" s="17"/>
+      <c r="AD26" s="17"/>
+      <c r="AE26" s="17"/>
+      <c r="AF26" s="17"/>
+      <c r="AG26" s="17"/>
+      <c r="AH26" s="17"/>
+      <c r="AI26" s="17"/>
+      <c r="AJ26" s="17"/>
+      <c r="AK26" s="17"/>
+      <c r="AL26" s="17"/>
+      <c r="AM26" s="17"/>
+      <c r="AN26" s="17"/>
+      <c r="AO26" s="17"/>
+      <c r="AP26" s="17"/>
+      <c r="AQ26" s="17"/>
+      <c r="AR26" s="17"/>
+      <c r="AS26" s="18"/>
       <c r="AT26" s="8"/>
       <c r="AU26" s="10"/>
       <c r="AV26" s="10"/>
@@ -9379,36 +9446,38 @@
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
       <c r="O27" s="11"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="18"/>
-      <c r="X27" s="18"/>
-      <c r="Y27" s="18"/>
-      <c r="Z27" s="18"/>
-      <c r="AA27" s="18"/>
-      <c r="AB27" s="18"/>
-      <c r="AC27" s="18"/>
-      <c r="AD27" s="18"/>
-      <c r="AE27" s="18"/>
-      <c r="AF27" s="18"/>
-      <c r="AG27" s="18"/>
-      <c r="AH27" s="18"/>
-      <c r="AI27" s="18"/>
-      <c r="AJ27" s="18"/>
-      <c r="AK27" s="18"/>
-      <c r="AL27" s="18"/>
-      <c r="AM27" s="18"/>
-      <c r="AN27" s="18"/>
-      <c r="AO27" s="18"/>
-      <c r="AP27" s="18"/>
-      <c r="AQ27" s="18"/>
-      <c r="AR27" s="18"/>
-      <c r="AS27" s="19"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="T27" s="19"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="22"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="17"/>
+      <c r="AA27" s="17"/>
+      <c r="AB27" s="17"/>
+      <c r="AC27" s="17"/>
+      <c r="AD27" s="17"/>
+      <c r="AE27" s="17"/>
+      <c r="AF27" s="17"/>
+      <c r="AG27" s="17"/>
+      <c r="AH27" s="17"/>
+      <c r="AI27" s="17"/>
+      <c r="AJ27" s="17"/>
+      <c r="AK27" s="17"/>
+      <c r="AL27" s="17"/>
+      <c r="AM27" s="17"/>
+      <c r="AN27" s="17"/>
+      <c r="AO27" s="17"/>
+      <c r="AP27" s="17"/>
+      <c r="AQ27" s="17"/>
+      <c r="AR27" s="17"/>
+      <c r="AS27" s="18"/>
       <c r="AT27" s="8"/>
       <c r="AU27" s="10"/>
       <c r="AV27" s="10"/>
@@ -9624,67 +9693,69 @@
       <c r="IX27" s="1"/>
     </row>
     <row r="28" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="13"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="13"/>
-      <c r="AB28" s="13"/>
-      <c r="AC28" s="13"/>
-      <c r="AD28" s="13"/>
-      <c r="AE28" s="13"/>
-      <c r="AF28" s="13"/>
-      <c r="AG28" s="13"/>
-      <c r="AH28" s="13"/>
-      <c r="AI28" s="13"/>
-      <c r="AJ28" s="13"/>
-      <c r="AK28" s="13"/>
-      <c r="AL28" s="13"/>
-      <c r="AM28" s="13"/>
-      <c r="AN28" s="13"/>
-      <c r="AO28" s="13"/>
-      <c r="AP28" s="13"/>
-      <c r="AQ28" s="13"/>
-      <c r="AR28" s="13"/>
-      <c r="AS28" s="13"/>
-      <c r="AT28" s="13"/>
-      <c r="AU28" s="13"/>
-      <c r="AV28" s="13"/>
-      <c r="AW28" s="13"/>
-      <c r="AX28" s="13"/>
-      <c r="AY28" s="13"/>
-      <c r="AZ28" s="13"/>
-      <c r="BA28" s="13"/>
-      <c r="BB28" s="13"/>
-      <c r="BC28" s="13"/>
-      <c r="BD28" s="13"/>
-      <c r="BE28" s="13"/>
-      <c r="BF28" s="13"/>
-      <c r="BG28" s="13"/>
-      <c r="BH28" s="13"/>
-      <c r="BI28" s="13"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="17"/>
+      <c r="AF28" s="17"/>
+      <c r="AG28" s="17"/>
+      <c r="AH28" s="17"/>
+      <c r="AI28" s="17"/>
+      <c r="AJ28" s="17"/>
+      <c r="AK28" s="17"/>
+      <c r="AL28" s="17"/>
+      <c r="AM28" s="17"/>
+      <c r="AN28" s="17"/>
+      <c r="AO28" s="17"/>
+      <c r="AP28" s="17"/>
+      <c r="AQ28" s="17"/>
+      <c r="AR28" s="17"/>
+      <c r="AS28" s="18"/>
+      <c r="AT28" s="8"/>
+      <c r="AU28" s="10"/>
+      <c r="AV28" s="10"/>
+      <c r="AW28" s="10"/>
+      <c r="AX28" s="10"/>
+      <c r="AY28" s="10"/>
+      <c r="AZ28" s="10"/>
+      <c r="BA28" s="10"/>
+      <c r="BB28" s="10"/>
+      <c r="BC28" s="10"/>
+      <c r="BD28" s="10"/>
+      <c r="BE28" s="10"/>
+      <c r="BF28" s="10"/>
+      <c r="BG28" s="10"/>
+      <c r="BH28" s="10"/>
+      <c r="BI28" s="11"/>
       <c r="BJ28" s="1"/>
       <c r="BK28" s="1"/>
       <c r="BL28" s="1"/>
@@ -9883,27 +9954,1057 @@
       <c r="IW28" s="1"/>
       <c r="IX28" s="1"/>
     </row>
+    <row r="29" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q29" s="21"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
+      <c r="AF29" s="17"/>
+      <c r="AG29" s="17"/>
+      <c r="AH29" s="17"/>
+      <c r="AI29" s="17"/>
+      <c r="AJ29" s="17"/>
+      <c r="AK29" s="17"/>
+      <c r="AL29" s="17"/>
+      <c r="AM29" s="17"/>
+      <c r="AN29" s="17"/>
+      <c r="AO29" s="17"/>
+      <c r="AP29" s="17"/>
+      <c r="AQ29" s="17"/>
+      <c r="AR29" s="17"/>
+      <c r="AS29" s="18"/>
+      <c r="AT29" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AU29" s="10"/>
+      <c r="AV29" s="10"/>
+      <c r="AW29" s="10"/>
+      <c r="AX29" s="10"/>
+      <c r="AY29" s="10"/>
+      <c r="AZ29" s="10"/>
+      <c r="BA29" s="10"/>
+      <c r="BB29" s="10"/>
+      <c r="BC29" s="10"/>
+      <c r="BD29" s="10"/>
+      <c r="BE29" s="10"/>
+      <c r="BF29" s="10"/>
+      <c r="BG29" s="10"/>
+      <c r="BH29" s="10"/>
+      <c r="BI29" s="11"/>
+      <c r="BJ29" s="1"/>
+      <c r="BK29" s="1"/>
+      <c r="BL29" s="1"/>
+      <c r="BM29" s="1"/>
+      <c r="BN29" s="1"/>
+      <c r="BO29" s="1"/>
+      <c r="BP29" s="1"/>
+      <c r="BQ29" s="1"/>
+      <c r="BR29" s="1"/>
+      <c r="BS29" s="1"/>
+      <c r="BT29" s="1"/>
+      <c r="BU29" s="1"/>
+      <c r="BV29" s="1"/>
+      <c r="BW29" s="1"/>
+      <c r="BX29" s="1"/>
+      <c r="BY29" s="1"/>
+      <c r="BZ29" s="1"/>
+      <c r="CA29" s="1"/>
+      <c r="CB29" s="1"/>
+      <c r="CC29" s="1"/>
+      <c r="CD29" s="1"/>
+      <c r="CE29" s="1"/>
+      <c r="CF29" s="1"/>
+      <c r="CG29" s="1"/>
+      <c r="CH29" s="1"/>
+      <c r="CI29" s="1"/>
+      <c r="CJ29" s="1"/>
+      <c r="CK29" s="1"/>
+      <c r="CL29" s="1"/>
+      <c r="CM29" s="1"/>
+      <c r="CN29" s="1"/>
+      <c r="CO29" s="1"/>
+      <c r="CP29" s="1"/>
+      <c r="CQ29" s="1"/>
+      <c r="CR29" s="1"/>
+      <c r="CS29" s="1"/>
+      <c r="CT29" s="1"/>
+      <c r="CU29" s="1"/>
+      <c r="CV29" s="1"/>
+      <c r="CW29" s="1"/>
+      <c r="CX29" s="1"/>
+      <c r="CY29" s="1"/>
+      <c r="CZ29" s="1"/>
+      <c r="DA29" s="1"/>
+      <c r="DB29" s="1"/>
+      <c r="DC29" s="1"/>
+      <c r="DD29" s="1"/>
+      <c r="DE29" s="1"/>
+      <c r="DF29" s="1"/>
+      <c r="DG29" s="1"/>
+      <c r="DH29" s="1"/>
+      <c r="DI29" s="1"/>
+      <c r="DJ29" s="1"/>
+      <c r="DK29" s="1"/>
+      <c r="DL29" s="1"/>
+      <c r="DM29" s="1"/>
+      <c r="DN29" s="1"/>
+      <c r="DO29" s="1"/>
+      <c r="DP29" s="1"/>
+      <c r="DQ29" s="1"/>
+      <c r="DR29" s="1"/>
+      <c r="DS29" s="1"/>
+      <c r="DT29" s="1"/>
+      <c r="DU29" s="1"/>
+      <c r="DV29" s="1"/>
+      <c r="DW29" s="1"/>
+      <c r="DX29" s="1"/>
+      <c r="DY29" s="1"/>
+      <c r="DZ29" s="1"/>
+      <c r="EA29" s="1"/>
+      <c r="EB29" s="1"/>
+      <c r="EC29" s="1"/>
+      <c r="ED29" s="1"/>
+      <c r="EE29" s="1"/>
+      <c r="EF29" s="1"/>
+      <c r="EG29" s="1"/>
+      <c r="EH29" s="1"/>
+      <c r="EI29" s="1"/>
+      <c r="EJ29" s="1"/>
+      <c r="EK29" s="1"/>
+      <c r="EL29" s="1"/>
+      <c r="EM29" s="1"/>
+      <c r="EN29" s="1"/>
+      <c r="EO29" s="1"/>
+      <c r="EP29" s="1"/>
+      <c r="EQ29" s="1"/>
+      <c r="ER29" s="1"/>
+      <c r="ES29" s="1"/>
+      <c r="ET29" s="1"/>
+      <c r="EU29" s="1"/>
+      <c r="EV29" s="1"/>
+      <c r="EW29" s="1"/>
+      <c r="EX29" s="1"/>
+      <c r="EY29" s="1"/>
+      <c r="EZ29" s="1"/>
+      <c r="FA29" s="1"/>
+      <c r="FB29" s="1"/>
+      <c r="FC29" s="1"/>
+      <c r="FD29" s="1"/>
+      <c r="FE29" s="1"/>
+      <c r="FF29" s="1"/>
+      <c r="FG29" s="1"/>
+      <c r="FH29" s="1"/>
+      <c r="FI29" s="1"/>
+      <c r="FJ29" s="1"/>
+      <c r="FK29" s="1"/>
+      <c r="FL29" s="1"/>
+      <c r="FM29" s="1"/>
+      <c r="FN29" s="1"/>
+      <c r="FO29" s="1"/>
+      <c r="FP29" s="1"/>
+      <c r="FQ29" s="1"/>
+      <c r="FR29" s="1"/>
+      <c r="FS29" s="1"/>
+      <c r="FT29" s="1"/>
+      <c r="FU29" s="1"/>
+      <c r="FV29" s="1"/>
+      <c r="FW29" s="1"/>
+      <c r="FX29" s="1"/>
+      <c r="FY29" s="1"/>
+      <c r="FZ29" s="1"/>
+      <c r="GA29" s="1"/>
+      <c r="GB29" s="1"/>
+      <c r="GC29" s="1"/>
+      <c r="GD29" s="1"/>
+      <c r="GE29" s="1"/>
+      <c r="GF29" s="1"/>
+      <c r="GG29" s="1"/>
+      <c r="GH29" s="1"/>
+      <c r="GI29" s="1"/>
+      <c r="GJ29" s="1"/>
+      <c r="GK29" s="1"/>
+      <c r="GL29" s="1"/>
+      <c r="GM29" s="1"/>
+      <c r="GN29" s="1"/>
+      <c r="GO29" s="1"/>
+      <c r="GP29" s="1"/>
+      <c r="GQ29" s="1"/>
+      <c r="GR29" s="1"/>
+      <c r="GS29" s="1"/>
+      <c r="GT29" s="1"/>
+      <c r="GU29" s="1"/>
+      <c r="GV29" s="1"/>
+      <c r="GW29" s="1"/>
+      <c r="GX29" s="1"/>
+      <c r="GY29" s="1"/>
+      <c r="GZ29" s="1"/>
+      <c r="HA29" s="1"/>
+      <c r="HB29" s="1"/>
+      <c r="HC29" s="1"/>
+      <c r="HD29" s="1"/>
+      <c r="HE29" s="1"/>
+      <c r="HF29" s="1"/>
+      <c r="HG29" s="1"/>
+      <c r="HH29" s="1"/>
+      <c r="HI29" s="1"/>
+      <c r="HJ29" s="1"/>
+      <c r="HK29" s="1"/>
+      <c r="HL29" s="1"/>
+      <c r="HM29" s="1"/>
+      <c r="HN29" s="1"/>
+      <c r="HO29" s="1"/>
+      <c r="HP29" s="1"/>
+      <c r="HQ29" s="1"/>
+      <c r="HR29" s="1"/>
+      <c r="HS29" s="1"/>
+      <c r="HT29" s="1"/>
+      <c r="HU29" s="1"/>
+      <c r="HV29" s="1"/>
+      <c r="HW29" s="1"/>
+      <c r="HX29" s="1"/>
+      <c r="HY29" s="1"/>
+      <c r="HZ29" s="1"/>
+      <c r="IA29" s="1"/>
+      <c r="IB29" s="1"/>
+      <c r="IC29" s="1"/>
+      <c r="ID29" s="1"/>
+      <c r="IE29" s="1"/>
+      <c r="IF29" s="1"/>
+      <c r="IG29" s="1"/>
+      <c r="IH29" s="1"/>
+      <c r="II29" s="1"/>
+      <c r="IJ29" s="1"/>
+      <c r="IK29" s="1"/>
+      <c r="IL29" s="1"/>
+      <c r="IM29" s="1"/>
+      <c r="IN29" s="1"/>
+      <c r="IO29" s="1"/>
+      <c r="IP29" s="1"/>
+      <c r="IQ29" s="1"/>
+      <c r="IR29" s="1"/>
+      <c r="IS29" s="1"/>
+      <c r="IT29" s="1"/>
+      <c r="IU29" s="1"/>
+      <c r="IV29" s="1"/>
+      <c r="IW29" s="1"/>
+      <c r="IX29" s="1"/>
+    </row>
+    <row r="30" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="21"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="17"/>
+      <c r="AA30" s="17"/>
+      <c r="AB30" s="17"/>
+      <c r="AC30" s="17"/>
+      <c r="AD30" s="17"/>
+      <c r="AE30" s="17"/>
+      <c r="AF30" s="17"/>
+      <c r="AG30" s="17"/>
+      <c r="AH30" s="17"/>
+      <c r="AI30" s="17"/>
+      <c r="AJ30" s="17"/>
+      <c r="AK30" s="17"/>
+      <c r="AL30" s="17"/>
+      <c r="AM30" s="17"/>
+      <c r="AN30" s="17"/>
+      <c r="AO30" s="17"/>
+      <c r="AP30" s="17"/>
+      <c r="AQ30" s="17"/>
+      <c r="AR30" s="17"/>
+      <c r="AS30" s="18"/>
+      <c r="AT30" s="8"/>
+      <c r="AU30" s="10"/>
+      <c r="AV30" s="10"/>
+      <c r="AW30" s="10"/>
+      <c r="AX30" s="10"/>
+      <c r="AY30" s="10"/>
+      <c r="AZ30" s="10"/>
+      <c r="BA30" s="10"/>
+      <c r="BB30" s="10"/>
+      <c r="BC30" s="10"/>
+      <c r="BD30" s="10"/>
+      <c r="BE30" s="10"/>
+      <c r="BF30" s="10"/>
+      <c r="BG30" s="10"/>
+      <c r="BH30" s="10"/>
+      <c r="BI30" s="11"/>
+      <c r="BJ30" s="1"/>
+      <c r="BK30" s="1"/>
+      <c r="BL30" s="1"/>
+      <c r="BM30" s="1"/>
+      <c r="BN30" s="1"/>
+      <c r="BO30" s="1"/>
+      <c r="BP30" s="1"/>
+      <c r="BQ30" s="1"/>
+      <c r="BR30" s="1"/>
+      <c r="BS30" s="1"/>
+      <c r="BT30" s="1"/>
+      <c r="BU30" s="1"/>
+      <c r="BV30" s="1"/>
+      <c r="BW30" s="1"/>
+      <c r="BX30" s="1"/>
+      <c r="BY30" s="1"/>
+      <c r="BZ30" s="1"/>
+      <c r="CA30" s="1"/>
+      <c r="CB30" s="1"/>
+      <c r="CC30" s="1"/>
+      <c r="CD30" s="1"/>
+      <c r="CE30" s="1"/>
+      <c r="CF30" s="1"/>
+      <c r="CG30" s="1"/>
+      <c r="CH30" s="1"/>
+      <c r="CI30" s="1"/>
+      <c r="CJ30" s="1"/>
+      <c r="CK30" s="1"/>
+      <c r="CL30" s="1"/>
+      <c r="CM30" s="1"/>
+      <c r="CN30" s="1"/>
+      <c r="CO30" s="1"/>
+      <c r="CP30" s="1"/>
+      <c r="CQ30" s="1"/>
+      <c r="CR30" s="1"/>
+      <c r="CS30" s="1"/>
+      <c r="CT30" s="1"/>
+      <c r="CU30" s="1"/>
+      <c r="CV30" s="1"/>
+      <c r="CW30" s="1"/>
+      <c r="CX30" s="1"/>
+      <c r="CY30" s="1"/>
+      <c r="CZ30" s="1"/>
+      <c r="DA30" s="1"/>
+      <c r="DB30" s="1"/>
+      <c r="DC30" s="1"/>
+      <c r="DD30" s="1"/>
+      <c r="DE30" s="1"/>
+      <c r="DF30" s="1"/>
+      <c r="DG30" s="1"/>
+      <c r="DH30" s="1"/>
+      <c r="DI30" s="1"/>
+      <c r="DJ30" s="1"/>
+      <c r="DK30" s="1"/>
+      <c r="DL30" s="1"/>
+      <c r="DM30" s="1"/>
+      <c r="DN30" s="1"/>
+      <c r="DO30" s="1"/>
+      <c r="DP30" s="1"/>
+      <c r="DQ30" s="1"/>
+      <c r="DR30" s="1"/>
+      <c r="DS30" s="1"/>
+      <c r="DT30" s="1"/>
+      <c r="DU30" s="1"/>
+      <c r="DV30" s="1"/>
+      <c r="DW30" s="1"/>
+      <c r="DX30" s="1"/>
+      <c r="DY30" s="1"/>
+      <c r="DZ30" s="1"/>
+      <c r="EA30" s="1"/>
+      <c r="EB30" s="1"/>
+      <c r="EC30" s="1"/>
+      <c r="ED30" s="1"/>
+      <c r="EE30" s="1"/>
+      <c r="EF30" s="1"/>
+      <c r="EG30" s="1"/>
+      <c r="EH30" s="1"/>
+      <c r="EI30" s="1"/>
+      <c r="EJ30" s="1"/>
+      <c r="EK30" s="1"/>
+      <c r="EL30" s="1"/>
+      <c r="EM30" s="1"/>
+      <c r="EN30" s="1"/>
+      <c r="EO30" s="1"/>
+      <c r="EP30" s="1"/>
+      <c r="EQ30" s="1"/>
+      <c r="ER30" s="1"/>
+      <c r="ES30" s="1"/>
+      <c r="ET30" s="1"/>
+      <c r="EU30" s="1"/>
+      <c r="EV30" s="1"/>
+      <c r="EW30" s="1"/>
+      <c r="EX30" s="1"/>
+      <c r="EY30" s="1"/>
+      <c r="EZ30" s="1"/>
+      <c r="FA30" s="1"/>
+      <c r="FB30" s="1"/>
+      <c r="FC30" s="1"/>
+      <c r="FD30" s="1"/>
+      <c r="FE30" s="1"/>
+      <c r="FF30" s="1"/>
+      <c r="FG30" s="1"/>
+      <c r="FH30" s="1"/>
+      <c r="FI30" s="1"/>
+      <c r="FJ30" s="1"/>
+      <c r="FK30" s="1"/>
+      <c r="FL30" s="1"/>
+      <c r="FM30" s="1"/>
+      <c r="FN30" s="1"/>
+      <c r="FO30" s="1"/>
+      <c r="FP30" s="1"/>
+      <c r="FQ30" s="1"/>
+      <c r="FR30" s="1"/>
+      <c r="FS30" s="1"/>
+      <c r="FT30" s="1"/>
+      <c r="FU30" s="1"/>
+      <c r="FV30" s="1"/>
+      <c r="FW30" s="1"/>
+      <c r="FX30" s="1"/>
+      <c r="FY30" s="1"/>
+      <c r="FZ30" s="1"/>
+      <c r="GA30" s="1"/>
+      <c r="GB30" s="1"/>
+      <c r="GC30" s="1"/>
+      <c r="GD30" s="1"/>
+      <c r="GE30" s="1"/>
+      <c r="GF30" s="1"/>
+      <c r="GG30" s="1"/>
+      <c r="GH30" s="1"/>
+      <c r="GI30" s="1"/>
+      <c r="GJ30" s="1"/>
+      <c r="GK30" s="1"/>
+      <c r="GL30" s="1"/>
+      <c r="GM30" s="1"/>
+      <c r="GN30" s="1"/>
+      <c r="GO30" s="1"/>
+      <c r="GP30" s="1"/>
+      <c r="GQ30" s="1"/>
+      <c r="GR30" s="1"/>
+      <c r="GS30" s="1"/>
+      <c r="GT30" s="1"/>
+      <c r="GU30" s="1"/>
+      <c r="GV30" s="1"/>
+      <c r="GW30" s="1"/>
+      <c r="GX30" s="1"/>
+      <c r="GY30" s="1"/>
+      <c r="GZ30" s="1"/>
+      <c r="HA30" s="1"/>
+      <c r="HB30" s="1"/>
+      <c r="HC30" s="1"/>
+      <c r="HD30" s="1"/>
+      <c r="HE30" s="1"/>
+      <c r="HF30" s="1"/>
+      <c r="HG30" s="1"/>
+      <c r="HH30" s="1"/>
+      <c r="HI30" s="1"/>
+      <c r="HJ30" s="1"/>
+      <c r="HK30" s="1"/>
+      <c r="HL30" s="1"/>
+      <c r="HM30" s="1"/>
+      <c r="HN30" s="1"/>
+      <c r="HO30" s="1"/>
+      <c r="HP30" s="1"/>
+      <c r="HQ30" s="1"/>
+      <c r="HR30" s="1"/>
+      <c r="HS30" s="1"/>
+      <c r="HT30" s="1"/>
+      <c r="HU30" s="1"/>
+      <c r="HV30" s="1"/>
+      <c r="HW30" s="1"/>
+      <c r="HX30" s="1"/>
+      <c r="HY30" s="1"/>
+      <c r="HZ30" s="1"/>
+      <c r="IA30" s="1"/>
+      <c r="IB30" s="1"/>
+      <c r="IC30" s="1"/>
+      <c r="ID30" s="1"/>
+      <c r="IE30" s="1"/>
+      <c r="IF30" s="1"/>
+      <c r="IG30" s="1"/>
+      <c r="IH30" s="1"/>
+      <c r="II30" s="1"/>
+      <c r="IJ30" s="1"/>
+      <c r="IK30" s="1"/>
+      <c r="IL30" s="1"/>
+      <c r="IM30" s="1"/>
+      <c r="IN30" s="1"/>
+      <c r="IO30" s="1"/>
+      <c r="IP30" s="1"/>
+      <c r="IQ30" s="1"/>
+      <c r="IR30" s="1"/>
+      <c r="IS30" s="1"/>
+      <c r="IT30" s="1"/>
+      <c r="IU30" s="1"/>
+      <c r="IV30" s="1"/>
+      <c r="IW30" s="1"/>
+      <c r="IX30" s="1"/>
+    </row>
+    <row r="31" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="19"/>
+      <c r="U31" s="22"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="17"/>
+      <c r="Y31" s="17"/>
+      <c r="Z31" s="17"/>
+      <c r="AA31" s="17"/>
+      <c r="AB31" s="17"/>
+      <c r="AC31" s="17"/>
+      <c r="AD31" s="17"/>
+      <c r="AE31" s="17"/>
+      <c r="AF31" s="17"/>
+      <c r="AG31" s="17"/>
+      <c r="AH31" s="17"/>
+      <c r="AI31" s="17"/>
+      <c r="AJ31" s="17"/>
+      <c r="AK31" s="17"/>
+      <c r="AL31" s="17"/>
+      <c r="AM31" s="17"/>
+      <c r="AN31" s="17"/>
+      <c r="AO31" s="17"/>
+      <c r="AP31" s="17"/>
+      <c r="AQ31" s="17"/>
+      <c r="AR31" s="17"/>
+      <c r="AS31" s="18"/>
+      <c r="AT31" s="8"/>
+      <c r="AU31" s="10"/>
+      <c r="AV31" s="10"/>
+      <c r="AW31" s="10"/>
+      <c r="AX31" s="10"/>
+      <c r="AY31" s="10"/>
+      <c r="AZ31" s="10"/>
+      <c r="BA31" s="10"/>
+      <c r="BB31" s="10"/>
+      <c r="BC31" s="10"/>
+      <c r="BD31" s="10"/>
+      <c r="BE31" s="10"/>
+      <c r="BF31" s="10"/>
+      <c r="BG31" s="10"/>
+      <c r="BH31" s="10"/>
+      <c r="BI31" s="11"/>
+      <c r="BJ31" s="1"/>
+      <c r="BK31" s="1"/>
+      <c r="BL31" s="1"/>
+      <c r="BM31" s="1"/>
+      <c r="BN31" s="1"/>
+      <c r="BO31" s="1"/>
+      <c r="BP31" s="1"/>
+      <c r="BQ31" s="1"/>
+      <c r="BR31" s="1"/>
+      <c r="BS31" s="1"/>
+      <c r="BT31" s="1"/>
+      <c r="BU31" s="1"/>
+      <c r="BV31" s="1"/>
+      <c r="BW31" s="1"/>
+      <c r="BX31" s="1"/>
+      <c r="BY31" s="1"/>
+      <c r="BZ31" s="1"/>
+      <c r="CA31" s="1"/>
+      <c r="CB31" s="1"/>
+      <c r="CC31" s="1"/>
+      <c r="CD31" s="1"/>
+      <c r="CE31" s="1"/>
+      <c r="CF31" s="1"/>
+      <c r="CG31" s="1"/>
+      <c r="CH31" s="1"/>
+      <c r="CI31" s="1"/>
+      <c r="CJ31" s="1"/>
+      <c r="CK31" s="1"/>
+      <c r="CL31" s="1"/>
+      <c r="CM31" s="1"/>
+      <c r="CN31" s="1"/>
+      <c r="CO31" s="1"/>
+      <c r="CP31" s="1"/>
+      <c r="CQ31" s="1"/>
+      <c r="CR31" s="1"/>
+      <c r="CS31" s="1"/>
+      <c r="CT31" s="1"/>
+      <c r="CU31" s="1"/>
+      <c r="CV31" s="1"/>
+      <c r="CW31" s="1"/>
+      <c r="CX31" s="1"/>
+      <c r="CY31" s="1"/>
+      <c r="CZ31" s="1"/>
+      <c r="DA31" s="1"/>
+      <c r="DB31" s="1"/>
+      <c r="DC31" s="1"/>
+      <c r="DD31" s="1"/>
+      <c r="DE31" s="1"/>
+      <c r="DF31" s="1"/>
+      <c r="DG31" s="1"/>
+      <c r="DH31" s="1"/>
+      <c r="DI31" s="1"/>
+      <c r="DJ31" s="1"/>
+      <c r="DK31" s="1"/>
+      <c r="DL31" s="1"/>
+      <c r="DM31" s="1"/>
+      <c r="DN31" s="1"/>
+      <c r="DO31" s="1"/>
+      <c r="DP31" s="1"/>
+      <c r="DQ31" s="1"/>
+      <c r="DR31" s="1"/>
+      <c r="DS31" s="1"/>
+      <c r="DT31" s="1"/>
+      <c r="DU31" s="1"/>
+      <c r="DV31" s="1"/>
+      <c r="DW31" s="1"/>
+      <c r="DX31" s="1"/>
+      <c r="DY31" s="1"/>
+      <c r="DZ31" s="1"/>
+      <c r="EA31" s="1"/>
+      <c r="EB31" s="1"/>
+      <c r="EC31" s="1"/>
+      <c r="ED31" s="1"/>
+      <c r="EE31" s="1"/>
+      <c r="EF31" s="1"/>
+      <c r="EG31" s="1"/>
+      <c r="EH31" s="1"/>
+      <c r="EI31" s="1"/>
+      <c r="EJ31" s="1"/>
+      <c r="EK31" s="1"/>
+      <c r="EL31" s="1"/>
+      <c r="EM31" s="1"/>
+      <c r="EN31" s="1"/>
+      <c r="EO31" s="1"/>
+      <c r="EP31" s="1"/>
+      <c r="EQ31" s="1"/>
+      <c r="ER31" s="1"/>
+      <c r="ES31" s="1"/>
+      <c r="ET31" s="1"/>
+      <c r="EU31" s="1"/>
+      <c r="EV31" s="1"/>
+      <c r="EW31" s="1"/>
+      <c r="EX31" s="1"/>
+      <c r="EY31" s="1"/>
+      <c r="EZ31" s="1"/>
+      <c r="FA31" s="1"/>
+      <c r="FB31" s="1"/>
+      <c r="FC31" s="1"/>
+      <c r="FD31" s="1"/>
+      <c r="FE31" s="1"/>
+      <c r="FF31" s="1"/>
+      <c r="FG31" s="1"/>
+      <c r="FH31" s="1"/>
+      <c r="FI31" s="1"/>
+      <c r="FJ31" s="1"/>
+      <c r="FK31" s="1"/>
+      <c r="FL31" s="1"/>
+      <c r="FM31" s="1"/>
+      <c r="FN31" s="1"/>
+      <c r="FO31" s="1"/>
+      <c r="FP31" s="1"/>
+      <c r="FQ31" s="1"/>
+      <c r="FR31" s="1"/>
+      <c r="FS31" s="1"/>
+      <c r="FT31" s="1"/>
+      <c r="FU31" s="1"/>
+      <c r="FV31" s="1"/>
+      <c r="FW31" s="1"/>
+      <c r="FX31" s="1"/>
+      <c r="FY31" s="1"/>
+      <c r="FZ31" s="1"/>
+      <c r="GA31" s="1"/>
+      <c r="GB31" s="1"/>
+      <c r="GC31" s="1"/>
+      <c r="GD31" s="1"/>
+      <c r="GE31" s="1"/>
+      <c r="GF31" s="1"/>
+      <c r="GG31" s="1"/>
+      <c r="GH31" s="1"/>
+      <c r="GI31" s="1"/>
+      <c r="GJ31" s="1"/>
+      <c r="GK31" s="1"/>
+      <c r="GL31" s="1"/>
+      <c r="GM31" s="1"/>
+      <c r="GN31" s="1"/>
+      <c r="GO31" s="1"/>
+      <c r="GP31" s="1"/>
+      <c r="GQ31" s="1"/>
+      <c r="GR31" s="1"/>
+      <c r="GS31" s="1"/>
+      <c r="GT31" s="1"/>
+      <c r="GU31" s="1"/>
+      <c r="GV31" s="1"/>
+      <c r="GW31" s="1"/>
+      <c r="GX31" s="1"/>
+      <c r="GY31" s="1"/>
+      <c r="GZ31" s="1"/>
+      <c r="HA31" s="1"/>
+      <c r="HB31" s="1"/>
+      <c r="HC31" s="1"/>
+      <c r="HD31" s="1"/>
+      <c r="HE31" s="1"/>
+      <c r="HF31" s="1"/>
+      <c r="HG31" s="1"/>
+      <c r="HH31" s="1"/>
+      <c r="HI31" s="1"/>
+      <c r="HJ31" s="1"/>
+      <c r="HK31" s="1"/>
+      <c r="HL31" s="1"/>
+      <c r="HM31" s="1"/>
+      <c r="HN31" s="1"/>
+      <c r="HO31" s="1"/>
+      <c r="HP31" s="1"/>
+      <c r="HQ31" s="1"/>
+      <c r="HR31" s="1"/>
+      <c r="HS31" s="1"/>
+      <c r="HT31" s="1"/>
+      <c r="HU31" s="1"/>
+      <c r="HV31" s="1"/>
+      <c r="HW31" s="1"/>
+      <c r="HX31" s="1"/>
+      <c r="HY31" s="1"/>
+      <c r="HZ31" s="1"/>
+      <c r="IA31" s="1"/>
+      <c r="IB31" s="1"/>
+      <c r="IC31" s="1"/>
+      <c r="ID31" s="1"/>
+      <c r="IE31" s="1"/>
+      <c r="IF31" s="1"/>
+      <c r="IG31" s="1"/>
+      <c r="IH31" s="1"/>
+      <c r="II31" s="1"/>
+      <c r="IJ31" s="1"/>
+      <c r="IK31" s="1"/>
+      <c r="IL31" s="1"/>
+      <c r="IM31" s="1"/>
+      <c r="IN31" s="1"/>
+      <c r="IO31" s="1"/>
+      <c r="IP31" s="1"/>
+      <c r="IQ31" s="1"/>
+      <c r="IR31" s="1"/>
+      <c r="IS31" s="1"/>
+      <c r="IT31" s="1"/>
+      <c r="IU31" s="1"/>
+      <c r="IV31" s="1"/>
+      <c r="IW31" s="1"/>
+      <c r="IX31" s="1"/>
+    </row>
+    <row r="32" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="13"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+      <c r="X32" s="13"/>
+      <c r="Y32" s="13"/>
+      <c r="Z32" s="13"/>
+      <c r="AA32" s="13"/>
+      <c r="AB32" s="13"/>
+      <c r="AC32" s="13"/>
+      <c r="AD32" s="13"/>
+      <c r="AE32" s="13"/>
+      <c r="AF32" s="13"/>
+      <c r="AG32" s="13"/>
+      <c r="AH32" s="13"/>
+      <c r="AI32" s="13"/>
+      <c r="AJ32" s="13"/>
+      <c r="AK32" s="13"/>
+      <c r="AL32" s="13"/>
+      <c r="AM32" s="13"/>
+      <c r="AN32" s="13"/>
+      <c r="AO32" s="13"/>
+      <c r="AP32" s="13"/>
+      <c r="AQ32" s="13"/>
+      <c r="AR32" s="13"/>
+      <c r="AS32" s="13"/>
+      <c r="AT32" s="13"/>
+      <c r="AU32" s="13"/>
+      <c r="AV32" s="13"/>
+      <c r="AW32" s="13"/>
+      <c r="AX32" s="13"/>
+      <c r="AY32" s="13"/>
+      <c r="AZ32" s="13"/>
+      <c r="BA32" s="13"/>
+      <c r="BB32" s="13"/>
+      <c r="BC32" s="13"/>
+      <c r="BD32" s="13"/>
+      <c r="BE32" s="13"/>
+      <c r="BF32" s="13"/>
+      <c r="BG32" s="13"/>
+      <c r="BH32" s="13"/>
+      <c r="BI32" s="13"/>
+      <c r="BJ32" s="1"/>
+      <c r="BK32" s="1"/>
+      <c r="BL32" s="1"/>
+      <c r="BM32" s="1"/>
+      <c r="BN32" s="1"/>
+      <c r="BO32" s="1"/>
+      <c r="BP32" s="1"/>
+      <c r="BQ32" s="1"/>
+      <c r="BR32" s="1"/>
+      <c r="BS32" s="1"/>
+      <c r="BT32" s="1"/>
+      <c r="BU32" s="1"/>
+      <c r="BV32" s="1"/>
+      <c r="BW32" s="1"/>
+      <c r="BX32" s="1"/>
+      <c r="BY32" s="1"/>
+      <c r="BZ32" s="1"/>
+      <c r="CA32" s="1"/>
+      <c r="CB32" s="1"/>
+      <c r="CC32" s="1"/>
+      <c r="CD32" s="1"/>
+      <c r="CE32" s="1"/>
+      <c r="CF32" s="1"/>
+      <c r="CG32" s="1"/>
+      <c r="CH32" s="1"/>
+      <c r="CI32" s="1"/>
+      <c r="CJ32" s="1"/>
+      <c r="CK32" s="1"/>
+      <c r="CL32" s="1"/>
+      <c r="CM32" s="1"/>
+      <c r="CN32" s="1"/>
+      <c r="CO32" s="1"/>
+      <c r="CP32" s="1"/>
+      <c r="CQ32" s="1"/>
+      <c r="CR32" s="1"/>
+      <c r="CS32" s="1"/>
+      <c r="CT32" s="1"/>
+      <c r="CU32" s="1"/>
+      <c r="CV32" s="1"/>
+      <c r="CW32" s="1"/>
+      <c r="CX32" s="1"/>
+      <c r="CY32" s="1"/>
+      <c r="CZ32" s="1"/>
+      <c r="DA32" s="1"/>
+      <c r="DB32" s="1"/>
+      <c r="DC32" s="1"/>
+      <c r="DD32" s="1"/>
+      <c r="DE32" s="1"/>
+      <c r="DF32" s="1"/>
+      <c r="DG32" s="1"/>
+      <c r="DH32" s="1"/>
+      <c r="DI32" s="1"/>
+      <c r="DJ32" s="1"/>
+      <c r="DK32" s="1"/>
+      <c r="DL32" s="1"/>
+      <c r="DM32" s="1"/>
+      <c r="DN32" s="1"/>
+      <c r="DO32" s="1"/>
+      <c r="DP32" s="1"/>
+      <c r="DQ32" s="1"/>
+      <c r="DR32" s="1"/>
+      <c r="DS32" s="1"/>
+      <c r="DT32" s="1"/>
+      <c r="DU32" s="1"/>
+      <c r="DV32" s="1"/>
+      <c r="DW32" s="1"/>
+      <c r="DX32" s="1"/>
+      <c r="DY32" s="1"/>
+      <c r="DZ32" s="1"/>
+      <c r="EA32" s="1"/>
+      <c r="EB32" s="1"/>
+      <c r="EC32" s="1"/>
+      <c r="ED32" s="1"/>
+      <c r="EE32" s="1"/>
+      <c r="EF32" s="1"/>
+      <c r="EG32" s="1"/>
+      <c r="EH32" s="1"/>
+      <c r="EI32" s="1"/>
+      <c r="EJ32" s="1"/>
+      <c r="EK32" s="1"/>
+      <c r="EL32" s="1"/>
+      <c r="EM32" s="1"/>
+      <c r="EN32" s="1"/>
+      <c r="EO32" s="1"/>
+      <c r="EP32" s="1"/>
+      <c r="EQ32" s="1"/>
+      <c r="ER32" s="1"/>
+      <c r="ES32" s="1"/>
+      <c r="ET32" s="1"/>
+      <c r="EU32" s="1"/>
+      <c r="EV32" s="1"/>
+      <c r="EW32" s="1"/>
+      <c r="EX32" s="1"/>
+      <c r="EY32" s="1"/>
+      <c r="EZ32" s="1"/>
+      <c r="FA32" s="1"/>
+      <c r="FB32" s="1"/>
+      <c r="FC32" s="1"/>
+      <c r="FD32" s="1"/>
+      <c r="FE32" s="1"/>
+      <c r="FF32" s="1"/>
+      <c r="FG32" s="1"/>
+      <c r="FH32" s="1"/>
+      <c r="FI32" s="1"/>
+      <c r="FJ32" s="1"/>
+      <c r="FK32" s="1"/>
+      <c r="FL32" s="1"/>
+      <c r="FM32" s="1"/>
+      <c r="FN32" s="1"/>
+      <c r="FO32" s="1"/>
+      <c r="FP32" s="1"/>
+      <c r="FQ32" s="1"/>
+      <c r="FR32" s="1"/>
+      <c r="FS32" s="1"/>
+      <c r="FT32" s="1"/>
+      <c r="FU32" s="1"/>
+      <c r="FV32" s="1"/>
+      <c r="FW32" s="1"/>
+      <c r="FX32" s="1"/>
+      <c r="FY32" s="1"/>
+      <c r="FZ32" s="1"/>
+      <c r="GA32" s="1"/>
+      <c r="GB32" s="1"/>
+      <c r="GC32" s="1"/>
+      <c r="GD32" s="1"/>
+      <c r="GE32" s="1"/>
+      <c r="GF32" s="1"/>
+      <c r="GG32" s="1"/>
+      <c r="GH32" s="1"/>
+      <c r="GI32" s="1"/>
+      <c r="GJ32" s="1"/>
+      <c r="GK32" s="1"/>
+      <c r="GL32" s="1"/>
+      <c r="GM32" s="1"/>
+      <c r="GN32" s="1"/>
+      <c r="GO32" s="1"/>
+      <c r="GP32" s="1"/>
+      <c r="GQ32" s="1"/>
+      <c r="GR32" s="1"/>
+      <c r="GS32" s="1"/>
+      <c r="GT32" s="1"/>
+      <c r="GU32" s="1"/>
+      <c r="GV32" s="1"/>
+      <c r="GW32" s="1"/>
+      <c r="GX32" s="1"/>
+      <c r="GY32" s="1"/>
+      <c r="GZ32" s="1"/>
+      <c r="HA32" s="1"/>
+      <c r="HB32" s="1"/>
+      <c r="HC32" s="1"/>
+      <c r="HD32" s="1"/>
+      <c r="HE32" s="1"/>
+      <c r="HF32" s="1"/>
+      <c r="HG32" s="1"/>
+      <c r="HH32" s="1"/>
+      <c r="HI32" s="1"/>
+      <c r="HJ32" s="1"/>
+      <c r="HK32" s="1"/>
+      <c r="HL32" s="1"/>
+      <c r="HM32" s="1"/>
+      <c r="HN32" s="1"/>
+      <c r="HO32" s="1"/>
+      <c r="HP32" s="1"/>
+      <c r="HQ32" s="1"/>
+      <c r="HR32" s="1"/>
+      <c r="HS32" s="1"/>
+      <c r="HT32" s="1"/>
+      <c r="HU32" s="1"/>
+      <c r="HV32" s="1"/>
+      <c r="HW32" s="1"/>
+      <c r="HX32" s="1"/>
+      <c r="HY32" s="1"/>
+      <c r="HZ32" s="1"/>
+      <c r="IA32" s="1"/>
+      <c r="IB32" s="1"/>
+      <c r="IC32" s="1"/>
+      <c r="ID32" s="1"/>
+      <c r="IE32" s="1"/>
+      <c r="IF32" s="1"/>
+      <c r="IG32" s="1"/>
+      <c r="IH32" s="1"/>
+      <c r="II32" s="1"/>
+      <c r="IJ32" s="1"/>
+      <c r="IK32" s="1"/>
+      <c r="IL32" s="1"/>
+      <c r="IM32" s="1"/>
+      <c r="IN32" s="1"/>
+      <c r="IO32" s="1"/>
+      <c r="IP32" s="1"/>
+      <c r="IQ32" s="1"/>
+      <c r="IR32" s="1"/>
+      <c r="IS32" s="1"/>
+      <c r="IT32" s="1"/>
+      <c r="IU32" s="1"/>
+      <c r="IV32" s="1"/>
+      <c r="IW32" s="1"/>
+      <c r="IX32" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:O9"/>
-    <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="P12:AS12"/>
-    <mergeCell ref="AT12:BI12"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="P10:AD10"/>
-    <mergeCell ref="AE10:BI10"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:O8"/>
-    <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="AE8:BI8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
     <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:BI4"/>
@@ -9920,11 +11021,25 @@
     <mergeCell ref="AT1:AZ1"/>
     <mergeCell ref="BA1:BC1"/>
     <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:O8"/>
+    <mergeCell ref="P8:AD8"/>
+    <mergeCell ref="AE8:BI8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="P12:AS12"/>
+    <mergeCell ref="AT12:BI12"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="P10:AD10"/>
+    <mergeCell ref="AE10:BI10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
@@ -9940,6 +11055,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F5656D937027614D93C88AB71AE3D10C" ma:contentTypeVersion="2" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="b60c200d0ae5f270a77b0ce61d313f15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="75fae816-41bf-471e-909f-5205fc9f8b57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="893732230ae29545b6addaf499a489b1" ns2:_="">
     <xsd:import namespace="75fae816-41bf-471e-909f-5205fc9f8b57"/>
@@ -10071,22 +11201,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7560E91F-1ABF-4BEF-A078-A8FA5AD9AA18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10102,21 +11234,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>